--- a/outputs/all_dogs_master.xlsx
+++ b/outputs/all_dogs_master.xlsx
@@ -789,9 +789,7 @@
           <t>PARADISE FLYER</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>62.46385193753615</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -825,15 +823,9 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="n">
-        <v>62.46385193753615</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>62.46385193753615</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>62.46385193753615</v>
-      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
           <t>6/11/2025</t>
@@ -977,9 +969,7 @@
           <t>SCELZI</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -1013,15 +1003,9 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -1165,9 +1149,7 @@
           <t>YUNDERUP TAMMY</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>61.29398410896709</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -1201,15 +1183,9 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="n">
-        <v>61.29398410896709</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>61.29398410896709</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>61.29398410896709</v>
-      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr">
         <is>
           <t>16/10/2025</t>
@@ -1433,9 +1409,7 @@
           <t>PANTHERS MAGIC</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>63.10344827586208</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -1469,15 +1443,9 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="n">
-        <v>63.10344827586208</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>63.10344827586208</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>63.10344827586208</v>
-      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -1621,9 +1589,7 @@
           <t>DON'T PLAY GAMES</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>63.85809312638581</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -1657,15 +1623,9 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="n">
-        <v>63.85809312638581</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>63.85809312638581</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>63.85809312638581</v>
-      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -1809,9 +1769,7 @@
           <t>BOILER MAKER</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>62.46385193753615</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -1845,15 +1803,9 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="n">
-        <v>62.46385193753615</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>62.46385193753615</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>62.46385193753615</v>
-      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
           <t>6/11/2025</t>
@@ -1997,9 +1949,7 @@
           <t>THANK YOU JOE</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>63.44125809435707</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -2033,15 +1983,9 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="n">
-        <v>63.44125809435707</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>63.44125809435707</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>63.44125809435707</v>
-      </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr">
         <is>
           <t>22/10/2025</t>
@@ -2185,9 +2129,7 @@
           <t>HARMONY RHYTHM</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>62.68738574040219</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -2221,15 +2163,9 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="n">
-        <v>62.68738574040219</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>62.68738574040219</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>62.68738574040219</v>
-      </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -2373,9 +2309,7 @@
           <t>SUNSET SKYLIGHT</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>62.46385193753615</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -2409,15 +2343,9 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="n">
-        <v>62.46385193753615</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>62.46385193753615</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>62.46385193753615</v>
-      </c>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr">
         <is>
           <t>6/11/2025</t>
@@ -2561,9 +2489,7 @@
           <t>KILLER KELLY</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>62.23230490018149</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -2597,15 +2523,9 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="n">
-        <v>62.23230490018149</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>62.23230490018149</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>62.23230490018149</v>
-      </c>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -2749,9 +2669,7 @@
           <t>RED HOT BERNIE</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>62.97709923664122</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -2785,15 +2703,9 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="n">
-        <v>62.97709923664122</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>62.97709923664122</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>62.97709923664122</v>
-      </c>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -2937,9 +2849,7 @@
           <t>PREDATOR GUNDI</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>60.69895769466586</v>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -2973,15 +2883,9 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="n">
-        <v>60.69895769466586</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>60.69895769466586</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>60.69895769466586</v>
-      </c>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -3125,9 +3029,7 @@
           <t>BERRIGAN DRIVE</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>61.47915732855223</v>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -3161,15 +3063,9 @@
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="n">
-        <v>61.47915732855223</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>61.47915732855223</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>61.47915732855223</v>
-      </c>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr">
         <is>
           <t>22/10/2025</t>
@@ -3245,9 +3141,7 @@
           <t>HANNAH'S PASSION</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -3281,15 +3175,9 @@
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -3433,9 +3321,7 @@
           <t>AUREATE</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -3469,15 +3355,9 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -3621,9 +3501,7 @@
           <t>WYONG EL PASO</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -3657,15 +3535,9 @@
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -3809,9 +3681,7 @@
           <t>LADY FREYA</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>62.74473924977127</v>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -3845,15 +3715,9 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="n">
-        <v>62.74473924977127</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>62.74473924977127</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>62.74473924977127</v>
-      </c>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -3997,9 +3861,7 @@
           <t>CANYA BON BON</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>61.22285332442365</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -4033,15 +3895,9 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="n">
-        <v>61.22285332442365</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>61.22285332442365</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>61.22285332442365</v>
-      </c>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr">
         <is>
           <t>27/10/2025</t>
@@ -4185,9 +4041,7 @@
           <t>CYCLONIC CLINTON</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>61.9054054054054</v>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -4221,15 +4075,9 @@
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="n">
-        <v>61.9054054054054</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>61.9054054054054</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>61.9054054054054</v>
-      </c>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr">
         <is>
           <t>13/10/2025</t>
@@ -4373,9 +4221,7 @@
           <t>TRUNKEY FRANK</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>62.23404255319149</v>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -4409,15 +4255,9 @@
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="n">
-        <v>62.23404255319149</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>62.23404255319149</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>62.23404255319149</v>
-      </c>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -4561,9 +4401,7 @@
           <t>TRUNKEY REBEL</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>62.97709923664122</v>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -4597,15 +4435,9 @@
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="n">
-        <v>62.97709923664122</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>62.97709923664122</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>62.97709923664122</v>
-      </c>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -4749,9 +4581,7 @@
           <t>SPEEDY DEVILLE</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>62.23230490018149</v>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -4785,15 +4615,9 @@
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="n">
-        <v>62.23230490018149</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>62.23230490018149</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>62.23230490018149</v>
-      </c>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -4937,9 +4761,7 @@
           <t>PECORINO MONELLI</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>63.41637010676158</v>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -4973,15 +4795,9 @@
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="n">
-        <v>63.41637010676158</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>63.41637010676158</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>63.41637010676158</v>
-      </c>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr">
         <is>
           <t>13/10/2025</t>
@@ -5125,9 +4941,7 @@
           <t>DON'T TURN</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>59.63190184049079</v>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
@@ -5161,15 +4975,9 @@
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr"/>
-      <c r="AE49" t="n">
-        <v>59.63190184049079</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>59.63190184049079</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>59.63190184049079</v>
-      </c>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr">
         <is>
           <t>13/10/2025</t>
@@ -5313,9 +5121,7 @@
           <t>CHAMPAGNE CATHY</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
@@ -5349,15 +5155,9 @@
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -5501,9 +5301,7 @@
           <t>ON RED ALERT</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
@@ -5537,15 +5335,9 @@
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr"/>
       <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -5689,9 +5481,7 @@
           <t>HUNTER</t>
         </is>
       </c>
-      <c r="E55" t="n">
-        <v>61.63977609483042</v>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
@@ -5725,15 +5515,9 @@
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr"/>
       <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="n">
-        <v>61.63977609483042</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>61.63977609483042</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>61.63977609483042</v>
-      </c>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr">
         <is>
           <t>29/10/2025</t>
@@ -5877,9 +5661,7 @@
           <t>CYNTHIA KEEPING</t>
         </is>
       </c>
-      <c r="E57" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
@@ -5913,15 +5695,9 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -6065,9 +5841,7 @@
           <t>SEND IT COCO</t>
         </is>
       </c>
-      <c r="E59" t="n">
-        <v>61.75596578117965</v>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
@@ -6101,15 +5875,9 @@
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr"/>
       <c r="AD59" t="inlineStr"/>
-      <c r="AE59" t="n">
-        <v>61.75596578117965</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>61.75596578117965</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>61.75596578117965</v>
-      </c>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr">
         <is>
           <t>8/10/2025</t>
@@ -6253,9 +6021,7 @@
           <t>JUST A BABE</t>
         </is>
       </c>
-      <c r="E61" t="n">
-        <v>62.23404255319149</v>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
@@ -6289,15 +6055,9 @@
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr"/>
       <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="n">
-        <v>62.23404255319149</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>62.23404255319149</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>62.23404255319149</v>
-      </c>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -6441,9 +6201,7 @@
           <t>FEARLESS PARKER</t>
         </is>
       </c>
-      <c r="E63" t="n">
-        <v>64.34316353887401</v>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
@@ -6477,15 +6235,9 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr"/>
       <c r="AD63" t="inlineStr"/>
-      <c r="AE63" t="n">
-        <v>64.34316353887401</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>64.34316353887401</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>64.34316353887401</v>
-      </c>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -6629,9 +6381,7 @@
           <t>REINA</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v>62.68738574040219</v>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
@@ -6665,15 +6415,9 @@
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="inlineStr"/>
-      <c r="AE65" t="n">
-        <v>62.68738574040219</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>62.68738574040219</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>62.68738574040219</v>
-      </c>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -6817,9 +6561,7 @@
           <t>RAPIDO MYSTIQUE</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>60.92307692307693</v>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
@@ -6853,15 +6595,9 @@
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr"/>
       <c r="AD67" t="inlineStr"/>
-      <c r="AE67" t="n">
-        <v>60.92307692307693</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>60.92307692307693</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>60.92307692307693</v>
-      </c>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -7005,9 +6741,7 @@
           <t>BRUISER MY UNCLE</t>
         </is>
       </c>
-      <c r="E69" t="n">
-        <v>62.90956749672346</v>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
@@ -7041,15 +6775,9 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr"/>
       <c r="AD69" t="inlineStr"/>
-      <c r="AE69" t="n">
-        <v>62.90956749672346</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>62.90956749672346</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>62.90956749672346</v>
-      </c>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr">
         <is>
           <t>3/11/2025</t>
@@ -7193,9 +6921,7 @@
           <t>WOODBURN GRACE</t>
         </is>
       </c>
-      <c r="E71" t="n">
-        <v>60.92307692307693</v>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
@@ -7229,15 +6955,9 @@
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr"/>
       <c r="AD71" t="inlineStr"/>
-      <c r="AE71" t="n">
-        <v>60.92307692307693</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>60.92307692307693</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>60.92307692307693</v>
-      </c>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -7313,9 +7033,7 @@
           <t>SUMMER SWELL</t>
         </is>
       </c>
-      <c r="E72" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
@@ -7349,15 +7067,9 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
-      <c r="AE72" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -7433,9 +7145,7 @@
           <t>ARIEL'S DRIVE</t>
         </is>
       </c>
-      <c r="E73" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
@@ -7469,15 +7179,9 @@
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr"/>
       <c r="AD73" t="inlineStr"/>
-      <c r="AE73" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AF73" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AG73" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -7553,9 +7257,7 @@
           <t>IMPRESS NEMO</t>
         </is>
       </c>
-      <c r="E74" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
@@ -7589,15 +7291,9 @@
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr"/>
       <c r="AD74" t="inlineStr"/>
-      <c r="AE74" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AF74" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AG74" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -7741,9 +7437,7 @@
           <t>SPEED CHELLER</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
@@ -7777,15 +7471,9 @@
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr"/>
       <c r="AD76" t="inlineStr"/>
-      <c r="AE76" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -7929,9 +7617,7 @@
           <t>RIPPIN' BLUE</t>
         </is>
       </c>
-      <c r="E78" t="n">
-        <v>62.74473924977127</v>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
@@ -7965,15 +7651,9 @@
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr"/>
       <c r="AD78" t="inlineStr"/>
-      <c r="AE78" t="n">
-        <v>62.74473924977127</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>62.74473924977127</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>62.74473924977127</v>
-      </c>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -8117,9 +7797,7 @@
           <t>FERNDALE FLYER</t>
         </is>
       </c>
-      <c r="E80" t="n">
-        <v>62.882096069869</v>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
@@ -8153,15 +7831,9 @@
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr"/>
       <c r="AD80" t="inlineStr"/>
-      <c r="AE80" t="n">
-        <v>62.882096069869</v>
-      </c>
-      <c r="AF80" t="n">
-        <v>62.882096069869</v>
-      </c>
-      <c r="AG80" t="n">
-        <v>62.882096069869</v>
-      </c>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr">
         <is>
           <t>1/11/2025</t>
@@ -8305,9 +7977,7 @@
           <t>MR</t>
         </is>
       </c>
-      <c r="E82" t="n">
-        <v>62.9004076878276</v>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
@@ -8341,15 +8011,9 @@
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr"/>
-      <c r="AE82" t="n">
-        <v>62.9004076878276</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>62.9004076878276</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>62.9004076878276</v>
-      </c>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr">
         <is>
           <t>30/10/2025</t>
@@ -8493,9 +8157,7 @@
           <t>JUDGE JEBRYNAH</t>
         </is>
       </c>
-      <c r="E84" t="n">
-        <v>60.69895769466586</v>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
@@ -8529,15 +8191,9 @@
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr"/>
       <c r="AD84" t="inlineStr"/>
-      <c r="AE84" t="n">
-        <v>60.69895769466586</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>60.69895769466586</v>
-      </c>
-      <c r="AG84" t="n">
-        <v>60.69895769466586</v>
-      </c>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -8681,9 +8337,7 @@
           <t>INFRARED GEM</t>
         </is>
       </c>
-      <c r="E86" t="n">
-        <v>60.69895769466586</v>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -8717,15 +8371,9 @@
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr"/>
       <c r="AD86" t="inlineStr"/>
-      <c r="AE86" t="n">
-        <v>60.69895769466586</v>
-      </c>
-      <c r="AF86" t="n">
-        <v>60.69895769466586</v>
-      </c>
-      <c r="AG86" t="n">
-        <v>60.69895769466586</v>
-      </c>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -8869,9 +8517,7 @@
           <t>DAIKOKU FLYER</t>
         </is>
       </c>
-      <c r="E88" t="n">
-        <v>61.51898734177216</v>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
@@ -8905,15 +8551,9 @@
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="inlineStr"/>
       <c r="AD88" t="inlineStr"/>
-      <c r="AE88" t="n">
-        <v>61.51898734177216</v>
-      </c>
-      <c r="AF88" t="n">
-        <v>61.51898734177216</v>
-      </c>
-      <c r="AG88" t="n">
-        <v>61.51898734177216</v>
-      </c>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr">
         <is>
           <t>15/09/2025</t>
@@ -9057,9 +8697,7 @@
           <t>CAKE IN TUMMY</t>
         </is>
       </c>
-      <c r="E90" t="n">
-        <v>62.97709923664122</v>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
@@ -9093,15 +8731,9 @@
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr"/>
       <c r="AD90" t="inlineStr"/>
-      <c r="AE90" t="n">
-        <v>62.97709923664122</v>
-      </c>
-      <c r="AF90" t="n">
-        <v>62.97709923664122</v>
-      </c>
-      <c r="AG90" t="n">
-        <v>62.97709923664122</v>
-      </c>
+      <c r="AE90" t="inlineStr"/>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -9245,9 +8877,7 @@
           <t>POPPY TAHLEIA</t>
         </is>
       </c>
-      <c r="E92" t="n">
-        <v>63.94316163410302</v>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
@@ -9281,15 +8911,9 @@
       <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="inlineStr"/>
       <c r="AD92" t="inlineStr"/>
-      <c r="AE92" t="n">
-        <v>63.94316163410302</v>
-      </c>
-      <c r="AF92" t="n">
-        <v>63.94316163410302</v>
-      </c>
-      <c r="AG92" t="n">
-        <v>63.94316163410302</v>
-      </c>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr">
         <is>
           <t>28/10/2025</t>
@@ -9433,9 +9057,7 @@
           <t>KING POTATO</t>
         </is>
       </c>
-      <c r="E94" t="n">
-        <v>63.43612334801763</v>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
@@ -9469,15 +9091,9 @@
       <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="inlineStr"/>
       <c r="AD94" t="inlineStr"/>
-      <c r="AE94" t="n">
-        <v>63.43612334801763</v>
-      </c>
-      <c r="AF94" t="n">
-        <v>63.43612334801763</v>
-      </c>
-      <c r="AG94" t="n">
-        <v>63.43612334801763</v>
-      </c>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -9621,9 +9237,7 @@
           <t>CROCODILE CRAWL</t>
         </is>
       </c>
-      <c r="E96" t="n">
-        <v>61.94573130377233</v>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
@@ -9657,15 +9271,9 @@
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr"/>
       <c r="AD96" t="inlineStr"/>
-      <c r="AE96" t="n">
-        <v>61.94573130377233</v>
-      </c>
-      <c r="AF96" t="n">
-        <v>61.94573130377233</v>
-      </c>
-      <c r="AG96" t="n">
-        <v>61.94573130377233</v>
-      </c>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr">
         <is>
           <t>8/11/2025</t>
@@ -9809,9 +9417,7 @@
           <t>JUST A PRINCESS</t>
         </is>
       </c>
-      <c r="E98" t="n">
-        <v>63.10344827586208</v>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
@@ -9845,15 +9451,9 @@
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr"/>
       <c r="AD98" t="inlineStr"/>
-      <c r="AE98" t="n">
-        <v>63.10344827586208</v>
-      </c>
-      <c r="AF98" t="n">
-        <v>63.10344827586208</v>
-      </c>
-      <c r="AG98" t="n">
-        <v>63.10344827586208</v>
-      </c>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -9997,9 +9597,7 @@
           <t>FOOT FALCON</t>
         </is>
       </c>
-      <c r="E100" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
@@ -10033,15 +9631,9 @@
       <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="inlineStr"/>
       <c r="AD100" t="inlineStr"/>
-      <c r="AE100" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AF100" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AG100" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -10185,9 +9777,7 @@
           <t>MY MOET</t>
         </is>
       </c>
-      <c r="E102" t="n">
-        <v>63.74455732946299</v>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
@@ -10221,15 +9811,9 @@
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr"/>
-      <c r="AE102" t="n">
-        <v>63.74455732946299</v>
-      </c>
-      <c r="AF102" t="n">
-        <v>63.74455732946299</v>
-      </c>
-      <c r="AG102" t="n">
-        <v>63.74455732946299</v>
-      </c>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr">
         <is>
           <t>31/10/2025</t>
@@ -10373,9 +9957,7 @@
           <t>ASTON FLORIN</t>
         </is>
       </c>
-      <c r="E104" t="n">
-        <v>64.02845709204091</v>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
@@ -10409,15 +9991,9 @@
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr"/>
       <c r="AD104" t="inlineStr"/>
-      <c r="AE104" t="n">
-        <v>64.02845709204091</v>
-      </c>
-      <c r="AF104" t="n">
-        <v>64.02845709204091</v>
-      </c>
-      <c r="AG104" t="n">
-        <v>64.02845709204091</v>
-      </c>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr">
         <is>
           <t>31/10/2025</t>
@@ -10561,9 +10137,7 @@
           <t>PRIDE AND POWER</t>
         </is>
       </c>
-      <c r="E106" t="n">
-        <v>63.82978723404256</v>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
@@ -10597,15 +10171,9 @@
       <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr"/>
       <c r="AD106" t="inlineStr"/>
-      <c r="AE106" t="n">
-        <v>63.82978723404256</v>
-      </c>
-      <c r="AF106" t="n">
-        <v>63.82978723404256</v>
-      </c>
-      <c r="AG106" t="n">
-        <v>63.82978723404256</v>
-      </c>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr">
         <is>
           <t>30/10/2025</t>
@@ -10749,9 +10317,7 @@
           <t>OUTSIDE THE FIRE</t>
         </is>
       </c>
-      <c r="E108" t="n">
-        <v>61.59327731092437</v>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
@@ -10785,15 +10351,9 @@
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr"/>
       <c r="AD108" t="inlineStr"/>
-      <c r="AE108" t="n">
-        <v>61.59327731092437</v>
-      </c>
-      <c r="AF108" t="n">
-        <v>61.59327731092437</v>
-      </c>
-      <c r="AG108" t="n">
-        <v>61.59327731092437</v>
-      </c>
+      <c r="AE108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr">
         <is>
           <t>6/10/2025</t>
@@ -10937,9 +10497,7 @@
           <t>PAID IN FULL</t>
         </is>
       </c>
-      <c r="E110" t="n">
-        <v>62.23230490018149</v>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
@@ -10973,15 +10531,9 @@
       <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="inlineStr"/>
       <c r="AD110" t="inlineStr"/>
-      <c r="AE110" t="n">
-        <v>62.23230490018149</v>
-      </c>
-      <c r="AF110" t="n">
-        <v>62.23230490018149</v>
-      </c>
-      <c r="AG110" t="n">
-        <v>62.23230490018149</v>
-      </c>
+      <c r="AE110" t="inlineStr"/>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -11125,9 +10677,7 @@
           <t>INVESTED</t>
         </is>
       </c>
-      <c r="E112" t="n">
-        <v>63.75442739079102</v>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
@@ -11161,15 +10711,9 @@
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr"/>
-      <c r="AE112" t="n">
-        <v>63.75442739079102</v>
-      </c>
-      <c r="AF112" t="n">
-        <v>63.75442739079102</v>
-      </c>
-      <c r="AG112" t="n">
-        <v>63.75442739079102</v>
-      </c>
+      <c r="AE112" t="inlineStr"/>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr">
         <is>
           <t>6/11/2025</t>
@@ -11313,9 +10857,7 @@
           <t>GOLDEN HANDCUFFS</t>
         </is>
       </c>
-      <c r="E114" t="n">
-        <v>62.60869565217391</v>
-      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
@@ -11349,15 +10891,9 @@
       <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr"/>
       <c r="AD114" t="inlineStr"/>
-      <c r="AE114" t="n">
-        <v>62.60869565217391</v>
-      </c>
-      <c r="AF114" t="n">
-        <v>62.60869565217391</v>
-      </c>
-      <c r="AG114" t="n">
-        <v>62.60869565217391</v>
-      </c>
+      <c r="AE114" t="inlineStr"/>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr">
         <is>
           <t>31/10/2025</t>
@@ -11581,9 +11117,7 @@
           <t>ELECTRA STARR</t>
         </is>
       </c>
-      <c r="E117" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
@@ -11617,15 +11151,9 @@
       <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="inlineStr"/>
       <c r="AD117" t="inlineStr"/>
-      <c r="AE117" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AF117" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AG117" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="AE117" t="inlineStr"/>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -11701,9 +11229,7 @@
           <t>RED HOT BONNIE</t>
         </is>
       </c>
-      <c r="E118" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
@@ -11737,15 +11263,9 @@
       <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr"/>
       <c r="AD118" t="inlineStr"/>
-      <c r="AE118" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AF118" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AG118" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="AE118" t="inlineStr"/>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -11889,9 +11409,7 @@
           <t>ZERO SURF</t>
         </is>
       </c>
-      <c r="E120" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
@@ -11925,15 +11443,9 @@
       <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="inlineStr"/>
       <c r="AD120" t="inlineStr"/>
-      <c r="AE120" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AF120" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AG120" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="AE120" t="inlineStr"/>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -12077,9 +11589,7 @@
           <t>ELITE ARNOTT</t>
         </is>
       </c>
-      <c r="E122" t="n">
-        <v>61.83949504057711</v>
-      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
@@ -12113,15 +11623,9 @@
       <c r="AB122" t="inlineStr"/>
       <c r="AC122" t="inlineStr"/>
       <c r="AD122" t="inlineStr"/>
-      <c r="AE122" t="n">
-        <v>61.83949504057711</v>
-      </c>
-      <c r="AF122" t="n">
-        <v>61.83949504057711</v>
-      </c>
-      <c r="AG122" t="n">
-        <v>61.83949504057711</v>
-      </c>
+      <c r="AE122" t="inlineStr"/>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr">
         <is>
           <t>22/10/2025</t>
@@ -12265,9 +11769,7 @@
           <t>WEST ON BURNIE</t>
         </is>
       </c>
-      <c r="E124" t="n">
-        <v>62.23404255319149</v>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
@@ -12301,15 +11803,9 @@
       <c r="AB124" t="inlineStr"/>
       <c r="AC124" t="inlineStr"/>
       <c r="AD124" t="inlineStr"/>
-      <c r="AE124" t="n">
-        <v>62.23404255319149</v>
-      </c>
-      <c r="AF124" t="n">
-        <v>62.23404255319149</v>
-      </c>
-      <c r="AG124" t="n">
-        <v>62.23404255319149</v>
-      </c>
+      <c r="AE124" t="inlineStr"/>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -12453,9 +11949,7 @@
           <t>HELLO BAILEY</t>
         </is>
       </c>
-      <c r="E126" t="n">
-        <v>62.97709923664122</v>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
@@ -12489,15 +11983,9 @@
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr"/>
       <c r="AD126" t="inlineStr"/>
-      <c r="AE126" t="n">
-        <v>62.97709923664122</v>
-      </c>
-      <c r="AF126" t="n">
-        <v>62.97709923664122</v>
-      </c>
-      <c r="AG126" t="n">
-        <v>62.97709923664122</v>
-      </c>
+      <c r="AE126" t="inlineStr"/>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -12641,9 +12129,7 @@
           <t>PURE LOVE</t>
         </is>
       </c>
-      <c r="E128" t="n">
-        <v>62.8021978021978</v>
-      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
@@ -12677,15 +12163,9 @@
       <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="inlineStr"/>
       <c r="AD128" t="inlineStr"/>
-      <c r="AE128" t="n">
-        <v>62.8021978021978</v>
-      </c>
-      <c r="AF128" t="n">
-        <v>62.8021978021978</v>
-      </c>
-      <c r="AG128" t="n">
-        <v>62.8021978021978</v>
-      </c>
+      <c r="AE128" t="inlineStr"/>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -12829,9 +12309,7 @@
           <t>FOUND THE BRAKE</t>
         </is>
       </c>
-      <c r="E130" t="n">
-        <v>61.56716417910449</v>
-      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
@@ -12865,15 +12343,9 @@
       <c r="AB130" t="inlineStr"/>
       <c r="AC130" t="inlineStr"/>
       <c r="AD130" t="inlineStr"/>
-      <c r="AE130" t="n">
-        <v>61.56716417910449</v>
-      </c>
-      <c r="AF130" t="n">
-        <v>61.56716417910449</v>
-      </c>
-      <c r="AG130" t="n">
-        <v>61.56716417910449</v>
-      </c>
+      <c r="AE130" t="inlineStr"/>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr">
         <is>
           <t>8/10/2025</t>
@@ -13017,9 +12489,7 @@
           <t>ARMED FOR ACTION</t>
         </is>
       </c>
-      <c r="E132" t="n">
-        <v>62.8021978021978</v>
-      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
@@ -13053,15 +12523,9 @@
       <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr"/>
       <c r="AD132" t="inlineStr"/>
-      <c r="AE132" t="n">
-        <v>62.8021978021978</v>
-      </c>
-      <c r="AF132" t="n">
-        <v>62.8021978021978</v>
-      </c>
-      <c r="AG132" t="n">
-        <v>62.8021978021978</v>
-      </c>
+      <c r="AE132" t="inlineStr"/>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -13205,9 +12669,7 @@
           <t>TINY TWIST</t>
         </is>
       </c>
-      <c r="E134" t="n">
-        <v>61.52889993784959</v>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
@@ -13241,15 +12703,9 @@
       <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr"/>
       <c r="AD134" t="inlineStr"/>
-      <c r="AE134" t="n">
-        <v>61.52889993784959</v>
-      </c>
-      <c r="AF134" t="n">
-        <v>61.52889993784959</v>
-      </c>
-      <c r="AG134" t="n">
-        <v>61.52889993784959</v>
-      </c>
+      <c r="AE134" t="inlineStr"/>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr">
         <is>
           <t>29/10/2025</t>
@@ -13393,9 +12849,7 @@
           <t>JUNGLE DELUXE</t>
         </is>
       </c>
-      <c r="E136" t="n">
-        <v>61.84340931615461</v>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
@@ -13429,15 +12883,9 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr"/>
       <c r="AD136" t="inlineStr"/>
-      <c r="AE136" t="n">
-        <v>61.84340931615461</v>
-      </c>
-      <c r="AF136" t="n">
-        <v>61.84340931615461</v>
-      </c>
-      <c r="AG136" t="n">
-        <v>61.84340931615461</v>
-      </c>
+      <c r="AE136" t="inlineStr"/>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr">
         <is>
           <t>10/09/2025</t>
@@ -13877,9 +13325,7 @@
           <t>FROTHING</t>
         </is>
       </c>
-      <c r="E142" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
@@ -13913,15 +13359,9 @@
       <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr"/>
-      <c r="AE142" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AF142" t="n">
-        <v>62.048392442824</v>
-      </c>
-      <c r="AG142" t="n">
-        <v>62.048392442824</v>
-      </c>
+      <c r="AE142" t="inlineStr"/>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -14065,9 +13505,7 @@
           <t>RIPPIN' PIKE</t>
         </is>
       </c>
-      <c r="E144" t="n">
-        <v>62.74473924977127</v>
-      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
@@ -14101,15 +13539,9 @@
       <c r="AB144" t="inlineStr"/>
       <c r="AC144" t="inlineStr"/>
       <c r="AD144" t="inlineStr"/>
-      <c r="AE144" t="n">
-        <v>62.74473924977127</v>
-      </c>
-      <c r="AF144" t="n">
-        <v>62.74473924977127</v>
-      </c>
-      <c r="AG144" t="n">
-        <v>62.74473924977127</v>
-      </c>
+      <c r="AE144" t="inlineStr"/>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -14253,9 +13685,7 @@
           <t>RAPIDO WARRIOR</t>
         </is>
       </c>
-      <c r="E146" t="n">
-        <v>62.23404255319149</v>
-      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
@@ -14289,15 +13719,9 @@
       <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr"/>
       <c r="AD146" t="inlineStr"/>
-      <c r="AE146" t="n">
-        <v>62.23404255319149</v>
-      </c>
-      <c r="AF146" t="n">
-        <v>62.23404255319149</v>
-      </c>
-      <c r="AG146" t="n">
-        <v>62.23404255319149</v>
-      </c>
+      <c r="AE146" t="inlineStr"/>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -14441,9 +13865,7 @@
           <t>REGGAE MELODY</t>
         </is>
       </c>
-      <c r="E148" t="n">
-        <v>63.06206896551724</v>
-      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
@@ -14477,15 +13899,9 @@
       <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr"/>
       <c r="AD148" t="inlineStr"/>
-      <c r="AE148" t="n">
-        <v>63.06206896551724</v>
-      </c>
-      <c r="AF148" t="n">
-        <v>63.06206896551724</v>
-      </c>
-      <c r="AG148" t="n">
-        <v>63.06206896551724</v>
-      </c>
+      <c r="AE148" t="inlineStr"/>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr">
         <is>
           <t>29/10/2025</t>
@@ -14629,9 +14045,7 @@
           <t>JANA BLADE</t>
         </is>
       </c>
-      <c r="E150" t="n">
-        <v>62.23230490018149</v>
-      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
@@ -14665,15 +14079,9 @@
       <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr"/>
       <c r="AD150" t="inlineStr"/>
-      <c r="AE150" t="n">
-        <v>62.23230490018149</v>
-      </c>
-      <c r="AF150" t="n">
-        <v>62.23230490018149</v>
-      </c>
-      <c r="AG150" t="n">
-        <v>62.23230490018149</v>
-      </c>
+      <c r="AE150" t="inlineStr"/>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -14817,9 +14225,7 @@
           <t>CHEDDAR MONELLI</t>
         </is>
       </c>
-      <c r="E152" t="n">
-        <v>60.88560885608856</v>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
@@ -14853,15 +14259,9 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="inlineStr"/>
-      <c r="AE152" t="n">
-        <v>60.88560885608856</v>
-      </c>
-      <c r="AF152" t="n">
-        <v>60.88560885608856</v>
-      </c>
-      <c r="AG152" t="n">
-        <v>60.88560885608856</v>
-      </c>
+      <c r="AE152" t="inlineStr"/>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr">
         <is>
           <t>29/10/2025</t>
@@ -15005,9 +14405,7 @@
           <t>RIPPIN' PEDRO</t>
         </is>
       </c>
-      <c r="E154" t="n">
-        <v>62.8021978021978</v>
-      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
@@ -15041,15 +14439,9 @@
       <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr"/>
       <c r="AD154" t="inlineStr"/>
-      <c r="AE154" t="n">
-        <v>62.8021978021978</v>
-      </c>
-      <c r="AF154" t="n">
-        <v>62.8021978021978</v>
-      </c>
-      <c r="AG154" t="n">
-        <v>62.8021978021978</v>
-      </c>
+      <c r="AE154" t="inlineStr"/>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -15193,9 +14585,7 @@
           <t>NOT MUCH KUNA</t>
         </is>
       </c>
-      <c r="E156" t="n">
-        <v>62.46056782334384</v>
-      </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
@@ -15229,15 +14619,9 @@
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="inlineStr"/>
-      <c r="AE156" t="n">
-        <v>62.46056782334384</v>
-      </c>
-      <c r="AF156" t="n">
-        <v>62.46056782334384</v>
-      </c>
-      <c r="AG156" t="n">
-        <v>62.46056782334384</v>
-      </c>
+      <c r="AE156" t="inlineStr"/>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="inlineStr"/>
       <c r="AH156" t="inlineStr">
         <is>
           <t>22/10/2025</t>
@@ -15381,9 +14765,7 @@
           <t>TEMPTING LULU</t>
         </is>
       </c>
-      <c r="E158" t="n">
-        <v>60.69895769466586</v>
-      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
@@ -15417,15 +14799,9 @@
       <c r="AB158" t="inlineStr"/>
       <c r="AC158" t="inlineStr"/>
       <c r="AD158" t="inlineStr"/>
-      <c r="AE158" t="n">
-        <v>60.69895769466586</v>
-      </c>
-      <c r="AF158" t="n">
-        <v>60.69895769466586</v>
-      </c>
-      <c r="AG158" t="n">
-        <v>60.69895769466586</v>
-      </c>
+      <c r="AE158" t="inlineStr"/>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="inlineStr"/>
       <c r="AH158" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -15569,9 +14945,7 @@
           <t>SMILE TIME</t>
         </is>
       </c>
-      <c r="E160" t="n">
-        <v>62.52713851498045</v>
-      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
@@ -15605,15 +14979,9 @@
       <c r="AB160" t="inlineStr"/>
       <c r="AC160" t="inlineStr"/>
       <c r="AD160" t="inlineStr"/>
-      <c r="AE160" t="n">
-        <v>62.52713851498045</v>
-      </c>
-      <c r="AF160" t="n">
-        <v>62.52713851498045</v>
-      </c>
-      <c r="AG160" t="n">
-        <v>62.52713851498045</v>
-      </c>
+      <c r="AE160" t="inlineStr"/>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="inlineStr"/>
       <c r="AH160" t="inlineStr">
         <is>
           <t>28/10/2025</t>
@@ -15757,9 +15125,7 @@
           <t>RIPPIN' RUBY</t>
         </is>
       </c>
-      <c r="E162" t="n">
-        <v>62.28882833787466</v>
-      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
@@ -15793,15 +15159,9 @@
       <c r="AB162" t="inlineStr"/>
       <c r="AC162" t="inlineStr"/>
       <c r="AD162" t="inlineStr"/>
-      <c r="AE162" t="n">
-        <v>62.28882833787466</v>
-      </c>
-      <c r="AF162" t="n">
-        <v>62.28882833787466</v>
-      </c>
-      <c r="AG162" t="n">
-        <v>62.28882833787466</v>
-      </c>
+      <c r="AE162" t="inlineStr"/>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr">
         <is>
           <t>17/09/2025</t>
@@ -16093,9 +15453,7 @@
           <t>HOLLY CAN BROWSE</t>
         </is>
       </c>
-      <c r="E166" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
@@ -16129,15 +15487,9 @@
       <c r="AB166" t="inlineStr"/>
       <c r="AC166" t="inlineStr"/>
       <c r="AD166" t="inlineStr"/>
-      <c r="AE166" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AF166" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AG166" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="AE166" t="inlineStr"/>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="inlineStr"/>
       <c r="AH166" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -16281,9 +15633,7 @@
           <t>MILKY BAR KID</t>
         </is>
       </c>
-      <c r="E168" t="n">
-        <v>62.74473924977127</v>
-      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
@@ -16317,15 +15667,9 @@
       <c r="AB168" t="inlineStr"/>
       <c r="AC168" t="inlineStr"/>
       <c r="AD168" t="inlineStr"/>
-      <c r="AE168" t="n">
-        <v>62.74473924977127</v>
-      </c>
-      <c r="AF168" t="n">
-        <v>62.74473924977127</v>
-      </c>
-      <c r="AG168" t="n">
-        <v>62.74473924977127</v>
-      </c>
+      <c r="AE168" t="inlineStr"/>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -16469,9 +15813,7 @@
           <t>MERL'S LAD</t>
         </is>
       </c>
-      <c r="E170" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
@@ -16505,15 +15847,9 @@
       <c r="AB170" t="inlineStr"/>
       <c r="AC170" t="inlineStr"/>
       <c r="AD170" t="inlineStr"/>
-      <c r="AE170" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AF170" t="n">
-        <v>62.17203586848224</v>
-      </c>
-      <c r="AG170" t="n">
-        <v>62.17203586848224</v>
-      </c>
+      <c r="AE170" t="inlineStr"/>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="inlineStr"/>
       <c r="AH170" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -16657,9 +15993,7 @@
           <t>SUNSET AMANDA</t>
         </is>
       </c>
-      <c r="E172" t="n">
-        <v>61.8392134181608</v>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
@@ -16693,15 +16027,9 @@
       <c r="AB172" t="inlineStr"/>
       <c r="AC172" t="inlineStr"/>
       <c r="AD172" t="inlineStr"/>
-      <c r="AE172" t="n">
-        <v>61.8392134181608</v>
-      </c>
-      <c r="AF172" t="n">
-        <v>61.8392134181608</v>
-      </c>
-      <c r="AG172" t="n">
-        <v>61.8392134181608</v>
-      </c>
+      <c r="AE172" t="inlineStr"/>
+      <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="inlineStr"/>
       <c r="AH172" t="inlineStr">
         <is>
           <t>6/10/2025</t>
@@ -16845,9 +16173,7 @@
           <t>FEARLESS COBRA</t>
         </is>
       </c>
-      <c r="E174" t="n">
-        <v>62.8021978021978</v>
-      </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
@@ -16881,15 +16207,9 @@
       <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="inlineStr"/>
       <c r="AD174" t="inlineStr"/>
-      <c r="AE174" t="n">
-        <v>62.8021978021978</v>
-      </c>
-      <c r="AF174" t="n">
-        <v>62.8021978021978</v>
-      </c>
-      <c r="AG174" t="n">
-        <v>62.8021978021978</v>
-      </c>
+      <c r="AE174" t="inlineStr"/>
+      <c r="AF174" t="inlineStr"/>
+      <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -17033,9 +16353,7 @@
           <t>VIVID LOVE</t>
         </is>
       </c>
-      <c r="E176" t="n">
-        <v>63.82978723404256</v>
-      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
@@ -17069,15 +16387,9 @@
       <c r="AB176" t="inlineStr"/>
       <c r="AC176" t="inlineStr"/>
       <c r="AD176" t="inlineStr"/>
-      <c r="AE176" t="n">
-        <v>63.82978723404256</v>
-      </c>
-      <c r="AF176" t="n">
-        <v>63.82978723404256</v>
-      </c>
-      <c r="AG176" t="n">
-        <v>63.82978723404256</v>
-      </c>
+      <c r="AE176" t="inlineStr"/>
+      <c r="AF176" t="inlineStr"/>
+      <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr">
         <is>
           <t>30/10/2025</t>
@@ -17221,9 +16533,7 @@
           <t>RAPIDO PRONTO</t>
         </is>
       </c>
-      <c r="E178" t="n">
-        <v>62.68738574040219</v>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
@@ -17257,15 +16567,9 @@
       <c r="AB178" t="inlineStr"/>
       <c r="AC178" t="inlineStr"/>
       <c r="AD178" t="inlineStr"/>
-      <c r="AE178" t="n">
-        <v>62.68738574040219</v>
-      </c>
-      <c r="AF178" t="n">
-        <v>62.68738574040219</v>
-      </c>
-      <c r="AG178" t="n">
-        <v>62.68738574040219</v>
-      </c>
+      <c r="AE178" t="inlineStr"/>
+      <c r="AF178" t="inlineStr"/>
+      <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -17409,9 +16713,7 @@
           <t>DOREEN KEEPING</t>
         </is>
       </c>
-      <c r="E180" t="n">
-        <v>62.97709923664122</v>
-      </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
@@ -17445,15 +16747,9 @@
       <c r="AB180" t="inlineStr"/>
       <c r="AC180" t="inlineStr"/>
       <c r="AD180" t="inlineStr"/>
-      <c r="AE180" t="n">
-        <v>62.97709923664122</v>
-      </c>
-      <c r="AF180" t="n">
-        <v>62.97709923664122</v>
-      </c>
-      <c r="AG180" t="n">
-        <v>62.97709923664122</v>
-      </c>
+      <c r="AE180" t="inlineStr"/>
+      <c r="AF180" t="inlineStr"/>
+      <c r="AG180" t="inlineStr"/>
       <c r="AH180" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -17597,9 +16893,7 @@
           <t>WIZARD'S NERO</t>
         </is>
       </c>
-      <c r="E182" t="n">
-        <v>62.10465784933871</v>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
@@ -17633,15 +16927,9 @@
       <c r="AB182" t="inlineStr"/>
       <c r="AC182" t="inlineStr"/>
       <c r="AD182" t="inlineStr"/>
-      <c r="AE182" t="n">
-        <v>62.10465784933871</v>
-      </c>
-      <c r="AF182" t="n">
-        <v>62.10465784933871</v>
-      </c>
-      <c r="AG182" t="n">
-        <v>62.10465784933871</v>
-      </c>
+      <c r="AE182" t="inlineStr"/>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr">
         <is>
           <t>3/11/2025</t>
@@ -17717,9 +17005,7 @@
           <t>NO ROLE MODELS</t>
         </is>
       </c>
-      <c r="E183" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
@@ -17753,15 +17039,9 @@
       <c r="AB183" t="inlineStr"/>
       <c r="AC183" t="inlineStr"/>
       <c r="AD183" t="inlineStr"/>
-      <c r="AE183" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AF183" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AG183" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="AE183" t="inlineStr"/>
+      <c r="AF183" t="inlineStr"/>
+      <c r="AG183" t="inlineStr"/>
       <c r="AH183" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -17905,9 +17185,7 @@
           <t>NAUGHTY EVIE</t>
         </is>
       </c>
-      <c r="E185" t="n">
-        <v>61.94573130377233</v>
-      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
@@ -17941,15 +17219,9 @@
       <c r="AB185" t="inlineStr"/>
       <c r="AC185" t="inlineStr"/>
       <c r="AD185" t="inlineStr"/>
-      <c r="AE185" t="n">
-        <v>61.94573130377233</v>
-      </c>
-      <c r="AF185" t="n">
-        <v>61.94573130377233</v>
-      </c>
-      <c r="AG185" t="n">
-        <v>61.94573130377233</v>
-      </c>
+      <c r="AE185" t="inlineStr"/>
+      <c r="AF185" t="inlineStr"/>
+      <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr">
         <is>
           <t>8/11/2025</t>
@@ -18093,9 +17365,7 @@
           <t>OFF SHORE</t>
         </is>
       </c>
-      <c r="E187" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
@@ -18129,15 +17399,9 @@
       <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="inlineStr"/>
       <c r="AD187" t="inlineStr"/>
-      <c r="AE187" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AF187" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AG187" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="AE187" t="inlineStr"/>
+      <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="inlineStr"/>
       <c r="AH187" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -18281,9 +17545,7 @@
           <t>ROCKIN' KINLOCH</t>
         </is>
       </c>
-      <c r="E189" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
@@ -18317,15 +17579,9 @@
       <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="inlineStr"/>
       <c r="AD189" t="inlineStr"/>
-      <c r="AE189" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AF189" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AG189" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="AE189" t="inlineStr"/>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="inlineStr"/>
       <c r="AH189" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -18469,9 +17725,7 @@
           <t>CITY OF LOVE</t>
         </is>
       </c>
-      <c r="E191" t="n">
-        <v>61.78378378378378</v>
-      </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
@@ -18505,15 +17759,9 @@
       <c r="AB191" t="inlineStr"/>
       <c r="AC191" t="inlineStr"/>
       <c r="AD191" t="inlineStr"/>
-      <c r="AE191" t="n">
-        <v>61.78378378378378</v>
-      </c>
-      <c r="AF191" t="n">
-        <v>61.78378378378378</v>
-      </c>
-      <c r="AG191" t="n">
-        <v>61.78378378378378</v>
-      </c>
+      <c r="AE191" t="inlineStr"/>
+      <c r="AF191" t="inlineStr"/>
+      <c r="AG191" t="inlineStr"/>
       <c r="AH191" t="inlineStr">
         <is>
           <t>8/11/2025</t>
@@ -18657,9 +17905,7 @@
           <t>MUST BE SPEEDY</t>
         </is>
       </c>
-      <c r="E193" t="n">
-        <v>63.74455732946299</v>
-      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
@@ -18693,15 +17939,9 @@
       <c r="AB193" t="inlineStr"/>
       <c r="AC193" t="inlineStr"/>
       <c r="AD193" t="inlineStr"/>
-      <c r="AE193" t="n">
-        <v>63.74455732946299</v>
-      </c>
-      <c r="AF193" t="n">
-        <v>63.74455732946299</v>
-      </c>
-      <c r="AG193" t="n">
-        <v>63.74455732946299</v>
-      </c>
+      <c r="AE193" t="inlineStr"/>
+      <c r="AF193" t="inlineStr"/>
+      <c r="AG193" t="inlineStr"/>
       <c r="AH193" t="inlineStr">
         <is>
           <t>7/11/2025</t>
@@ -18845,9 +18085,7 @@
           <t>FIDEL PRONTO</t>
         </is>
       </c>
-      <c r="E195" t="n">
-        <v>62.68738574040219</v>
-      </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
@@ -18881,15 +18119,9 @@
       <c r="AB195" t="inlineStr"/>
       <c r="AC195" t="inlineStr"/>
       <c r="AD195" t="inlineStr"/>
-      <c r="AE195" t="n">
-        <v>62.68738574040219</v>
-      </c>
-      <c r="AF195" t="n">
-        <v>62.68738574040219</v>
-      </c>
-      <c r="AG195" t="n">
-        <v>62.68738574040219</v>
-      </c>
+      <c r="AE195" t="inlineStr"/>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="inlineStr"/>
       <c r="AH195" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -19033,9 +18265,7 @@
           <t>SHINBONER PIXIE</t>
         </is>
       </c>
-      <c r="E197" t="n">
-        <v>62.23230490018149</v>
-      </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
@@ -19069,15 +18299,9 @@
       <c r="AB197" t="inlineStr"/>
       <c r="AC197" t="inlineStr"/>
       <c r="AD197" t="inlineStr"/>
-      <c r="AE197" t="n">
-        <v>62.23230490018149</v>
-      </c>
-      <c r="AF197" t="n">
-        <v>62.23230490018149</v>
-      </c>
-      <c r="AG197" t="n">
-        <v>62.23230490018149</v>
-      </c>
+      <c r="AE197" t="inlineStr"/>
+      <c r="AF197" t="inlineStr"/>
+      <c r="AG197" t="inlineStr"/>
       <c r="AH197" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -19221,9 +18445,7 @@
           <t>POP'S ANGEL</t>
         </is>
       </c>
-      <c r="E199" t="n">
-        <v>61.08597285067874</v>
-      </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
@@ -19257,15 +18479,9 @@
       <c r="AB199" t="inlineStr"/>
       <c r="AC199" t="inlineStr"/>
       <c r="AD199" t="inlineStr"/>
-      <c r="AE199" t="n">
-        <v>61.08597285067874</v>
-      </c>
-      <c r="AF199" t="n">
-        <v>61.08597285067874</v>
-      </c>
-      <c r="AG199" t="n">
-        <v>61.08597285067874</v>
-      </c>
+      <c r="AE199" t="inlineStr"/>
+      <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="inlineStr"/>
       <c r="AH199" t="inlineStr">
         <is>
           <t>3/11/2025</t>
@@ -19409,9 +18625,7 @@
           <t>LIGHTNING BOLT</t>
         </is>
       </c>
-      <c r="E201" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
@@ -19445,15 +18659,9 @@
       <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="inlineStr"/>
       <c r="AD201" t="inlineStr"/>
-      <c r="AE201" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AF201" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AG201" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="AE201" t="inlineStr"/>
+      <c r="AF201" t="inlineStr"/>
+      <c r="AG201" t="inlineStr"/>
       <c r="AH201" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -19529,9 +18737,7 @@
           <t>OFF SHORE</t>
         </is>
       </c>
-      <c r="E202" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
@@ -19565,15 +18771,9 @@
       <c r="AB202" t="inlineStr"/>
       <c r="AC202" t="inlineStr"/>
       <c r="AD202" t="inlineStr"/>
-      <c r="AE202" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AF202" t="n">
-        <v>62.1195652173913</v>
-      </c>
-      <c r="AG202" t="n">
-        <v>62.1195652173913</v>
-      </c>
+      <c r="AE202" t="inlineStr"/>
+      <c r="AF202" t="inlineStr"/>
+      <c r="AG202" t="inlineStr"/>
       <c r="AH202" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -19717,9 +18917,7 @@
           <t>NAUGHTY EVIE</t>
         </is>
       </c>
-      <c r="E204" t="n">
-        <v>61.94573130377233</v>
-      </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
@@ -19753,15 +18951,9 @@
       <c r="AB204" t="inlineStr"/>
       <c r="AC204" t="inlineStr"/>
       <c r="AD204" t="inlineStr"/>
-      <c r="AE204" t="n">
-        <v>61.94573130377233</v>
-      </c>
-      <c r="AF204" t="n">
-        <v>61.94573130377233</v>
-      </c>
-      <c r="AG204" t="n">
-        <v>61.94573130377233</v>
-      </c>
+      <c r="AE204" t="inlineStr"/>
+      <c r="AF204" t="inlineStr"/>
+      <c r="AG204" t="inlineStr"/>
       <c r="AH204" t="inlineStr">
         <is>
           <t>8/11/2025</t>
@@ -19905,9 +19097,7 @@
           <t>MAKUTZ</t>
         </is>
       </c>
-      <c r="E206" t="n">
-        <v>62.74473924977127</v>
-      </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
@@ -19941,15 +19131,9 @@
       <c r="AB206" t="inlineStr"/>
       <c r="AC206" t="inlineStr"/>
       <c r="AD206" t="inlineStr"/>
-      <c r="AE206" t="n">
-        <v>62.74473924977127</v>
-      </c>
-      <c r="AF206" t="n">
-        <v>62.74473924977127</v>
-      </c>
-      <c r="AG206" t="n">
-        <v>62.74473924977127</v>
-      </c>
+      <c r="AE206" t="inlineStr"/>
+      <c r="AF206" t="inlineStr"/>
+      <c r="AG206" t="inlineStr"/>
       <c r="AH206" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -20093,9 +19277,7 @@
           <t>CHAMBERLAIN</t>
         </is>
       </c>
-      <c r="E208" t="n">
-        <v>64.02845709204091</v>
-      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
@@ -20129,15 +19311,9 @@
       <c r="AB208" t="inlineStr"/>
       <c r="AC208" t="inlineStr"/>
       <c r="AD208" t="inlineStr"/>
-      <c r="AE208" t="n">
-        <v>64.02845709204091</v>
-      </c>
-      <c r="AF208" t="n">
-        <v>64.02845709204091</v>
-      </c>
-      <c r="AG208" t="n">
-        <v>64.02845709204091</v>
-      </c>
+      <c r="AE208" t="inlineStr"/>
+      <c r="AF208" t="inlineStr"/>
+      <c r="AG208" t="inlineStr"/>
       <c r="AH208" t="inlineStr">
         <is>
           <t>10/10/2025</t>
@@ -20281,9 +19457,7 @@
           <t>BISCOTTI BLAST</t>
         </is>
       </c>
-      <c r="E210" t="n">
-        <v>62.96670030272453</v>
-      </c>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
@@ -20317,15 +19491,9 @@
       <c r="AB210" t="inlineStr"/>
       <c r="AC210" t="inlineStr"/>
       <c r="AD210" t="inlineStr"/>
-      <c r="AE210" t="n">
-        <v>62.96670030272453</v>
-      </c>
-      <c r="AF210" t="n">
-        <v>62.96670030272453</v>
-      </c>
-      <c r="AG210" t="n">
-        <v>62.96670030272453</v>
-      </c>
+      <c r="AE210" t="inlineStr"/>
+      <c r="AF210" t="inlineStr"/>
+      <c r="AG210" t="inlineStr"/>
       <c r="AH210" t="inlineStr">
         <is>
           <t>1/11/2025</t>
@@ -20469,9 +19637,7 @@
           <t>CONCORD GUNDI</t>
         </is>
       </c>
-      <c r="E212" t="n">
-        <v>62.68738574040219</v>
-      </c>
+      <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
@@ -20505,15 +19671,9 @@
       <c r="AB212" t="inlineStr"/>
       <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr"/>
-      <c r="AE212" t="n">
-        <v>62.68738574040219</v>
-      </c>
-      <c r="AF212" t="n">
-        <v>62.68738574040219</v>
-      </c>
-      <c r="AG212" t="n">
-        <v>62.68738574040219</v>
-      </c>
+      <c r="AE212" t="inlineStr"/>
+      <c r="AF212" t="inlineStr"/>
+      <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -20657,9 +19817,7 @@
           <t>WEST ON HALO</t>
         </is>
       </c>
-      <c r="E214" t="n">
-        <v>62.23230490018149</v>
-      </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
@@ -20693,15 +19851,9 @@
       <c r="AB214" t="inlineStr"/>
       <c r="AC214" t="inlineStr"/>
       <c r="AD214" t="inlineStr"/>
-      <c r="AE214" t="n">
-        <v>62.23230490018149</v>
-      </c>
-      <c r="AF214" t="n">
-        <v>62.23230490018149</v>
-      </c>
-      <c r="AG214" t="n">
-        <v>62.23230490018149</v>
-      </c>
+      <c r="AE214" t="inlineStr"/>
+      <c r="AF214" t="inlineStr"/>
+      <c r="AG214" t="inlineStr"/>
       <c r="AH214" t="inlineStr">
         <is>
           <t>5/11/2025</t>

--- a/outputs/all_dogs_master.xlsx
+++ b/outputs/all_dogs_master.xlsx
@@ -808,9 +808,15 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>62.46385193753615</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>62.46385193753615</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>62.46385193753615</v>
+      </c>
       <c r="AG3" t="inlineStr">
         <is>
           <t>6/11/2025</t>
@@ -839,7 +845,9 @@
         </is>
       </c>
       <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>62.46385193753615</v>
+      </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr">
@@ -978,9 +986,15 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AG5" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -1009,7 +1023,9 @@
         </is>
       </c>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr">
@@ -1148,9 +1164,15 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>61.29398410896709</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>61.29398410896709</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>61.29398410896709</v>
+      </c>
       <c r="AG7" t="inlineStr">
         <is>
           <t>16/10/2025</t>
@@ -1179,7 +1201,9 @@
         </is>
       </c>
       <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>61.29398410896709</v>
+      </c>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr">
@@ -1393,9 +1417,15 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>63.10344827586208</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>63.10344827586208</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>63.10344827586208</v>
+      </c>
       <c r="AG10" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -1424,7 +1454,9 @@
         </is>
       </c>
       <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>63.10344827586208</v>
+      </c>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr">
@@ -1563,9 +1595,15 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>63.85809312638581</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>63.85809312638581</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>63.85809312638581</v>
+      </c>
       <c r="AG12" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -1594,7 +1632,9 @@
         </is>
       </c>
       <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>63.85809312638581</v>
+      </c>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr">
@@ -1733,9 +1773,15 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>62.46385193753615</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>62.46385193753615</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>62.46385193753615</v>
+      </c>
       <c r="AG14" t="inlineStr">
         <is>
           <t>6/11/2025</t>
@@ -1764,7 +1810,9 @@
         </is>
       </c>
       <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
+      <c r="AO14" t="n">
+        <v>62.46385193753615</v>
+      </c>
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr">
@@ -1903,9 +1951,15 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
+      <c r="AD16" t="n">
+        <v>63.44125809435707</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>63.44125809435707</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>63.44125809435707</v>
+      </c>
       <c r="AG16" t="inlineStr">
         <is>
           <t>22/10/2025</t>
@@ -1934,7 +1988,9 @@
         </is>
       </c>
       <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
+      <c r="AO16" t="n">
+        <v>63.44125809435707</v>
+      </c>
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr">
@@ -2073,9 +2129,15 @@
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
+      <c r="AD18" t="n">
+        <v>62.68738574040219</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>62.68738574040219</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>62.68738574040219</v>
+      </c>
       <c r="AG18" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -2104,7 +2166,9 @@
         </is>
       </c>
       <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
+      <c r="AO18" t="n">
+        <v>62.68738574040219</v>
+      </c>
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="inlineStr">
@@ -2243,9 +2307,15 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
+      <c r="AD20" t="n">
+        <v>62.46385193753615</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>62.46385193753615</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>62.46385193753615</v>
+      </c>
       <c r="AG20" t="inlineStr">
         <is>
           <t>6/11/2025</t>
@@ -2274,7 +2344,9 @@
         </is>
       </c>
       <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
+      <c r="AO20" t="n">
+        <v>62.46385193753615</v>
+      </c>
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr">
@@ -2413,9 +2485,15 @@
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
+      <c r="AD22" t="n">
+        <v>62.23230490018149</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>62.23230490018149</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>62.23230490018149</v>
+      </c>
       <c r="AG22" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -2444,7 +2522,9 @@
         </is>
       </c>
       <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
+      <c r="AO22" t="n">
+        <v>62.23230490018149</v>
+      </c>
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="inlineStr">
@@ -2583,9 +2663,15 @@
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
+      <c r="AD24" t="n">
+        <v>62.97709923664122</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>62.97709923664122</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>62.97709923664122</v>
+      </c>
       <c r="AG24" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -2614,7 +2700,9 @@
         </is>
       </c>
       <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
+      <c r="AO24" t="n">
+        <v>62.97709923664122</v>
+      </c>
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="inlineStr">
@@ -2753,9 +2841,15 @@
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
+      <c r="AD26" t="n">
+        <v>60.69895769466586</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>60.69895769466586</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>60.69895769466586</v>
+      </c>
       <c r="AG26" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -2784,7 +2878,9 @@
         </is>
       </c>
       <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
+      <c r="AO26" t="n">
+        <v>60.69895769466586</v>
+      </c>
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr"/>
       <c r="AR26" t="inlineStr">
@@ -2923,9 +3019,15 @@
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
+      <c r="AD28" t="n">
+        <v>61.47915732855223</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>61.47915732855223</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>61.47915732855223</v>
+      </c>
       <c r="AG28" t="inlineStr">
         <is>
           <t>22/10/2025</t>
@@ -2954,7 +3056,9 @@
         </is>
       </c>
       <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
+      <c r="AO28" t="n">
+        <v>61.47915732855223</v>
+      </c>
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr"/>
       <c r="AR28" t="inlineStr">
@@ -3030,9 +3134,15 @@
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
+      <c r="AD29" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AG29" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -3061,7 +3171,9 @@
         </is>
       </c>
       <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
+      <c r="AO29" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr">
@@ -3200,9 +3312,15 @@
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
+      <c r="AD31" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AG31" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -3231,7 +3349,9 @@
         </is>
       </c>
       <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
+      <c r="AO31" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr">
@@ -3370,9 +3490,15 @@
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
+      <c r="AD33" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AG33" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -3401,7 +3527,9 @@
         </is>
       </c>
       <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
+      <c r="AO33" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AP33" t="inlineStr"/>
       <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="inlineStr">
@@ -3540,9 +3668,15 @@
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
+      <c r="AD35" t="n">
+        <v>62.74473924977127</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>62.74473924977127</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>62.74473924977127</v>
+      </c>
       <c r="AG35" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -3571,7 +3705,9 @@
         </is>
       </c>
       <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
+      <c r="AO35" t="n">
+        <v>62.74473924977127</v>
+      </c>
       <c r="AP35" t="inlineStr"/>
       <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="inlineStr">
@@ -3710,9 +3846,15 @@
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
+      <c r="AD37" t="n">
+        <v>61.22285332442365</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>61.22285332442365</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>61.22285332442365</v>
+      </c>
       <c r="AG37" t="inlineStr">
         <is>
           <t>27/10/2025</t>
@@ -3741,7 +3883,9 @@
         </is>
       </c>
       <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
+      <c r="AO37" t="n">
+        <v>61.22285332442365</v>
+      </c>
       <c r="AP37" t="inlineStr"/>
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="inlineStr">
@@ -3880,9 +4024,15 @@
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
+      <c r="AD39" t="n">
+        <v>61.9054054054054</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>61.9054054054054</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>61.9054054054054</v>
+      </c>
       <c r="AG39" t="inlineStr">
         <is>
           <t>13/10/2025</t>
@@ -3911,7 +4061,9 @@
         </is>
       </c>
       <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
+      <c r="AO39" t="n">
+        <v>61.9054054054054</v>
+      </c>
       <c r="AP39" t="inlineStr"/>
       <c r="AQ39" t="inlineStr"/>
       <c r="AR39" t="inlineStr">
@@ -4050,9 +4202,15 @@
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
+      <c r="AD41" t="n">
+        <v>62.23404255319149</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>62.23404255319149</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>62.23404255319149</v>
+      </c>
       <c r="AG41" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -4081,7 +4239,9 @@
         </is>
       </c>
       <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="inlineStr"/>
+      <c r="AO41" t="n">
+        <v>62.23404255319149</v>
+      </c>
       <c r="AP41" t="inlineStr"/>
       <c r="AQ41" t="inlineStr"/>
       <c r="AR41" t="inlineStr">
@@ -4220,9 +4380,15 @@
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
+      <c r="AD43" t="n">
+        <v>62.97709923664122</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>62.97709923664122</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>62.97709923664122</v>
+      </c>
       <c r="AG43" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -4251,7 +4417,9 @@
         </is>
       </c>
       <c r="AN43" t="inlineStr"/>
-      <c r="AO43" t="inlineStr"/>
+      <c r="AO43" t="n">
+        <v>62.97709923664122</v>
+      </c>
       <c r="AP43" t="inlineStr"/>
       <c r="AQ43" t="inlineStr"/>
       <c r="AR43" t="inlineStr">
@@ -4390,9 +4558,15 @@
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr"/>
+      <c r="AD45" t="n">
+        <v>62.23230490018149</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>62.23230490018149</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>62.23230490018149</v>
+      </c>
       <c r="AG45" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -4421,7 +4595,9 @@
         </is>
       </c>
       <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr"/>
+      <c r="AO45" t="n">
+        <v>62.23230490018149</v>
+      </c>
       <c r="AP45" t="inlineStr"/>
       <c r="AQ45" t="inlineStr"/>
       <c r="AR45" t="inlineStr">
@@ -4560,9 +4736,15 @@
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
+      <c r="AD47" t="n">
+        <v>63.41637010676158</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>63.41637010676158</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>63.41637010676158</v>
+      </c>
       <c r="AG47" t="inlineStr">
         <is>
           <t>13/10/2025</t>
@@ -4591,7 +4773,9 @@
         </is>
       </c>
       <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="inlineStr"/>
+      <c r="AO47" t="n">
+        <v>63.41637010676158</v>
+      </c>
       <c r="AP47" t="inlineStr"/>
       <c r="AQ47" t="inlineStr"/>
       <c r="AR47" t="inlineStr">
@@ -4730,9 +4914,15 @@
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr"/>
-      <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr"/>
+      <c r="AD49" t="n">
+        <v>59.63190184049079</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>59.63190184049079</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>59.63190184049079</v>
+      </c>
       <c r="AG49" t="inlineStr">
         <is>
           <t>13/10/2025</t>
@@ -4761,7 +4951,9 @@
         </is>
       </c>
       <c r="AN49" t="inlineStr"/>
-      <c r="AO49" t="inlineStr"/>
+      <c r="AO49" t="n">
+        <v>59.63190184049079</v>
+      </c>
       <c r="AP49" t="inlineStr"/>
       <c r="AQ49" t="inlineStr"/>
       <c r="AR49" t="inlineStr">
@@ -4900,9 +5092,15 @@
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
+      <c r="AD51" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AG51" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -4931,7 +5129,9 @@
         </is>
       </c>
       <c r="AN51" t="inlineStr"/>
-      <c r="AO51" t="inlineStr"/>
+      <c r="AO51" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AP51" t="inlineStr"/>
       <c r="AQ51" t="inlineStr"/>
       <c r="AR51" t="inlineStr">
@@ -5070,9 +5270,15 @@
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
+      <c r="AD53" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AG53" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -5101,7 +5307,9 @@
         </is>
       </c>
       <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr"/>
+      <c r="AO53" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AP53" t="inlineStr"/>
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="inlineStr">
@@ -5240,9 +5448,15 @@
       <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
+      <c r="AD55" t="n">
+        <v>61.63977609483042</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>61.63977609483042</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>61.63977609483042</v>
+      </c>
       <c r="AG55" t="inlineStr">
         <is>
           <t>29/10/2025</t>
@@ -5271,7 +5485,9 @@
         </is>
       </c>
       <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr"/>
+      <c r="AO55" t="n">
+        <v>61.63977609483042</v>
+      </c>
       <c r="AP55" t="inlineStr"/>
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="inlineStr">
@@ -5410,9 +5626,15 @@
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr"/>
+      <c r="AD57" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AG57" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -5441,7 +5663,9 @@
         </is>
       </c>
       <c r="AN57" t="inlineStr"/>
-      <c r="AO57" t="inlineStr"/>
+      <c r="AO57" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AP57" t="inlineStr"/>
       <c r="AQ57" t="inlineStr"/>
       <c r="AR57" t="inlineStr">
@@ -5580,9 +5804,15 @@
       <c r="AA59" t="inlineStr"/>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr"/>
-      <c r="AE59" t="inlineStr"/>
-      <c r="AF59" t="inlineStr"/>
+      <c r="AD59" t="n">
+        <v>61.75596578117965</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>61.75596578117965</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>61.75596578117965</v>
+      </c>
       <c r="AG59" t="inlineStr">
         <is>
           <t>8/10/2025</t>
@@ -5611,7 +5841,9 @@
         </is>
       </c>
       <c r="AN59" t="inlineStr"/>
-      <c r="AO59" t="inlineStr"/>
+      <c r="AO59" t="n">
+        <v>61.75596578117965</v>
+      </c>
       <c r="AP59" t="inlineStr"/>
       <c r="AQ59" t="inlineStr"/>
       <c r="AR59" t="inlineStr">
@@ -5750,9 +5982,15 @@
       <c r="AA61" t="inlineStr"/>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr"/>
+      <c r="AD61" t="n">
+        <v>62.23404255319149</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>62.23404255319149</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>62.23404255319149</v>
+      </c>
       <c r="AG61" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -5781,7 +6019,9 @@
         </is>
       </c>
       <c r="AN61" t="inlineStr"/>
-      <c r="AO61" t="inlineStr"/>
+      <c r="AO61" t="n">
+        <v>62.23404255319149</v>
+      </c>
       <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr">
@@ -5920,9 +6160,15 @@
       <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr"/>
-      <c r="AD63" t="inlineStr"/>
-      <c r="AE63" t="inlineStr"/>
-      <c r="AF63" t="inlineStr"/>
+      <c r="AD63" t="n">
+        <v>64.34316353887401</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>64.34316353887401</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>64.34316353887401</v>
+      </c>
       <c r="AG63" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -5951,7 +6197,9 @@
         </is>
       </c>
       <c r="AN63" t="inlineStr"/>
-      <c r="AO63" t="inlineStr"/>
+      <c r="AO63" t="n">
+        <v>64.34316353887401</v>
+      </c>
       <c r="AP63" t="inlineStr"/>
       <c r="AQ63" t="inlineStr"/>
       <c r="AR63" t="inlineStr">
@@ -6090,9 +6338,15 @@
       <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr"/>
-      <c r="AD65" t="inlineStr"/>
-      <c r="AE65" t="inlineStr"/>
-      <c r="AF65" t="inlineStr"/>
+      <c r="AD65" t="n">
+        <v>62.68738574040219</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>62.68738574040219</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>62.68738574040219</v>
+      </c>
       <c r="AG65" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -6121,7 +6375,9 @@
         </is>
       </c>
       <c r="AN65" t="inlineStr"/>
-      <c r="AO65" t="inlineStr"/>
+      <c r="AO65" t="n">
+        <v>62.68738574040219</v>
+      </c>
       <c r="AP65" t="inlineStr"/>
       <c r="AQ65" t="inlineStr"/>
       <c r="AR65" t="inlineStr">
@@ -6260,9 +6516,15 @@
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr"/>
-      <c r="AD67" t="inlineStr"/>
-      <c r="AE67" t="inlineStr"/>
-      <c r="AF67" t="inlineStr"/>
+      <c r="AD67" t="n">
+        <v>60.92307692307693</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>60.92307692307693</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>60.92307692307693</v>
+      </c>
       <c r="AG67" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -6291,7 +6553,9 @@
         </is>
       </c>
       <c r="AN67" t="inlineStr"/>
-      <c r="AO67" t="inlineStr"/>
+      <c r="AO67" t="n">
+        <v>60.92307692307693</v>
+      </c>
       <c r="AP67" t="inlineStr"/>
       <c r="AQ67" t="inlineStr"/>
       <c r="AR67" t="inlineStr">
@@ -6430,9 +6694,15 @@
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr"/>
-      <c r="AD69" t="inlineStr"/>
-      <c r="AE69" t="inlineStr"/>
-      <c r="AF69" t="inlineStr"/>
+      <c r="AD69" t="n">
+        <v>62.90956749672346</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>62.90956749672346</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>62.90956749672346</v>
+      </c>
       <c r="AG69" t="inlineStr">
         <is>
           <t>3/11/2025</t>
@@ -6461,7 +6731,9 @@
         </is>
       </c>
       <c r="AN69" t="inlineStr"/>
-      <c r="AO69" t="inlineStr"/>
+      <c r="AO69" t="n">
+        <v>62.90956749672346</v>
+      </c>
       <c r="AP69" t="inlineStr"/>
       <c r="AQ69" t="inlineStr"/>
       <c r="AR69" t="inlineStr">
@@ -6600,9 +6872,15 @@
       <c r="AA71" t="inlineStr"/>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr"/>
-      <c r="AD71" t="inlineStr"/>
-      <c r="AE71" t="inlineStr"/>
-      <c r="AF71" t="inlineStr"/>
+      <c r="AD71" t="n">
+        <v>60.92307692307693</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>60.92307692307693</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>60.92307692307693</v>
+      </c>
       <c r="AG71" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -6631,7 +6909,9 @@
         </is>
       </c>
       <c r="AN71" t="inlineStr"/>
-      <c r="AO71" t="inlineStr"/>
+      <c r="AO71" t="n">
+        <v>60.92307692307693</v>
+      </c>
       <c r="AP71" t="inlineStr"/>
       <c r="AQ71" t="inlineStr"/>
       <c r="AR71" t="inlineStr">
@@ -6707,9 +6987,15 @@
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr"/>
-      <c r="AD72" t="inlineStr"/>
-      <c r="AE72" t="inlineStr"/>
-      <c r="AF72" t="inlineStr"/>
+      <c r="AD72" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AG72" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -6738,7 +7024,9 @@
         </is>
       </c>
       <c r="AN72" t="inlineStr"/>
-      <c r="AO72" t="inlineStr"/>
+      <c r="AO72" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AP72" t="inlineStr"/>
       <c r="AQ72" t="inlineStr"/>
       <c r="AR72" t="inlineStr">
@@ -6814,9 +7102,15 @@
       <c r="AA73" t="inlineStr"/>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr"/>
-      <c r="AD73" t="inlineStr"/>
-      <c r="AE73" t="inlineStr"/>
-      <c r="AF73" t="inlineStr"/>
+      <c r="AD73" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AG73" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -6845,7 +7139,9 @@
         </is>
       </c>
       <c r="AN73" t="inlineStr"/>
-      <c r="AO73" t="inlineStr"/>
+      <c r="AO73" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AP73" t="inlineStr"/>
       <c r="AQ73" t="inlineStr"/>
       <c r="AR73" t="inlineStr">
@@ -6921,9 +7217,15 @@
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr"/>
-      <c r="AD74" t="inlineStr"/>
-      <c r="AE74" t="inlineStr"/>
-      <c r="AF74" t="inlineStr"/>
+      <c r="AD74" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AG74" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -6952,7 +7254,9 @@
         </is>
       </c>
       <c r="AN74" t="inlineStr"/>
-      <c r="AO74" t="inlineStr"/>
+      <c r="AO74" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AP74" t="inlineStr"/>
       <c r="AQ74" t="inlineStr"/>
       <c r="AR74" t="inlineStr">
@@ -7091,9 +7395,15 @@
       <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr"/>
-      <c r="AD76" t="inlineStr"/>
-      <c r="AE76" t="inlineStr"/>
-      <c r="AF76" t="inlineStr"/>
+      <c r="AD76" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AG76" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -7122,7 +7432,9 @@
         </is>
       </c>
       <c r="AN76" t="inlineStr"/>
-      <c r="AO76" t="inlineStr"/>
+      <c r="AO76" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AP76" t="inlineStr"/>
       <c r="AQ76" t="inlineStr"/>
       <c r="AR76" t="inlineStr">
@@ -7261,9 +7573,15 @@
       <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr"/>
-      <c r="AD78" t="inlineStr"/>
-      <c r="AE78" t="inlineStr"/>
-      <c r="AF78" t="inlineStr"/>
+      <c r="AD78" t="n">
+        <v>62.74473924977127</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>62.74473924977127</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>62.74473924977127</v>
+      </c>
       <c r="AG78" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -7292,7 +7610,9 @@
         </is>
       </c>
       <c r="AN78" t="inlineStr"/>
-      <c r="AO78" t="inlineStr"/>
+      <c r="AO78" t="n">
+        <v>62.74473924977127</v>
+      </c>
       <c r="AP78" t="inlineStr"/>
       <c r="AQ78" t="inlineStr"/>
       <c r="AR78" t="inlineStr">
@@ -7431,9 +7751,15 @@
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr"/>
-      <c r="AD80" t="inlineStr"/>
-      <c r="AE80" t="inlineStr"/>
-      <c r="AF80" t="inlineStr"/>
+      <c r="AD80" t="n">
+        <v>62.882096069869</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>62.882096069869</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>62.882096069869</v>
+      </c>
       <c r="AG80" t="inlineStr">
         <is>
           <t>1/11/2025</t>
@@ -7462,7 +7788,9 @@
         </is>
       </c>
       <c r="AN80" t="inlineStr"/>
-      <c r="AO80" t="inlineStr"/>
+      <c r="AO80" t="n">
+        <v>62.882096069869</v>
+      </c>
       <c r="AP80" t="inlineStr"/>
       <c r="AQ80" t="inlineStr"/>
       <c r="AR80" t="inlineStr">
@@ -7601,9 +7929,15 @@
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr"/>
-      <c r="AD82" t="inlineStr"/>
-      <c r="AE82" t="inlineStr"/>
-      <c r="AF82" t="inlineStr"/>
+      <c r="AD82" t="n">
+        <v>62.9004076878276</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>62.9004076878276</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>62.9004076878276</v>
+      </c>
       <c r="AG82" t="inlineStr">
         <is>
           <t>30/10/2025</t>
@@ -7632,7 +7966,9 @@
         </is>
       </c>
       <c r="AN82" t="inlineStr"/>
-      <c r="AO82" t="inlineStr"/>
+      <c r="AO82" t="n">
+        <v>62.9004076878276</v>
+      </c>
       <c r="AP82" t="inlineStr"/>
       <c r="AQ82" t="inlineStr"/>
       <c r="AR82" t="inlineStr">
@@ -7771,9 +8107,15 @@
       <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr"/>
-      <c r="AD84" t="inlineStr"/>
-      <c r="AE84" t="inlineStr"/>
-      <c r="AF84" t="inlineStr"/>
+      <c r="AD84" t="n">
+        <v>60.69895769466586</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>60.69895769466586</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>60.69895769466586</v>
+      </c>
       <c r="AG84" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -7802,7 +8144,9 @@
         </is>
       </c>
       <c r="AN84" t="inlineStr"/>
-      <c r="AO84" t="inlineStr"/>
+      <c r="AO84" t="n">
+        <v>60.69895769466586</v>
+      </c>
       <c r="AP84" t="inlineStr"/>
       <c r="AQ84" t="inlineStr"/>
       <c r="AR84" t="inlineStr">
@@ -7941,9 +8285,15 @@
       <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr"/>
-      <c r="AD86" t="inlineStr"/>
-      <c r="AE86" t="inlineStr"/>
-      <c r="AF86" t="inlineStr"/>
+      <c r="AD86" t="n">
+        <v>60.69895769466586</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>60.69895769466586</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>60.69895769466586</v>
+      </c>
       <c r="AG86" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -7972,7 +8322,9 @@
         </is>
       </c>
       <c r="AN86" t="inlineStr"/>
-      <c r="AO86" t="inlineStr"/>
+      <c r="AO86" t="n">
+        <v>60.69895769466586</v>
+      </c>
       <c r="AP86" t="inlineStr"/>
       <c r="AQ86" t="inlineStr"/>
       <c r="AR86" t="inlineStr">
@@ -8111,9 +8463,15 @@
       <c r="AA88" t="inlineStr"/>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="inlineStr"/>
-      <c r="AD88" t="inlineStr"/>
-      <c r="AE88" t="inlineStr"/>
-      <c r="AF88" t="inlineStr"/>
+      <c r="AD88" t="n">
+        <v>61.51898734177216</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>61.51898734177216</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>61.51898734177216</v>
+      </c>
       <c r="AG88" t="inlineStr">
         <is>
           <t>15/09/2025</t>
@@ -8142,7 +8500,9 @@
         </is>
       </c>
       <c r="AN88" t="inlineStr"/>
-      <c r="AO88" t="inlineStr"/>
+      <c r="AO88" t="n">
+        <v>61.51898734177216</v>
+      </c>
       <c r="AP88" t="inlineStr"/>
       <c r="AQ88" t="inlineStr"/>
       <c r="AR88" t="inlineStr">
@@ -8281,9 +8641,15 @@
       <c r="AA90" t="inlineStr"/>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr"/>
-      <c r="AD90" t="inlineStr"/>
-      <c r="AE90" t="inlineStr"/>
-      <c r="AF90" t="inlineStr"/>
+      <c r="AD90" t="n">
+        <v>62.97709923664122</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>62.97709923664122</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>62.97709923664122</v>
+      </c>
       <c r="AG90" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -8312,7 +8678,9 @@
         </is>
       </c>
       <c r="AN90" t="inlineStr"/>
-      <c r="AO90" t="inlineStr"/>
+      <c r="AO90" t="n">
+        <v>62.97709923664122</v>
+      </c>
       <c r="AP90" t="inlineStr"/>
       <c r="AQ90" t="inlineStr"/>
       <c r="AR90" t="inlineStr">
@@ -8451,9 +8819,15 @@
       <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="inlineStr"/>
-      <c r="AD92" t="inlineStr"/>
-      <c r="AE92" t="inlineStr"/>
-      <c r="AF92" t="inlineStr"/>
+      <c r="AD92" t="n">
+        <v>63.94316163410302</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>63.94316163410302</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>63.94316163410302</v>
+      </c>
       <c r="AG92" t="inlineStr">
         <is>
           <t>28/10/2025</t>
@@ -8482,7 +8856,9 @@
         </is>
       </c>
       <c r="AN92" t="inlineStr"/>
-      <c r="AO92" t="inlineStr"/>
+      <c r="AO92" t="n">
+        <v>63.94316163410302</v>
+      </c>
       <c r="AP92" t="inlineStr"/>
       <c r="AQ92" t="inlineStr"/>
       <c r="AR92" t="inlineStr">
@@ -8621,9 +8997,15 @@
       <c r="AA94" t="inlineStr"/>
       <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="inlineStr"/>
-      <c r="AD94" t="inlineStr"/>
-      <c r="AE94" t="inlineStr"/>
-      <c r="AF94" t="inlineStr"/>
+      <c r="AD94" t="n">
+        <v>63.43612334801763</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>63.43612334801763</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>63.43612334801763</v>
+      </c>
       <c r="AG94" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -8652,7 +9034,9 @@
         </is>
       </c>
       <c r="AN94" t="inlineStr"/>
-      <c r="AO94" t="inlineStr"/>
+      <c r="AO94" t="n">
+        <v>63.43612334801763</v>
+      </c>
       <c r="AP94" t="inlineStr"/>
       <c r="AQ94" t="inlineStr"/>
       <c r="AR94" t="inlineStr">
@@ -8791,9 +9175,15 @@
       <c r="AA96" t="inlineStr"/>
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr"/>
-      <c r="AD96" t="inlineStr"/>
-      <c r="AE96" t="inlineStr"/>
-      <c r="AF96" t="inlineStr"/>
+      <c r="AD96" t="n">
+        <v>61.94573130377233</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>61.94573130377233</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>61.94573130377233</v>
+      </c>
       <c r="AG96" t="inlineStr">
         <is>
           <t>8/11/2025</t>
@@ -8822,7 +9212,9 @@
         </is>
       </c>
       <c r="AN96" t="inlineStr"/>
-      <c r="AO96" t="inlineStr"/>
+      <c r="AO96" t="n">
+        <v>61.94573130377233</v>
+      </c>
       <c r="AP96" t="inlineStr"/>
       <c r="AQ96" t="inlineStr"/>
       <c r="AR96" t="inlineStr">
@@ -8961,9 +9353,15 @@
       <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr"/>
-      <c r="AD98" t="inlineStr"/>
-      <c r="AE98" t="inlineStr"/>
-      <c r="AF98" t="inlineStr"/>
+      <c r="AD98" t="n">
+        <v>63.10344827586208</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>63.10344827586208</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>63.10344827586208</v>
+      </c>
       <c r="AG98" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -8992,7 +9390,9 @@
         </is>
       </c>
       <c r="AN98" t="inlineStr"/>
-      <c r="AO98" t="inlineStr"/>
+      <c r="AO98" t="n">
+        <v>63.10344827586208</v>
+      </c>
       <c r="AP98" t="inlineStr"/>
       <c r="AQ98" t="inlineStr"/>
       <c r="AR98" t="inlineStr">
@@ -9131,9 +9531,15 @@
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="inlineStr"/>
-      <c r="AD100" t="inlineStr"/>
-      <c r="AE100" t="inlineStr"/>
-      <c r="AF100" t="inlineStr"/>
+      <c r="AD100" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AG100" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -9162,7 +9568,9 @@
         </is>
       </c>
       <c r="AN100" t="inlineStr"/>
-      <c r="AO100" t="inlineStr"/>
+      <c r="AO100" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AP100" t="inlineStr"/>
       <c r="AQ100" t="inlineStr"/>
       <c r="AR100" t="inlineStr">
@@ -9301,9 +9709,15 @@
       <c r="AA102" t="inlineStr"/>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
-      <c r="AD102" t="inlineStr"/>
-      <c r="AE102" t="inlineStr"/>
-      <c r="AF102" t="inlineStr"/>
+      <c r="AD102" t="n">
+        <v>63.74455732946299</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>63.74455732946299</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>63.74455732946299</v>
+      </c>
       <c r="AG102" t="inlineStr">
         <is>
           <t>31/10/2025</t>
@@ -9332,7 +9746,9 @@
         </is>
       </c>
       <c r="AN102" t="inlineStr"/>
-      <c r="AO102" t="inlineStr"/>
+      <c r="AO102" t="n">
+        <v>63.74455732946299</v>
+      </c>
       <c r="AP102" t="inlineStr"/>
       <c r="AQ102" t="inlineStr"/>
       <c r="AR102" t="inlineStr">
@@ -9471,9 +9887,15 @@
       <c r="AA104" t="inlineStr"/>
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr"/>
-      <c r="AD104" t="inlineStr"/>
-      <c r="AE104" t="inlineStr"/>
-      <c r="AF104" t="inlineStr"/>
+      <c r="AD104" t="n">
+        <v>64.02845709204091</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>64.02845709204091</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>64.02845709204091</v>
+      </c>
       <c r="AG104" t="inlineStr">
         <is>
           <t>31/10/2025</t>
@@ -9502,7 +9924,9 @@
         </is>
       </c>
       <c r="AN104" t="inlineStr"/>
-      <c r="AO104" t="inlineStr"/>
+      <c r="AO104" t="n">
+        <v>64.02845709204091</v>
+      </c>
       <c r="AP104" t="inlineStr"/>
       <c r="AQ104" t="inlineStr"/>
       <c r="AR104" t="inlineStr">
@@ -9641,9 +10065,15 @@
       <c r="AA106" t="inlineStr"/>
       <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr"/>
-      <c r="AD106" t="inlineStr"/>
-      <c r="AE106" t="inlineStr"/>
-      <c r="AF106" t="inlineStr"/>
+      <c r="AD106" t="n">
+        <v>63.82978723404256</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>63.82978723404256</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>63.82978723404256</v>
+      </c>
       <c r="AG106" t="inlineStr">
         <is>
           <t>30/10/2025</t>
@@ -9672,7 +10102,9 @@
         </is>
       </c>
       <c r="AN106" t="inlineStr"/>
-      <c r="AO106" t="inlineStr"/>
+      <c r="AO106" t="n">
+        <v>63.82978723404256</v>
+      </c>
       <c r="AP106" t="inlineStr"/>
       <c r="AQ106" t="inlineStr"/>
       <c r="AR106" t="inlineStr">
@@ -9811,9 +10243,15 @@
       <c r="AA108" t="inlineStr"/>
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr"/>
-      <c r="AD108" t="inlineStr"/>
-      <c r="AE108" t="inlineStr"/>
-      <c r="AF108" t="inlineStr"/>
+      <c r="AD108" t="n">
+        <v>61.59327731092437</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>61.59327731092437</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>61.59327731092437</v>
+      </c>
       <c r="AG108" t="inlineStr">
         <is>
           <t>6/10/2025</t>
@@ -9842,7 +10280,9 @@
         </is>
       </c>
       <c r="AN108" t="inlineStr"/>
-      <c r="AO108" t="inlineStr"/>
+      <c r="AO108" t="n">
+        <v>61.59327731092437</v>
+      </c>
       <c r="AP108" t="inlineStr"/>
       <c r="AQ108" t="inlineStr"/>
       <c r="AR108" t="inlineStr">
@@ -9981,9 +10421,15 @@
       <c r="AA110" t="inlineStr"/>
       <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="inlineStr"/>
-      <c r="AD110" t="inlineStr"/>
-      <c r="AE110" t="inlineStr"/>
-      <c r="AF110" t="inlineStr"/>
+      <c r="AD110" t="n">
+        <v>62.23230490018149</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>62.23230490018149</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>62.23230490018149</v>
+      </c>
       <c r="AG110" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -10012,7 +10458,9 @@
         </is>
       </c>
       <c r="AN110" t="inlineStr"/>
-      <c r="AO110" t="inlineStr"/>
+      <c r="AO110" t="n">
+        <v>62.23230490018149</v>
+      </c>
       <c r="AP110" t="inlineStr"/>
       <c r="AQ110" t="inlineStr"/>
       <c r="AR110" t="inlineStr">
@@ -10151,9 +10599,15 @@
       <c r="AA112" t="inlineStr"/>
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr"/>
-      <c r="AD112" t="inlineStr"/>
-      <c r="AE112" t="inlineStr"/>
-      <c r="AF112" t="inlineStr"/>
+      <c r="AD112" t="n">
+        <v>63.75442739079102</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>63.75442739079102</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>63.75442739079102</v>
+      </c>
       <c r="AG112" t="inlineStr">
         <is>
           <t>6/11/2025</t>
@@ -10182,7 +10636,9 @@
         </is>
       </c>
       <c r="AN112" t="inlineStr"/>
-      <c r="AO112" t="inlineStr"/>
+      <c r="AO112" t="n">
+        <v>63.75442739079102</v>
+      </c>
       <c r="AP112" t="inlineStr"/>
       <c r="AQ112" t="inlineStr"/>
       <c r="AR112" t="inlineStr">
@@ -10321,9 +10777,15 @@
       <c r="AA114" t="inlineStr"/>
       <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr"/>
-      <c r="AD114" t="inlineStr"/>
-      <c r="AE114" t="inlineStr"/>
-      <c r="AF114" t="inlineStr"/>
+      <c r="AD114" t="n">
+        <v>62.60869565217391</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>62.60869565217391</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>62.60869565217391</v>
+      </c>
       <c r="AG114" t="inlineStr">
         <is>
           <t>31/10/2025</t>
@@ -10352,7 +10814,9 @@
         </is>
       </c>
       <c r="AN114" t="inlineStr"/>
-      <c r="AO114" t="inlineStr"/>
+      <c r="AO114" t="n">
+        <v>62.60869565217391</v>
+      </c>
       <c r="AP114" t="inlineStr"/>
       <c r="AQ114" t="inlineStr"/>
       <c r="AR114" t="inlineStr">
@@ -10566,9 +11030,15 @@
       <c r="AA117" t="inlineStr"/>
       <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="inlineStr"/>
-      <c r="AD117" t="inlineStr"/>
-      <c r="AE117" t="inlineStr"/>
-      <c r="AF117" t="inlineStr"/>
+      <c r="AD117" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AG117" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -10597,7 +11067,9 @@
         </is>
       </c>
       <c r="AN117" t="inlineStr"/>
-      <c r="AO117" t="inlineStr"/>
+      <c r="AO117" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AP117" t="inlineStr"/>
       <c r="AQ117" t="inlineStr"/>
       <c r="AR117" t="inlineStr">
@@ -10673,9 +11145,15 @@
       <c r="AA118" t="inlineStr"/>
       <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr"/>
-      <c r="AD118" t="inlineStr"/>
-      <c r="AE118" t="inlineStr"/>
-      <c r="AF118" t="inlineStr"/>
+      <c r="AD118" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AG118" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -10704,7 +11182,9 @@
         </is>
       </c>
       <c r="AN118" t="inlineStr"/>
-      <c r="AO118" t="inlineStr"/>
+      <c r="AO118" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AP118" t="inlineStr"/>
       <c r="AQ118" t="inlineStr"/>
       <c r="AR118" t="inlineStr">
@@ -10843,9 +11323,15 @@
       <c r="AA120" t="inlineStr"/>
       <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="inlineStr"/>
-      <c r="AD120" t="inlineStr"/>
-      <c r="AE120" t="inlineStr"/>
-      <c r="AF120" t="inlineStr"/>
+      <c r="AD120" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AG120" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -10874,7 +11360,9 @@
         </is>
       </c>
       <c r="AN120" t="inlineStr"/>
-      <c r="AO120" t="inlineStr"/>
+      <c r="AO120" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AP120" t="inlineStr"/>
       <c r="AQ120" t="inlineStr"/>
       <c r="AR120" t="inlineStr">
@@ -11013,9 +11501,15 @@
       <c r="AA122" t="inlineStr"/>
       <c r="AB122" t="inlineStr"/>
       <c r="AC122" t="inlineStr"/>
-      <c r="AD122" t="inlineStr"/>
-      <c r="AE122" t="inlineStr"/>
-      <c r="AF122" t="inlineStr"/>
+      <c r="AD122" t="n">
+        <v>61.83949504057711</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>61.83949504057711</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>61.83949504057711</v>
+      </c>
       <c r="AG122" t="inlineStr">
         <is>
           <t>22/10/2025</t>
@@ -11044,7 +11538,9 @@
         </is>
       </c>
       <c r="AN122" t="inlineStr"/>
-      <c r="AO122" t="inlineStr"/>
+      <c r="AO122" t="n">
+        <v>61.83949504057711</v>
+      </c>
       <c r="AP122" t="inlineStr"/>
       <c r="AQ122" t="inlineStr"/>
       <c r="AR122" t="inlineStr">
@@ -11183,9 +11679,15 @@
       <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="inlineStr"/>
       <c r="AC124" t="inlineStr"/>
-      <c r="AD124" t="inlineStr"/>
-      <c r="AE124" t="inlineStr"/>
-      <c r="AF124" t="inlineStr"/>
+      <c r="AD124" t="n">
+        <v>62.23404255319149</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>62.23404255319149</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>62.23404255319149</v>
+      </c>
       <c r="AG124" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -11214,7 +11716,9 @@
         </is>
       </c>
       <c r="AN124" t="inlineStr"/>
-      <c r="AO124" t="inlineStr"/>
+      <c r="AO124" t="n">
+        <v>62.23404255319149</v>
+      </c>
       <c r="AP124" t="inlineStr"/>
       <c r="AQ124" t="inlineStr"/>
       <c r="AR124" t="inlineStr">
@@ -11353,9 +11857,15 @@
       <c r="AA126" t="inlineStr"/>
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr"/>
-      <c r="AD126" t="inlineStr"/>
-      <c r="AE126" t="inlineStr"/>
-      <c r="AF126" t="inlineStr"/>
+      <c r="AD126" t="n">
+        <v>62.97709923664122</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>62.97709923664122</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>62.97709923664122</v>
+      </c>
       <c r="AG126" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -11384,7 +11894,9 @@
         </is>
       </c>
       <c r="AN126" t="inlineStr"/>
-      <c r="AO126" t="inlineStr"/>
+      <c r="AO126" t="n">
+        <v>62.97709923664122</v>
+      </c>
       <c r="AP126" t="inlineStr"/>
       <c r="AQ126" t="inlineStr"/>
       <c r="AR126" t="inlineStr">
@@ -11523,9 +12035,15 @@
       <c r="AA128" t="inlineStr"/>
       <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="inlineStr"/>
-      <c r="AD128" t="inlineStr"/>
-      <c r="AE128" t="inlineStr"/>
-      <c r="AF128" t="inlineStr"/>
+      <c r="AD128" t="n">
+        <v>62.8021978021978</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>62.8021978021978</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>62.8021978021978</v>
+      </c>
       <c r="AG128" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -11554,7 +12072,9 @@
         </is>
       </c>
       <c r="AN128" t="inlineStr"/>
-      <c r="AO128" t="inlineStr"/>
+      <c r="AO128" t="n">
+        <v>62.8021978021978</v>
+      </c>
       <c r="AP128" t="inlineStr"/>
       <c r="AQ128" t="inlineStr"/>
       <c r="AR128" t="inlineStr">
@@ -11693,9 +12213,15 @@
       <c r="AA130" t="inlineStr"/>
       <c r="AB130" t="inlineStr"/>
       <c r="AC130" t="inlineStr"/>
-      <c r="AD130" t="inlineStr"/>
-      <c r="AE130" t="inlineStr"/>
-      <c r="AF130" t="inlineStr"/>
+      <c r="AD130" t="n">
+        <v>61.56716417910449</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>61.56716417910449</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>61.56716417910449</v>
+      </c>
       <c r="AG130" t="inlineStr">
         <is>
           <t>8/10/2025</t>
@@ -11724,7 +12250,9 @@
         </is>
       </c>
       <c r="AN130" t="inlineStr"/>
-      <c r="AO130" t="inlineStr"/>
+      <c r="AO130" t="n">
+        <v>61.56716417910449</v>
+      </c>
       <c r="AP130" t="inlineStr"/>
       <c r="AQ130" t="inlineStr"/>
       <c r="AR130" t="inlineStr">
@@ -11863,9 +12391,15 @@
       <c r="AA132" t="inlineStr"/>
       <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr"/>
-      <c r="AD132" t="inlineStr"/>
-      <c r="AE132" t="inlineStr"/>
-      <c r="AF132" t="inlineStr"/>
+      <c r="AD132" t="n">
+        <v>62.8021978021978</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>62.8021978021978</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>62.8021978021978</v>
+      </c>
       <c r="AG132" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -11894,7 +12428,9 @@
         </is>
       </c>
       <c r="AN132" t="inlineStr"/>
-      <c r="AO132" t="inlineStr"/>
+      <c r="AO132" t="n">
+        <v>62.8021978021978</v>
+      </c>
       <c r="AP132" t="inlineStr"/>
       <c r="AQ132" t="inlineStr"/>
       <c r="AR132" t="inlineStr">
@@ -12033,9 +12569,15 @@
       <c r="AA134" t="inlineStr"/>
       <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr"/>
-      <c r="AD134" t="inlineStr"/>
-      <c r="AE134" t="inlineStr"/>
-      <c r="AF134" t="inlineStr"/>
+      <c r="AD134" t="n">
+        <v>61.52889993784959</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>61.52889993784959</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>61.52889993784959</v>
+      </c>
       <c r="AG134" t="inlineStr">
         <is>
           <t>29/10/2025</t>
@@ -12064,7 +12606,9 @@
         </is>
       </c>
       <c r="AN134" t="inlineStr"/>
-      <c r="AO134" t="inlineStr"/>
+      <c r="AO134" t="n">
+        <v>61.52889993784959</v>
+      </c>
       <c r="AP134" t="inlineStr"/>
       <c r="AQ134" t="inlineStr"/>
       <c r="AR134" t="inlineStr">
@@ -12203,9 +12747,15 @@
       <c r="AA136" t="inlineStr"/>
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr"/>
-      <c r="AD136" t="inlineStr"/>
-      <c r="AE136" t="inlineStr"/>
-      <c r="AF136" t="inlineStr"/>
+      <c r="AD136" t="n">
+        <v>61.84340931615461</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>61.84340931615461</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>61.84340931615461</v>
+      </c>
       <c r="AG136" t="inlineStr">
         <is>
           <t>10/09/2025</t>
@@ -12234,7 +12784,9 @@
         </is>
       </c>
       <c r="AN136" t="inlineStr"/>
-      <c r="AO136" t="inlineStr"/>
+      <c r="AO136" t="n">
+        <v>61.84340931615461</v>
+      </c>
       <c r="AP136" t="inlineStr"/>
       <c r="AQ136" t="inlineStr"/>
       <c r="AR136" t="inlineStr">
@@ -12649,9 +13201,15 @@
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr"/>
-      <c r="AD142" t="inlineStr"/>
-      <c r="AE142" t="inlineStr"/>
-      <c r="AF142" t="inlineStr"/>
+      <c r="AD142" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>62.048392442824</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AG142" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -12680,7 +13238,9 @@
         </is>
       </c>
       <c r="AN142" t="inlineStr"/>
-      <c r="AO142" t="inlineStr"/>
+      <c r="AO142" t="n">
+        <v>62.048392442824</v>
+      </c>
       <c r="AP142" t="inlineStr"/>
       <c r="AQ142" t="inlineStr"/>
       <c r="AR142" t="inlineStr">
@@ -12819,9 +13379,15 @@
       <c r="AA144" t="inlineStr"/>
       <c r="AB144" t="inlineStr"/>
       <c r="AC144" t="inlineStr"/>
-      <c r="AD144" t="inlineStr"/>
-      <c r="AE144" t="inlineStr"/>
-      <c r="AF144" t="inlineStr"/>
+      <c r="AD144" t="n">
+        <v>62.74473924977127</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>62.74473924977127</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>62.74473924977127</v>
+      </c>
       <c r="AG144" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -12850,7 +13416,9 @@
         </is>
       </c>
       <c r="AN144" t="inlineStr"/>
-      <c r="AO144" t="inlineStr"/>
+      <c r="AO144" t="n">
+        <v>62.74473924977127</v>
+      </c>
       <c r="AP144" t="inlineStr"/>
       <c r="AQ144" t="inlineStr"/>
       <c r="AR144" t="inlineStr">
@@ -12989,9 +13557,15 @@
       <c r="AA146" t="inlineStr"/>
       <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr"/>
-      <c r="AD146" t="inlineStr"/>
-      <c r="AE146" t="inlineStr"/>
-      <c r="AF146" t="inlineStr"/>
+      <c r="AD146" t="n">
+        <v>62.23404255319149</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>62.23404255319149</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>62.23404255319149</v>
+      </c>
       <c r="AG146" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -13020,7 +13594,9 @@
         </is>
       </c>
       <c r="AN146" t="inlineStr"/>
-      <c r="AO146" t="inlineStr"/>
+      <c r="AO146" t="n">
+        <v>62.23404255319149</v>
+      </c>
       <c r="AP146" t="inlineStr"/>
       <c r="AQ146" t="inlineStr"/>
       <c r="AR146" t="inlineStr">
@@ -13159,9 +13735,15 @@
       <c r="AA148" t="inlineStr"/>
       <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr"/>
-      <c r="AD148" t="inlineStr"/>
-      <c r="AE148" t="inlineStr"/>
-      <c r="AF148" t="inlineStr"/>
+      <c r="AD148" t="n">
+        <v>63.06206896551724</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>63.06206896551724</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>63.06206896551724</v>
+      </c>
       <c r="AG148" t="inlineStr">
         <is>
           <t>29/10/2025</t>
@@ -13190,7 +13772,9 @@
         </is>
       </c>
       <c r="AN148" t="inlineStr"/>
-      <c r="AO148" t="inlineStr"/>
+      <c r="AO148" t="n">
+        <v>63.06206896551724</v>
+      </c>
       <c r="AP148" t="inlineStr"/>
       <c r="AQ148" t="inlineStr"/>
       <c r="AR148" t="inlineStr">
@@ -13329,9 +13913,15 @@
       <c r="AA150" t="inlineStr"/>
       <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr"/>
-      <c r="AD150" t="inlineStr"/>
-      <c r="AE150" t="inlineStr"/>
-      <c r="AF150" t="inlineStr"/>
+      <c r="AD150" t="n">
+        <v>62.23230490018149</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>62.23230490018149</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>62.23230490018149</v>
+      </c>
       <c r="AG150" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -13360,7 +13950,9 @@
         </is>
       </c>
       <c r="AN150" t="inlineStr"/>
-      <c r="AO150" t="inlineStr"/>
+      <c r="AO150" t="n">
+        <v>62.23230490018149</v>
+      </c>
       <c r="AP150" t="inlineStr"/>
       <c r="AQ150" t="inlineStr"/>
       <c r="AR150" t="inlineStr">
@@ -13499,9 +14091,15 @@
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr"/>
-      <c r="AD152" t="inlineStr"/>
-      <c r="AE152" t="inlineStr"/>
-      <c r="AF152" t="inlineStr"/>
+      <c r="AD152" t="n">
+        <v>60.88560885608856</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>60.88560885608856</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>60.88560885608856</v>
+      </c>
       <c r="AG152" t="inlineStr">
         <is>
           <t>29/10/2025</t>
@@ -13530,7 +14128,9 @@
         </is>
       </c>
       <c r="AN152" t="inlineStr"/>
-      <c r="AO152" t="inlineStr"/>
+      <c r="AO152" t="n">
+        <v>60.88560885608856</v>
+      </c>
       <c r="AP152" t="inlineStr"/>
       <c r="AQ152" t="inlineStr"/>
       <c r="AR152" t="inlineStr">
@@ -13669,9 +14269,15 @@
       <c r="AA154" t="inlineStr"/>
       <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr"/>
-      <c r="AD154" t="inlineStr"/>
-      <c r="AE154" t="inlineStr"/>
-      <c r="AF154" t="inlineStr"/>
+      <c r="AD154" t="n">
+        <v>62.8021978021978</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>62.8021978021978</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>62.8021978021978</v>
+      </c>
       <c r="AG154" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -13700,7 +14306,9 @@
         </is>
       </c>
       <c r="AN154" t="inlineStr"/>
-      <c r="AO154" t="inlineStr"/>
+      <c r="AO154" t="n">
+        <v>62.8021978021978</v>
+      </c>
       <c r="AP154" t="inlineStr"/>
       <c r="AQ154" t="inlineStr"/>
       <c r="AR154" t="inlineStr">
@@ -13839,9 +14447,15 @@
       <c r="AA156" t="inlineStr"/>
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr"/>
-      <c r="AD156" t="inlineStr"/>
-      <c r="AE156" t="inlineStr"/>
-      <c r="AF156" t="inlineStr"/>
+      <c r="AD156" t="n">
+        <v>62.46056782334384</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>62.46056782334384</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>62.46056782334384</v>
+      </c>
       <c r="AG156" t="inlineStr">
         <is>
           <t>22/10/2025</t>
@@ -13870,7 +14484,9 @@
         </is>
       </c>
       <c r="AN156" t="inlineStr"/>
-      <c r="AO156" t="inlineStr"/>
+      <c r="AO156" t="n">
+        <v>62.46056782334384</v>
+      </c>
       <c r="AP156" t="inlineStr"/>
       <c r="AQ156" t="inlineStr"/>
       <c r="AR156" t="inlineStr">
@@ -14009,9 +14625,15 @@
       <c r="AA158" t="inlineStr"/>
       <c r="AB158" t="inlineStr"/>
       <c r="AC158" t="inlineStr"/>
-      <c r="AD158" t="inlineStr"/>
-      <c r="AE158" t="inlineStr"/>
-      <c r="AF158" t="inlineStr"/>
+      <c r="AD158" t="n">
+        <v>60.69895769466586</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>60.69895769466586</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>60.69895769466586</v>
+      </c>
       <c r="AG158" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -14040,7 +14662,9 @@
         </is>
       </c>
       <c r="AN158" t="inlineStr"/>
-      <c r="AO158" t="inlineStr"/>
+      <c r="AO158" t="n">
+        <v>60.69895769466586</v>
+      </c>
       <c r="AP158" t="inlineStr"/>
       <c r="AQ158" t="inlineStr"/>
       <c r="AR158" t="inlineStr">
@@ -14179,9 +14803,15 @@
       <c r="AA160" t="inlineStr"/>
       <c r="AB160" t="inlineStr"/>
       <c r="AC160" t="inlineStr"/>
-      <c r="AD160" t="inlineStr"/>
-      <c r="AE160" t="inlineStr"/>
-      <c r="AF160" t="inlineStr"/>
+      <c r="AD160" t="n">
+        <v>62.52713851498045</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>62.52713851498045</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>62.52713851498045</v>
+      </c>
       <c r="AG160" t="inlineStr">
         <is>
           <t>28/10/2025</t>
@@ -14210,7 +14840,9 @@
         </is>
       </c>
       <c r="AN160" t="inlineStr"/>
-      <c r="AO160" t="inlineStr"/>
+      <c r="AO160" t="n">
+        <v>62.52713851498045</v>
+      </c>
       <c r="AP160" t="inlineStr"/>
       <c r="AQ160" t="inlineStr"/>
       <c r="AR160" t="inlineStr">
@@ -14349,9 +14981,15 @@
       <c r="AA162" t="inlineStr"/>
       <c r="AB162" t="inlineStr"/>
       <c r="AC162" t="inlineStr"/>
-      <c r="AD162" t="inlineStr"/>
-      <c r="AE162" t="inlineStr"/>
-      <c r="AF162" t="inlineStr"/>
+      <c r="AD162" t="n">
+        <v>62.28882833787466</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>62.28882833787466</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>62.28882833787466</v>
+      </c>
       <c r="AG162" t="inlineStr">
         <is>
           <t>17/09/2025</t>
@@ -14380,7 +15018,9 @@
         </is>
       </c>
       <c r="AN162" t="inlineStr"/>
-      <c r="AO162" t="inlineStr"/>
+      <c r="AO162" t="n">
+        <v>62.28882833787466</v>
+      </c>
       <c r="AP162" t="inlineStr"/>
       <c r="AQ162" t="inlineStr"/>
       <c r="AR162" t="inlineStr">
@@ -14657,9 +15297,15 @@
       <c r="AA166" t="inlineStr"/>
       <c r="AB166" t="inlineStr"/>
       <c r="AC166" t="inlineStr"/>
-      <c r="AD166" t="inlineStr"/>
-      <c r="AE166" t="inlineStr"/>
-      <c r="AF166" t="inlineStr"/>
+      <c r="AD166" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AG166" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -14688,7 +15334,9 @@
         </is>
       </c>
       <c r="AN166" t="inlineStr"/>
-      <c r="AO166" t="inlineStr"/>
+      <c r="AO166" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AP166" t="inlineStr"/>
       <c r="AQ166" t="inlineStr"/>
       <c r="AR166" t="inlineStr">
@@ -14827,9 +15475,15 @@
       <c r="AA168" t="inlineStr"/>
       <c r="AB168" t="inlineStr"/>
       <c r="AC168" t="inlineStr"/>
-      <c r="AD168" t="inlineStr"/>
-      <c r="AE168" t="inlineStr"/>
-      <c r="AF168" t="inlineStr"/>
+      <c r="AD168" t="n">
+        <v>62.74473924977127</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>62.74473924977127</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>62.74473924977127</v>
+      </c>
       <c r="AG168" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -14858,7 +15512,9 @@
         </is>
       </c>
       <c r="AN168" t="inlineStr"/>
-      <c r="AO168" t="inlineStr"/>
+      <c r="AO168" t="n">
+        <v>62.74473924977127</v>
+      </c>
       <c r="AP168" t="inlineStr"/>
       <c r="AQ168" t="inlineStr"/>
       <c r="AR168" t="inlineStr">
@@ -14997,9 +15653,15 @@
       <c r="AA170" t="inlineStr"/>
       <c r="AB170" t="inlineStr"/>
       <c r="AC170" t="inlineStr"/>
-      <c r="AD170" t="inlineStr"/>
-      <c r="AE170" t="inlineStr"/>
-      <c r="AF170" t="inlineStr"/>
+      <c r="AD170" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>62.17203586848224</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AG170" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -15028,7 +15690,9 @@
         </is>
       </c>
       <c r="AN170" t="inlineStr"/>
-      <c r="AO170" t="inlineStr"/>
+      <c r="AO170" t="n">
+        <v>62.17203586848224</v>
+      </c>
       <c r="AP170" t="inlineStr"/>
       <c r="AQ170" t="inlineStr"/>
       <c r="AR170" t="inlineStr">
@@ -15167,9 +15831,15 @@
       <c r="AA172" t="inlineStr"/>
       <c r="AB172" t="inlineStr"/>
       <c r="AC172" t="inlineStr"/>
-      <c r="AD172" t="inlineStr"/>
-      <c r="AE172" t="inlineStr"/>
-      <c r="AF172" t="inlineStr"/>
+      <c r="AD172" t="n">
+        <v>61.8392134181608</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>61.8392134181608</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>61.8392134181608</v>
+      </c>
       <c r="AG172" t="inlineStr">
         <is>
           <t>6/10/2025</t>
@@ -15198,7 +15868,9 @@
         </is>
       </c>
       <c r="AN172" t="inlineStr"/>
-      <c r="AO172" t="inlineStr"/>
+      <c r="AO172" t="n">
+        <v>61.8392134181608</v>
+      </c>
       <c r="AP172" t="inlineStr"/>
       <c r="AQ172" t="inlineStr"/>
       <c r="AR172" t="inlineStr">
@@ -15337,9 +16009,15 @@
       <c r="AA174" t="inlineStr"/>
       <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="inlineStr"/>
-      <c r="AD174" t="inlineStr"/>
-      <c r="AE174" t="inlineStr"/>
-      <c r="AF174" t="inlineStr"/>
+      <c r="AD174" t="n">
+        <v>62.8021978021978</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>62.8021978021978</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>62.8021978021978</v>
+      </c>
       <c r="AG174" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -15368,7 +16046,9 @@
         </is>
       </c>
       <c r="AN174" t="inlineStr"/>
-      <c r="AO174" t="inlineStr"/>
+      <c r="AO174" t="n">
+        <v>62.8021978021978</v>
+      </c>
       <c r="AP174" t="inlineStr"/>
       <c r="AQ174" t="inlineStr"/>
       <c r="AR174" t="inlineStr">
@@ -15507,9 +16187,15 @@
       <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="inlineStr"/>
       <c r="AC176" t="inlineStr"/>
-      <c r="AD176" t="inlineStr"/>
-      <c r="AE176" t="inlineStr"/>
-      <c r="AF176" t="inlineStr"/>
+      <c r="AD176" t="n">
+        <v>63.82978723404256</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>63.82978723404256</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>63.82978723404256</v>
+      </c>
       <c r="AG176" t="inlineStr">
         <is>
           <t>30/10/2025</t>
@@ -15538,7 +16224,9 @@
         </is>
       </c>
       <c r="AN176" t="inlineStr"/>
-      <c r="AO176" t="inlineStr"/>
+      <c r="AO176" t="n">
+        <v>63.82978723404256</v>
+      </c>
       <c r="AP176" t="inlineStr"/>
       <c r="AQ176" t="inlineStr"/>
       <c r="AR176" t="inlineStr">
@@ -15677,9 +16365,15 @@
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr"/>
       <c r="AC178" t="inlineStr"/>
-      <c r="AD178" t="inlineStr"/>
-      <c r="AE178" t="inlineStr"/>
-      <c r="AF178" t="inlineStr"/>
+      <c r="AD178" t="n">
+        <v>62.68738574040219</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>62.68738574040219</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>62.68738574040219</v>
+      </c>
       <c r="AG178" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -15708,7 +16402,9 @@
         </is>
       </c>
       <c r="AN178" t="inlineStr"/>
-      <c r="AO178" t="inlineStr"/>
+      <c r="AO178" t="n">
+        <v>62.68738574040219</v>
+      </c>
       <c r="AP178" t="inlineStr"/>
       <c r="AQ178" t="inlineStr"/>
       <c r="AR178" t="inlineStr">
@@ -15847,9 +16543,15 @@
       <c r="AA180" t="inlineStr"/>
       <c r="AB180" t="inlineStr"/>
       <c r="AC180" t="inlineStr"/>
-      <c r="AD180" t="inlineStr"/>
-      <c r="AE180" t="inlineStr"/>
-      <c r="AF180" t="inlineStr"/>
+      <c r="AD180" t="n">
+        <v>62.97709923664122</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>62.97709923664122</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>62.97709923664122</v>
+      </c>
       <c r="AG180" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -15878,7 +16580,9 @@
         </is>
       </c>
       <c r="AN180" t="inlineStr"/>
-      <c r="AO180" t="inlineStr"/>
+      <c r="AO180" t="n">
+        <v>62.97709923664122</v>
+      </c>
       <c r="AP180" t="inlineStr"/>
       <c r="AQ180" t="inlineStr"/>
       <c r="AR180" t="inlineStr">
@@ -16017,9 +16721,15 @@
       <c r="AA182" t="inlineStr"/>
       <c r="AB182" t="inlineStr"/>
       <c r="AC182" t="inlineStr"/>
-      <c r="AD182" t="inlineStr"/>
-      <c r="AE182" t="inlineStr"/>
-      <c r="AF182" t="inlineStr"/>
+      <c r="AD182" t="n">
+        <v>62.10465784933871</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>62.10465784933871</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>62.10465784933871</v>
+      </c>
       <c r="AG182" t="inlineStr">
         <is>
           <t>3/11/2025</t>
@@ -16048,7 +16758,9 @@
         </is>
       </c>
       <c r="AN182" t="inlineStr"/>
-      <c r="AO182" t="inlineStr"/>
+      <c r="AO182" t="n">
+        <v>62.10465784933871</v>
+      </c>
       <c r="AP182" t="inlineStr"/>
       <c r="AQ182" t="inlineStr"/>
       <c r="AR182" t="inlineStr">
@@ -16124,9 +16836,15 @@
       <c r="AA183" t="inlineStr"/>
       <c r="AB183" t="inlineStr"/>
       <c r="AC183" t="inlineStr"/>
-      <c r="AD183" t="inlineStr"/>
-      <c r="AE183" t="inlineStr"/>
-      <c r="AF183" t="inlineStr"/>
+      <c r="AD183" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AG183" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -16155,7 +16873,9 @@
         </is>
       </c>
       <c r="AN183" t="inlineStr"/>
-      <c r="AO183" t="inlineStr"/>
+      <c r="AO183" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AP183" t="inlineStr"/>
       <c r="AQ183" t="inlineStr"/>
       <c r="AR183" t="inlineStr">
@@ -16294,9 +17014,15 @@
       <c r="AA185" t="inlineStr"/>
       <c r="AB185" t="inlineStr"/>
       <c r="AC185" t="inlineStr"/>
-      <c r="AD185" t="inlineStr"/>
-      <c r="AE185" t="inlineStr"/>
-      <c r="AF185" t="inlineStr"/>
+      <c r="AD185" t="n">
+        <v>61.94573130377233</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>61.94573130377233</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>61.94573130377233</v>
+      </c>
       <c r="AG185" t="inlineStr">
         <is>
           <t>8/11/2025</t>
@@ -16325,7 +17051,9 @@
         </is>
       </c>
       <c r="AN185" t="inlineStr"/>
-      <c r="AO185" t="inlineStr"/>
+      <c r="AO185" t="n">
+        <v>61.94573130377233</v>
+      </c>
       <c r="AP185" t="inlineStr"/>
       <c r="AQ185" t="inlineStr"/>
       <c r="AR185" t="inlineStr">
@@ -16464,9 +17192,15 @@
       <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="inlineStr"/>
-      <c r="AD187" t="inlineStr"/>
-      <c r="AE187" t="inlineStr"/>
-      <c r="AF187" t="inlineStr"/>
+      <c r="AD187" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AG187" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -16495,7 +17229,9 @@
         </is>
       </c>
       <c r="AN187" t="inlineStr"/>
-      <c r="AO187" t="inlineStr"/>
+      <c r="AO187" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AP187" t="inlineStr"/>
       <c r="AQ187" t="inlineStr"/>
       <c r="AR187" t="inlineStr">
@@ -16634,9 +17370,15 @@
       <c r="AA189" t="inlineStr"/>
       <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="inlineStr"/>
-      <c r="AD189" t="inlineStr"/>
-      <c r="AE189" t="inlineStr"/>
-      <c r="AF189" t="inlineStr"/>
+      <c r="AD189" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AG189" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -16665,7 +17407,9 @@
         </is>
       </c>
       <c r="AN189" t="inlineStr"/>
-      <c r="AO189" t="inlineStr"/>
+      <c r="AO189" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AP189" t="inlineStr"/>
       <c r="AQ189" t="inlineStr"/>
       <c r="AR189" t="inlineStr">
@@ -16804,9 +17548,15 @@
       <c r="AA191" t="inlineStr"/>
       <c r="AB191" t="inlineStr"/>
       <c r="AC191" t="inlineStr"/>
-      <c r="AD191" t="inlineStr"/>
-      <c r="AE191" t="inlineStr"/>
-      <c r="AF191" t="inlineStr"/>
+      <c r="AD191" t="n">
+        <v>61.78378378378378</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>61.78378378378378</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>61.78378378378378</v>
+      </c>
       <c r="AG191" t="inlineStr">
         <is>
           <t>8/11/2025</t>
@@ -16835,7 +17585,9 @@
         </is>
       </c>
       <c r="AN191" t="inlineStr"/>
-      <c r="AO191" t="inlineStr"/>
+      <c r="AO191" t="n">
+        <v>61.78378378378378</v>
+      </c>
       <c r="AP191" t="inlineStr"/>
       <c r="AQ191" t="inlineStr"/>
       <c r="AR191" t="inlineStr">
@@ -16974,9 +17726,15 @@
       <c r="AA193" t="inlineStr"/>
       <c r="AB193" t="inlineStr"/>
       <c r="AC193" t="inlineStr"/>
-      <c r="AD193" t="inlineStr"/>
-      <c r="AE193" t="inlineStr"/>
-      <c r="AF193" t="inlineStr"/>
+      <c r="AD193" t="n">
+        <v>63.74455732946299</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>63.74455732946299</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>63.74455732946299</v>
+      </c>
       <c r="AG193" t="inlineStr">
         <is>
           <t>7/11/2025</t>
@@ -17005,7 +17763,9 @@
         </is>
       </c>
       <c r="AN193" t="inlineStr"/>
-      <c r="AO193" t="inlineStr"/>
+      <c r="AO193" t="n">
+        <v>63.74455732946299</v>
+      </c>
       <c r="AP193" t="inlineStr"/>
       <c r="AQ193" t="inlineStr"/>
       <c r="AR193" t="inlineStr">
@@ -17144,9 +17904,15 @@
       <c r="AA195" t="inlineStr"/>
       <c r="AB195" t="inlineStr"/>
       <c r="AC195" t="inlineStr"/>
-      <c r="AD195" t="inlineStr"/>
-      <c r="AE195" t="inlineStr"/>
-      <c r="AF195" t="inlineStr"/>
+      <c r="AD195" t="n">
+        <v>62.68738574040219</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>62.68738574040219</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>62.68738574040219</v>
+      </c>
       <c r="AG195" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -17175,7 +17941,9 @@
         </is>
       </c>
       <c r="AN195" t="inlineStr"/>
-      <c r="AO195" t="inlineStr"/>
+      <c r="AO195" t="n">
+        <v>62.68738574040219</v>
+      </c>
       <c r="AP195" t="inlineStr"/>
       <c r="AQ195" t="inlineStr"/>
       <c r="AR195" t="inlineStr">
@@ -17314,9 +18082,15 @@
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr"/>
       <c r="AC197" t="inlineStr"/>
-      <c r="AD197" t="inlineStr"/>
-      <c r="AE197" t="inlineStr"/>
-      <c r="AF197" t="inlineStr"/>
+      <c r="AD197" t="n">
+        <v>62.23230490018149</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>62.23230490018149</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>62.23230490018149</v>
+      </c>
       <c r="AG197" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -17345,7 +18119,9 @@
         </is>
       </c>
       <c r="AN197" t="inlineStr"/>
-      <c r="AO197" t="inlineStr"/>
+      <c r="AO197" t="n">
+        <v>62.23230490018149</v>
+      </c>
       <c r="AP197" t="inlineStr"/>
       <c r="AQ197" t="inlineStr"/>
       <c r="AR197" t="inlineStr">
@@ -17484,9 +18260,15 @@
       <c r="AA199" t="inlineStr"/>
       <c r="AB199" t="inlineStr"/>
       <c r="AC199" t="inlineStr"/>
-      <c r="AD199" t="inlineStr"/>
-      <c r="AE199" t="inlineStr"/>
-      <c r="AF199" t="inlineStr"/>
+      <c r="AD199" t="n">
+        <v>61.08597285067874</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>61.08597285067874</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>61.08597285067874</v>
+      </c>
       <c r="AG199" t="inlineStr">
         <is>
           <t>3/11/2025</t>
@@ -17515,7 +18297,9 @@
         </is>
       </c>
       <c r="AN199" t="inlineStr"/>
-      <c r="AO199" t="inlineStr"/>
+      <c r="AO199" t="n">
+        <v>61.08597285067874</v>
+      </c>
       <c r="AP199" t="inlineStr"/>
       <c r="AQ199" t="inlineStr"/>
       <c r="AR199" t="inlineStr">
@@ -17654,9 +18438,15 @@
       <c r="AA201" t="inlineStr"/>
       <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="inlineStr"/>
-      <c r="AD201" t="inlineStr"/>
-      <c r="AE201" t="inlineStr"/>
-      <c r="AF201" t="inlineStr"/>
+      <c r="AD201" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AG201" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -17685,7 +18475,9 @@
         </is>
       </c>
       <c r="AN201" t="inlineStr"/>
-      <c r="AO201" t="inlineStr"/>
+      <c r="AO201" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AP201" t="inlineStr"/>
       <c r="AQ201" t="inlineStr"/>
       <c r="AR201" t="inlineStr">
@@ -17761,9 +18553,15 @@
       <c r="AA202" t="inlineStr"/>
       <c r="AB202" t="inlineStr"/>
       <c r="AC202" t="inlineStr"/>
-      <c r="AD202" t="inlineStr"/>
-      <c r="AE202" t="inlineStr"/>
-      <c r="AF202" t="inlineStr"/>
+      <c r="AD202" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>62.1195652173913</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AG202" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -17792,7 +18590,9 @@
         </is>
       </c>
       <c r="AN202" t="inlineStr"/>
-      <c r="AO202" t="inlineStr"/>
+      <c r="AO202" t="n">
+        <v>62.1195652173913</v>
+      </c>
       <c r="AP202" t="inlineStr"/>
       <c r="AQ202" t="inlineStr"/>
       <c r="AR202" t="inlineStr">
@@ -17931,9 +18731,15 @@
       <c r="AA204" t="inlineStr"/>
       <c r="AB204" t="inlineStr"/>
       <c r="AC204" t="inlineStr"/>
-      <c r="AD204" t="inlineStr"/>
-      <c r="AE204" t="inlineStr"/>
-      <c r="AF204" t="inlineStr"/>
+      <c r="AD204" t="n">
+        <v>61.94573130377233</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>61.94573130377233</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>61.94573130377233</v>
+      </c>
       <c r="AG204" t="inlineStr">
         <is>
           <t>8/11/2025</t>
@@ -17962,7 +18768,9 @@
         </is>
       </c>
       <c r="AN204" t="inlineStr"/>
-      <c r="AO204" t="inlineStr"/>
+      <c r="AO204" t="n">
+        <v>61.94573130377233</v>
+      </c>
       <c r="AP204" t="inlineStr"/>
       <c r="AQ204" t="inlineStr"/>
       <c r="AR204" t="inlineStr">
@@ -18101,9 +18909,15 @@
       <c r="AA206" t="inlineStr"/>
       <c r="AB206" t="inlineStr"/>
       <c r="AC206" t="inlineStr"/>
-      <c r="AD206" t="inlineStr"/>
-      <c r="AE206" t="inlineStr"/>
-      <c r="AF206" t="inlineStr"/>
+      <c r="AD206" t="n">
+        <v>62.74473924977127</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>62.74473924977127</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>62.74473924977127</v>
+      </c>
       <c r="AG206" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -18132,7 +18946,9 @@
         </is>
       </c>
       <c r="AN206" t="inlineStr"/>
-      <c r="AO206" t="inlineStr"/>
+      <c r="AO206" t="n">
+        <v>62.74473924977127</v>
+      </c>
       <c r="AP206" t="inlineStr"/>
       <c r="AQ206" t="inlineStr"/>
       <c r="AR206" t="inlineStr">
@@ -18271,9 +19087,15 @@
       <c r="AA208" t="inlineStr"/>
       <c r="AB208" t="inlineStr"/>
       <c r="AC208" t="inlineStr"/>
-      <c r="AD208" t="inlineStr"/>
-      <c r="AE208" t="inlineStr"/>
-      <c r="AF208" t="inlineStr"/>
+      <c r="AD208" t="n">
+        <v>64.02845709204091</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>64.02845709204091</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>64.02845709204091</v>
+      </c>
       <c r="AG208" t="inlineStr">
         <is>
           <t>10/10/2025</t>
@@ -18302,7 +19124,9 @@
         </is>
       </c>
       <c r="AN208" t="inlineStr"/>
-      <c r="AO208" t="inlineStr"/>
+      <c r="AO208" t="n">
+        <v>64.02845709204091</v>
+      </c>
       <c r="AP208" t="inlineStr"/>
       <c r="AQ208" t="inlineStr"/>
       <c r="AR208" t="inlineStr">
@@ -18441,9 +19265,15 @@
       <c r="AA210" t="inlineStr"/>
       <c r="AB210" t="inlineStr"/>
       <c r="AC210" t="inlineStr"/>
-      <c r="AD210" t="inlineStr"/>
-      <c r="AE210" t="inlineStr"/>
-      <c r="AF210" t="inlineStr"/>
+      <c r="AD210" t="n">
+        <v>62.96670030272453</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>62.96670030272453</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>62.96670030272453</v>
+      </c>
       <c r="AG210" t="inlineStr">
         <is>
           <t>1/11/2025</t>
@@ -18472,7 +19302,9 @@
         </is>
       </c>
       <c r="AN210" t="inlineStr"/>
-      <c r="AO210" t="inlineStr"/>
+      <c r="AO210" t="n">
+        <v>62.96670030272453</v>
+      </c>
       <c r="AP210" t="inlineStr"/>
       <c r="AQ210" t="inlineStr"/>
       <c r="AR210" t="inlineStr">
@@ -18611,9 +19443,15 @@
       <c r="AA212" t="inlineStr"/>
       <c r="AB212" t="inlineStr"/>
       <c r="AC212" t="inlineStr"/>
-      <c r="AD212" t="inlineStr"/>
-      <c r="AE212" t="inlineStr"/>
-      <c r="AF212" t="inlineStr"/>
+      <c r="AD212" t="n">
+        <v>62.68738574040219</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>62.68738574040219</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>62.68738574040219</v>
+      </c>
       <c r="AG212" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -18642,7 +19480,9 @@
         </is>
       </c>
       <c r="AN212" t="inlineStr"/>
-      <c r="AO212" t="inlineStr"/>
+      <c r="AO212" t="n">
+        <v>62.68738574040219</v>
+      </c>
       <c r="AP212" t="inlineStr"/>
       <c r="AQ212" t="inlineStr"/>
       <c r="AR212" t="inlineStr">
@@ -18781,9 +19621,15 @@
       <c r="AA214" t="inlineStr"/>
       <c r="AB214" t="inlineStr"/>
       <c r="AC214" t="inlineStr"/>
-      <c r="AD214" t="inlineStr"/>
-      <c r="AE214" t="inlineStr"/>
-      <c r="AF214" t="inlineStr"/>
+      <c r="AD214" t="n">
+        <v>62.23230490018149</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>62.23230490018149</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>62.23230490018149</v>
+      </c>
       <c r="AG214" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -18812,7 +19658,9 @@
         </is>
       </c>
       <c r="AN214" t="inlineStr"/>
-      <c r="AO214" t="inlineStr"/>
+      <c r="AO214" t="n">
+        <v>62.23230490018149</v>
+      </c>
       <c r="AP214" t="inlineStr"/>
       <c r="AQ214" t="inlineStr"/>
       <c r="AR214" t="inlineStr">

--- a/outputs/all_dogs_master.xlsx
+++ b/outputs/all_dogs_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC179"/>
+  <dimension ref="A1:BF179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,14 +436,14 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Race_Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Race_No</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Race_Date</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Box</t>
@@ -466,242 +466,257 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>BP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>A/S</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>WT (kg)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Trainer</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sire</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Dam</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Career_W-P-S</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Prize_Money</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>RTC</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>DLR</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DLW</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Car_PM/s (G1)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>12m_PM/s (G2)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>API (G3)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>RTC/km</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Trainer_Win_%</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Trainer_Place_%</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Raced_Dist_W-P-S</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Crs_W-P-S</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Dist_W-P-S</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>FU_W-P-S</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>2U_W-P-S</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>DOD</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Avg_Speed_km/h</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Min_Speed_km/h</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Max_Speed_km/h</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Date</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Track</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Distance</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Finish_Pos</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Margin_L</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Race_Time</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Sec_Time</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Sec_Time_Adj</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Speed_km/h</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_SOT</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_RST</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_BP</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Odds</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_API</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Prize_Won</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Winner</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_2nd_Place</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_3rd_Place</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Settled_Turn</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Ongoing_Winners</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Hist_Track_Direction</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Hist_Count</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Date</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Track</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Distance</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Finish_Pos</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Margin_L</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Race_Time</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Sec_Time</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Sec_Time_Adj</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Speed_km/h</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_SOT</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_RST</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_BP</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Odds</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_API</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Prize_Won</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Winner</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_2nd_Place</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_3rd_Place</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Settled_Turn</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Ongoing_Winners</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>Hist_Track_Direction</t>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Data_Source_File</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Parse_Timestamp</t>
         </is>
       </c>
     </row>
@@ -711,13 +726,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>12</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -755,9 +770,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
@@ -779,6 +792,15 @@
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -786,13 +808,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>12</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -830,9 +852,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
@@ -854,6 +874,15 @@
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -861,13 +890,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>12</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -905,9 +934,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
@@ -929,6 +956,15 @@
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -936,13 +972,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>12</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -980,9 +1016,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
@@ -1004,6 +1038,15 @@
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1011,13 +1054,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>12</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -1055,9 +1098,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
@@ -1079,6 +1120,15 @@
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1086,13 +1136,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>12</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1130,9 +1180,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
@@ -1154,6 +1202,15 @@
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1161,13 +1218,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>12</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -1205,9 +1262,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
@@ -1229,6 +1284,15 @@
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1236,13 +1300,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>12</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -1280,9 +1344,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
@@ -1304,6 +1366,15 @@
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1311,13 +1382,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>12</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -1355,9 +1426,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
@@ -1379,6 +1448,15 @@
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1386,13 +1464,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>12</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -1430,9 +1508,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
@@ -1454,6 +1530,15 @@
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1461,13 +1546,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>12</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -1505,9 +1590,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
@@ -1529,6 +1612,15 @@
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1536,13 +1628,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>12</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -1580,9 +1672,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
@@ -1604,6 +1694,15 @@
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1611,13 +1710,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>12</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
@@ -1655,9 +1754,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
@@ -1679,6 +1776,15 @@
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1686,13 +1792,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>12</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -1730,9 +1836,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
@@ -1754,6 +1858,15 @@
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1761,13 +1874,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>12</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -1805,9 +1918,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
@@ -1829,6 +1940,15 @@
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1836,13 +1956,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>12</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
@@ -1880,9 +2000,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
@@ -1904,6 +2022,15 @@
       <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1911,13 +2038,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>12</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1955,9 +2082,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
@@ -1979,6 +2104,15 @@
       <c r="BA18" t="inlineStr"/>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1986,13 +2120,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>12</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D19" t="n">
         <v>2</v>
@@ -2030,9 +2164,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
@@ -2054,6 +2186,15 @@
       <c r="BA19" t="inlineStr"/>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2061,13 +2202,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>12</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D20" t="n">
         <v>2</v>
@@ -2105,9 +2246,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
@@ -2129,6 +2268,15 @@
       <c r="BA20" t="inlineStr"/>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2136,13 +2284,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>12</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -2180,9 +2328,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
@@ -2204,6 +2350,15 @@
       <c r="BA21" t="inlineStr"/>
       <c r="BB21" t="inlineStr"/>
       <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2211,13 +2366,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>12</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
@@ -2255,9 +2410,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
@@ -2279,6 +2432,15 @@
       <c r="BA22" t="inlineStr"/>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2286,13 +2448,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>12</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -2330,9 +2492,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
@@ -2354,6 +2514,15 @@
       <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2361,13 +2530,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>12</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D24" t="n">
         <v>2</v>
@@ -2405,9 +2574,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
@@ -2429,6 +2596,15 @@
       <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="inlineStr"/>
       <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2436,13 +2612,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>12</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D25" t="n">
         <v>3</v>
@@ -2480,9 +2656,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
@@ -2504,6 +2678,15 @@
       <c r="BA25" t="inlineStr"/>
       <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2511,13 +2694,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>12</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D26" t="n">
         <v>3</v>
@@ -2555,9 +2738,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
@@ -2579,6 +2760,15 @@
       <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="inlineStr"/>
       <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2586,13 +2776,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>12</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D27" t="n">
         <v>3</v>
@@ -2630,9 +2820,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
@@ -2654,6 +2842,15 @@
       <c r="BA27" t="inlineStr"/>
       <c r="BB27" t="inlineStr"/>
       <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2661,13 +2858,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>12</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D28" t="n">
         <v>3</v>
@@ -2705,9 +2902,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
@@ -2729,6 +2924,15 @@
       <c r="BA28" t="inlineStr"/>
       <c r="BB28" t="inlineStr"/>
       <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2736,13 +2940,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>12</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D29" t="n">
         <v>3</v>
@@ -2780,9 +2984,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
@@ -2804,6 +3006,15 @@
       <c r="BA29" t="inlineStr"/>
       <c r="BB29" t="inlineStr"/>
       <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2811,13 +3022,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>12</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D30" t="n">
         <v>3</v>
@@ -2855,9 +3066,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
@@ -2879,6 +3088,15 @@
       <c r="BA30" t="inlineStr"/>
       <c r="BB30" t="inlineStr"/>
       <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2886,13 +3104,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>12</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D31" t="n">
         <v>3</v>
@@ -2930,9 +3148,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
@@ -2954,6 +3170,15 @@
       <c r="BA31" t="inlineStr"/>
       <c r="BB31" t="inlineStr"/>
       <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2961,13 +3186,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
         <v>12</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D32" t="n">
         <v>3</v>
@@ -3005,9 +3230,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
@@ -3029,6 +3252,15 @@
       <c r="BA32" t="inlineStr"/>
       <c r="BB32" t="inlineStr"/>
       <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3036,13 +3268,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
         <v>12</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D33" t="n">
         <v>3</v>
@@ -3080,9 +3312,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr"/>
@@ -3104,6 +3334,15 @@
       <c r="BA33" t="inlineStr"/>
       <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3111,13 +3350,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
         <v>12</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D34" t="n">
         <v>4</v>
@@ -3155,9 +3394,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
@@ -3179,6 +3416,15 @@
       <c r="BA34" t="inlineStr"/>
       <c r="BB34" t="inlineStr"/>
       <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3186,13 +3432,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>12</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D35" t="n">
         <v>4</v>
@@ -3230,9 +3476,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
@@ -3254,6 +3498,15 @@
       <c r="BA35" t="inlineStr"/>
       <c r="BB35" t="inlineStr"/>
       <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3261,13 +3514,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
         <v>12</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D36" t="n">
         <v>4</v>
@@ -3305,9 +3558,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
@@ -3329,6 +3580,15 @@
       <c r="BA36" t="inlineStr"/>
       <c r="BB36" t="inlineStr"/>
       <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3336,13 +3596,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>12</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D37" t="n">
         <v>4</v>
@@ -3380,9 +3640,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
@@ -3404,6 +3662,15 @@
       <c r="BA37" t="inlineStr"/>
       <c r="BB37" t="inlineStr"/>
       <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3411,13 +3678,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
         <v>12</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D38" t="n">
         <v>4</v>
@@ -3455,9 +3722,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
@@ -3479,6 +3744,15 @@
       <c r="BA38" t="inlineStr"/>
       <c r="BB38" t="inlineStr"/>
       <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3486,13 +3760,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
         <v>12</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D39" t="n">
         <v>4</v>
@@ -3530,9 +3804,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
@@ -3554,6 +3826,15 @@
       <c r="BA39" t="inlineStr"/>
       <c r="BB39" t="inlineStr"/>
       <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3561,13 +3842,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
         <v>12</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D40" t="n">
         <v>4</v>
@@ -3605,9 +3886,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
@@ -3629,6 +3908,15 @@
       <c r="BA40" t="inlineStr"/>
       <c r="BB40" t="inlineStr"/>
       <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3636,13 +3924,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
         <v>12</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D41" t="n">
         <v>4</v>
@@ -3680,9 +3968,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
@@ -3704,6 +3990,15 @@
       <c r="BA41" t="inlineStr"/>
       <c r="BB41" t="inlineStr"/>
       <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3711,13 +4006,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
         <v>12</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D42" t="n">
         <v>4</v>
@@ -3755,9 +4050,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
@@ -3779,6 +4072,15 @@
       <c r="BA42" t="inlineStr"/>
       <c r="BB42" t="inlineStr"/>
       <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3786,13 +4088,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
         <v>12</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D43" t="n">
         <v>4</v>
@@ -3830,9 +4132,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
@@ -3854,6 +4154,15 @@
       <c r="BA43" t="inlineStr"/>
       <c r="BB43" t="inlineStr"/>
       <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3861,13 +4170,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
         <v>12</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D44" t="n">
         <v>4</v>
@@ -3905,9 +4214,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
@@ -3929,6 +4236,15 @@
       <c r="BA44" t="inlineStr"/>
       <c r="BB44" t="inlineStr"/>
       <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3936,13 +4252,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
         <v>12</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D45" t="n">
         <v>5</v>
@@ -3980,9 +4296,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
@@ -4004,6 +4318,15 @@
       <c r="BA45" t="inlineStr"/>
       <c r="BB45" t="inlineStr"/>
       <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4011,13 +4334,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
         <v>12</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D46" t="n">
         <v>5</v>
@@ -4055,9 +4378,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
@@ -4079,6 +4400,15 @@
       <c r="BA46" t="inlineStr"/>
       <c r="BB46" t="inlineStr"/>
       <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4086,13 +4416,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
         <v>12</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D47" t="n">
         <v>5</v>
@@ -4130,9 +4460,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr"/>
@@ -4154,6 +4482,15 @@
       <c r="BA47" t="inlineStr"/>
       <c r="BB47" t="inlineStr"/>
       <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4161,13 +4498,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
         <v>12</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D48" t="n">
         <v>5</v>
@@ -4205,9 +4542,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
       <c r="AK48" t="inlineStr"/>
@@ -4229,6 +4564,15 @@
       <c r="BA48" t="inlineStr"/>
       <c r="BB48" t="inlineStr"/>
       <c r="BC48" t="inlineStr"/>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="inlineStr"/>
+      <c r="BF48" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4236,13 +4580,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
         <v>12</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D49" t="n">
         <v>5</v>
@@ -4280,9 +4624,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr"/>
@@ -4304,6 +4646,15 @@
       <c r="BA49" t="inlineStr"/>
       <c r="BB49" t="inlineStr"/>
       <c r="BC49" t="inlineStr"/>
+      <c r="BD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE49" t="inlineStr"/>
+      <c r="BF49" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4311,13 +4662,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
         <v>12</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D50" t="n">
         <v>5</v>
@@ -4355,9 +4706,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="inlineStr"/>
@@ -4379,6 +4728,15 @@
       <c r="BA50" t="inlineStr"/>
       <c r="BB50" t="inlineStr"/>
       <c r="BC50" t="inlineStr"/>
+      <c r="BD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE50" t="inlineStr"/>
+      <c r="BF50" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4386,13 +4744,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
         <v>12</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D51" t="n">
         <v>5</v>
@@ -4430,9 +4788,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr"/>
@@ -4454,6 +4810,15 @@
       <c r="BA51" t="inlineStr"/>
       <c r="BB51" t="inlineStr"/>
       <c r="BC51" t="inlineStr"/>
+      <c r="BD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE51" t="inlineStr"/>
+      <c r="BF51" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4461,13 +4826,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
         <v>12</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D52" t="n">
         <v>5</v>
@@ -4505,9 +4870,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr"/>
@@ -4529,6 +4892,15 @@
       <c r="BA52" t="inlineStr"/>
       <c r="BB52" t="inlineStr"/>
       <c r="BC52" t="inlineStr"/>
+      <c r="BD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE52" t="inlineStr"/>
+      <c r="BF52" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4536,13 +4908,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
         <v>12</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D53" t="n">
         <v>5</v>
@@ -4580,9 +4952,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
@@ -4604,6 +4974,15 @@
       <c r="BA53" t="inlineStr"/>
       <c r="BB53" t="inlineStr"/>
       <c r="BC53" t="inlineStr"/>
+      <c r="BD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE53" t="inlineStr"/>
+      <c r="BF53" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4611,13 +4990,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
         <v>12</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D54" t="n">
         <v>5</v>
@@ -4655,9 +5034,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
@@ -4679,6 +5056,15 @@
       <c r="BA54" t="inlineStr"/>
       <c r="BB54" t="inlineStr"/>
       <c r="BC54" t="inlineStr"/>
+      <c r="BD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE54" t="inlineStr"/>
+      <c r="BF54" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4686,13 +5072,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
         <v>12</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D55" t="n">
         <v>5</v>
@@ -4730,9 +5116,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr"/>
@@ -4754,6 +5138,15 @@
       <c r="BA55" t="inlineStr"/>
       <c r="BB55" t="inlineStr"/>
       <c r="BC55" t="inlineStr"/>
+      <c r="BD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE55" t="inlineStr"/>
+      <c r="BF55" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4761,13 +5154,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
         <v>12</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D56" t="n">
         <v>6</v>
@@ -4805,9 +5198,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="inlineStr"/>
@@ -4829,6 +5220,15 @@
       <c r="BA56" t="inlineStr"/>
       <c r="BB56" t="inlineStr"/>
       <c r="BC56" t="inlineStr"/>
+      <c r="BD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE56" t="inlineStr"/>
+      <c r="BF56" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4836,13 +5236,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
         <v>12</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D57" t="n">
         <v>6</v>
@@ -4880,9 +5280,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="inlineStr"/>
       <c r="AJ57" t="inlineStr"/>
       <c r="AK57" t="inlineStr"/>
@@ -4904,6 +5302,15 @@
       <c r="BA57" t="inlineStr"/>
       <c r="BB57" t="inlineStr"/>
       <c r="BC57" t="inlineStr"/>
+      <c r="BD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE57" t="inlineStr"/>
+      <c r="BF57" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4911,13 +5318,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
         <v>12</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D58" t="n">
         <v>6</v>
@@ -4955,9 +5362,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="inlineStr"/>
       <c r="AJ58" t="inlineStr"/>
       <c r="AK58" t="inlineStr"/>
@@ -4979,6 +5384,15 @@
       <c r="BA58" t="inlineStr"/>
       <c r="BB58" t="inlineStr"/>
       <c r="BC58" t="inlineStr"/>
+      <c r="BD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE58" t="inlineStr"/>
+      <c r="BF58" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4986,13 +5400,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
         <v>12</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D59" t="n">
         <v>6</v>
@@ -5030,9 +5444,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="inlineStr"/>
@@ -5054,6 +5466,15 @@
       <c r="BA59" t="inlineStr"/>
       <c r="BB59" t="inlineStr"/>
       <c r="BC59" t="inlineStr"/>
+      <c r="BD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE59" t="inlineStr"/>
+      <c r="BF59" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5061,13 +5482,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
         <v>12</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D60" t="n">
         <v>6</v>
@@ -5105,9 +5526,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
       <c r="AK60" t="inlineStr"/>
@@ -5129,6 +5548,15 @@
       <c r="BA60" t="inlineStr"/>
       <c r="BB60" t="inlineStr"/>
       <c r="BC60" t="inlineStr"/>
+      <c r="BD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE60" t="inlineStr"/>
+      <c r="BF60" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5136,13 +5564,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
         <v>12</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D61" t="n">
         <v>6</v>
@@ -5180,9 +5608,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
       <c r="AK61" t="inlineStr"/>
@@ -5204,6 +5630,15 @@
       <c r="BA61" t="inlineStr"/>
       <c r="BB61" t="inlineStr"/>
       <c r="BC61" t="inlineStr"/>
+      <c r="BD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE61" t="inlineStr"/>
+      <c r="BF61" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5211,13 +5646,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
         <v>12</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D62" t="n">
         <v>6</v>
@@ -5255,9 +5690,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
@@ -5279,6 +5712,15 @@
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
+      <c r="BD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE62" t="inlineStr"/>
+      <c r="BF62" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5286,13 +5728,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
         <v>12</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D63" t="n">
         <v>6</v>
@@ -5330,9 +5772,7 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
-      <c r="AH63" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr"/>
       <c r="AK63" t="inlineStr"/>
@@ -5354,6 +5794,15 @@
       <c r="BA63" t="inlineStr"/>
       <c r="BB63" t="inlineStr"/>
       <c r="BC63" t="inlineStr"/>
+      <c r="BD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE63" t="inlineStr"/>
+      <c r="BF63" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5361,13 +5810,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
         <v>12</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D64" t="n">
         <v>6</v>
@@ -5405,9 +5854,7 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
-      <c r="AH64" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr"/>
       <c r="AK64" t="inlineStr"/>
@@ -5429,6 +5876,15 @@
       <c r="BA64" t="inlineStr"/>
       <c r="BB64" t="inlineStr"/>
       <c r="BC64" t="inlineStr"/>
+      <c r="BD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE64" t="inlineStr"/>
+      <c r="BF64" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5436,13 +5892,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
         <v>12</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D65" t="n">
         <v>6</v>
@@ -5480,9 +5936,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
-      <c r="AH65" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="inlineStr"/>
       <c r="AJ65" t="inlineStr"/>
       <c r="AK65" t="inlineStr"/>
@@ -5504,6 +5958,15 @@
       <c r="BA65" t="inlineStr"/>
       <c r="BB65" t="inlineStr"/>
       <c r="BC65" t="inlineStr"/>
+      <c r="BD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE65" t="inlineStr"/>
+      <c r="BF65" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5511,13 +5974,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
         <v>12</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D66" t="n">
         <v>6</v>
@@ -5555,9 +6018,7 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
-      <c r="AH66" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="inlineStr"/>
       <c r="AJ66" t="inlineStr"/>
       <c r="AK66" t="inlineStr"/>
@@ -5579,6 +6040,15 @@
       <c r="BA66" t="inlineStr"/>
       <c r="BB66" t="inlineStr"/>
       <c r="BC66" t="inlineStr"/>
+      <c r="BD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE66" t="inlineStr"/>
+      <c r="BF66" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5586,13 +6056,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
         <v>12</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D67" t="n">
         <v>7</v>
@@ -5630,9 +6100,7 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
-      <c r="AH67" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="inlineStr"/>
       <c r="AJ67" t="inlineStr"/>
       <c r="AK67" t="inlineStr"/>
@@ -5654,6 +6122,15 @@
       <c r="BA67" t="inlineStr"/>
       <c r="BB67" t="inlineStr"/>
       <c r="BC67" t="inlineStr"/>
+      <c r="BD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE67" t="inlineStr"/>
+      <c r="BF67" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5661,13 +6138,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
         <v>12</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D68" t="n">
         <v>7</v>
@@ -5705,9 +6182,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
-      <c r="AH68" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="inlineStr"/>
       <c r="AJ68" t="inlineStr"/>
       <c r="AK68" t="inlineStr"/>
@@ -5729,6 +6204,15 @@
       <c r="BA68" t="inlineStr"/>
       <c r="BB68" t="inlineStr"/>
       <c r="BC68" t="inlineStr"/>
+      <c r="BD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE68" t="inlineStr"/>
+      <c r="BF68" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5736,13 +6220,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
         <v>12</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D69" t="n">
         <v>7</v>
@@ -5780,9 +6264,7 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
-      <c r="AH69" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="inlineStr"/>
       <c r="AJ69" t="inlineStr"/>
       <c r="AK69" t="inlineStr"/>
@@ -5804,6 +6286,15 @@
       <c r="BA69" t="inlineStr"/>
       <c r="BB69" t="inlineStr"/>
       <c r="BC69" t="inlineStr"/>
+      <c r="BD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE69" t="inlineStr"/>
+      <c r="BF69" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5811,13 +6302,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
         <v>12</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D70" t="n">
         <v>7</v>
@@ -5855,9 +6346,7 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
-      <c r="AH70" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="inlineStr"/>
       <c r="AJ70" t="inlineStr"/>
       <c r="AK70" t="inlineStr"/>
@@ -5879,6 +6368,15 @@
       <c r="BA70" t="inlineStr"/>
       <c r="BB70" t="inlineStr"/>
       <c r="BC70" t="inlineStr"/>
+      <c r="BD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE70" t="inlineStr"/>
+      <c r="BF70" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5886,13 +6384,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
         <v>12</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D71" t="n">
         <v>7</v>
@@ -5930,9 +6428,7 @@
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
-      <c r="AH71" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="inlineStr"/>
       <c r="AJ71" t="inlineStr"/>
       <c r="AK71" t="inlineStr"/>
@@ -5954,6 +6450,15 @@
       <c r="BA71" t="inlineStr"/>
       <c r="BB71" t="inlineStr"/>
       <c r="BC71" t="inlineStr"/>
+      <c r="BD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE71" t="inlineStr"/>
+      <c r="BF71" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5961,13 +6466,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
         <v>12</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D72" t="n">
         <v>7</v>
@@ -6005,9 +6510,7 @@
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
-      <c r="AH72" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="inlineStr"/>
       <c r="AJ72" t="inlineStr"/>
       <c r="AK72" t="inlineStr"/>
@@ -6029,6 +6532,15 @@
       <c r="BA72" t="inlineStr"/>
       <c r="BB72" t="inlineStr"/>
       <c r="BC72" t="inlineStr"/>
+      <c r="BD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE72" t="inlineStr"/>
+      <c r="BF72" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6036,13 +6548,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
         <v>12</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D73" t="n">
         <v>7</v>
@@ -6056,21 +6568,21 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
         <is>
           <t>COREY WHITE BP</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr">
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
         <is>
           <t>2,070</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
@@ -6088,9 +6600,7 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
-      <c r="AH73" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="inlineStr">
         <is>
           <t>31/10/2025</t>
@@ -6136,6 +6646,15 @@
       <c r="BA73" t="inlineStr"/>
       <c r="BB73" t="inlineStr"/>
       <c r="BC73" t="inlineStr"/>
+      <c r="BD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE73" t="inlineStr"/>
+      <c r="BF73" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6143,13 +6662,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
         <v>12</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D74" t="n">
         <v>7</v>
@@ -6187,9 +6706,7 @@
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
-      <c r="AH74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="inlineStr"/>
       <c r="AJ74" t="inlineStr"/>
       <c r="AK74" t="inlineStr"/>
@@ -6211,6 +6728,15 @@
       <c r="BA74" t="inlineStr"/>
       <c r="BB74" t="inlineStr"/>
       <c r="BC74" t="inlineStr"/>
+      <c r="BD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE74" t="inlineStr"/>
+      <c r="BF74" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6218,13 +6744,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
         <v>12</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D75" t="n">
         <v>7</v>
@@ -6262,9 +6788,7 @@
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
-      <c r="AH75" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="inlineStr"/>
       <c r="AJ75" t="inlineStr"/>
       <c r="AK75" t="inlineStr"/>
@@ -6286,6 +6810,15 @@
       <c r="BA75" t="inlineStr"/>
       <c r="BB75" t="inlineStr"/>
       <c r="BC75" t="inlineStr"/>
+      <c r="BD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE75" t="inlineStr"/>
+      <c r="BF75" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6293,13 +6826,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
         <v>12</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D76" t="n">
         <v>7</v>
@@ -6313,21 +6846,21 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
         <is>
           <t>Victoria Cook Ongoing Winners</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr">
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
         <is>
           <t>2,070</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
@@ -6345,9 +6878,7 @@
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
-      <c r="AH76" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="inlineStr">
         <is>
           <t>6/11/2025</t>
@@ -6393,6 +6924,15 @@
       <c r="BA76" t="inlineStr"/>
       <c r="BB76" t="inlineStr"/>
       <c r="BC76" t="inlineStr"/>
+      <c r="BD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE76" t="inlineStr"/>
+      <c r="BF76" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6400,13 +6940,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
         <v>12</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D77" t="n">
         <v>7</v>
@@ -6444,9 +6984,7 @@
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
-      <c r="AH77" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="inlineStr"/>
       <c r="AJ77" t="inlineStr"/>
       <c r="AK77" t="inlineStr"/>
@@ -6468,6 +7006,15 @@
       <c r="BA77" t="inlineStr"/>
       <c r="BB77" t="inlineStr"/>
       <c r="BC77" t="inlineStr"/>
+      <c r="BD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE77" t="inlineStr"/>
+      <c r="BF77" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6475,13 +7022,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
         <v>12</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D78" t="n">
         <v>7</v>
@@ -6495,21 +7042,21 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr">
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
         <is>
           <t>Shayne Williams Ongoing Winners</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr">
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
         <is>
           <t>2,510</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
@@ -6527,9 +7074,7 @@
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
-      <c r="AH78" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -6575,6 +7120,15 @@
       <c r="BA78" t="inlineStr"/>
       <c r="BB78" t="inlineStr"/>
       <c r="BC78" t="inlineStr"/>
+      <c r="BD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE78" t="inlineStr"/>
+      <c r="BF78" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6582,13 +7136,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
         <v>12</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D79" t="n">
         <v>8</v>
@@ -6626,9 +7180,7 @@
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
-      <c r="AH79" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="inlineStr"/>
       <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="inlineStr"/>
@@ -6650,6 +7202,15 @@
       <c r="BA79" t="inlineStr"/>
       <c r="BB79" t="inlineStr"/>
       <c r="BC79" t="inlineStr"/>
+      <c r="BD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE79" t="inlineStr"/>
+      <c r="BF79" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6657,13 +7218,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
         <v>12</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D80" t="n">
         <v>8</v>
@@ -6701,9 +7262,7 @@
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
-      <c r="AH80" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="inlineStr"/>
       <c r="AJ80" t="inlineStr"/>
       <c r="AK80" t="inlineStr"/>
@@ -6725,6 +7284,15 @@
       <c r="BA80" t="inlineStr"/>
       <c r="BB80" t="inlineStr"/>
       <c r="BC80" t="inlineStr"/>
+      <c r="BD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE80" t="inlineStr"/>
+      <c r="BF80" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6732,13 +7300,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
         <v>12</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D81" t="n">
         <v>8</v>
@@ -6776,9 +7344,7 @@
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
-      <c r="AH81" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="inlineStr"/>
       <c r="AJ81" t="inlineStr"/>
       <c r="AK81" t="inlineStr"/>
@@ -6800,6 +7366,15 @@
       <c r="BA81" t="inlineStr"/>
       <c r="BB81" t="inlineStr"/>
       <c r="BC81" t="inlineStr"/>
+      <c r="BD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE81" t="inlineStr"/>
+      <c r="BF81" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6807,13 +7382,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
         <v>12</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D82" t="n">
         <v>8</v>
@@ -6851,9 +7426,7 @@
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
-      <c r="AH82" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="inlineStr"/>
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
@@ -6875,6 +7448,15 @@
       <c r="BA82" t="inlineStr"/>
       <c r="BB82" t="inlineStr"/>
       <c r="BC82" t="inlineStr"/>
+      <c r="BD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE82" t="inlineStr"/>
+      <c r="BF82" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6882,13 +7464,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
         <v>12</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D83" t="n">
         <v>8</v>
@@ -6926,9 +7508,7 @@
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
-      <c r="AH83" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="inlineStr"/>
       <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="inlineStr"/>
@@ -6950,6 +7530,15 @@
       <c r="BA83" t="inlineStr"/>
       <c r="BB83" t="inlineStr"/>
       <c r="BC83" t="inlineStr"/>
+      <c r="BD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE83" t="inlineStr"/>
+      <c r="BF83" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6957,13 +7546,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
         <v>12</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D84" t="n">
         <v>8</v>
@@ -7001,9 +7590,7 @@
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="inlineStr"/>
-      <c r="AH84" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="inlineStr"/>
       <c r="AJ84" t="inlineStr"/>
       <c r="AK84" t="inlineStr"/>
@@ -7025,6 +7612,15 @@
       <c r="BA84" t="inlineStr"/>
       <c r="BB84" t="inlineStr"/>
       <c r="BC84" t="inlineStr"/>
+      <c r="BD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE84" t="inlineStr"/>
+      <c r="BF84" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7032,13 +7628,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
         <v>12</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D85" t="n">
         <v>8</v>
@@ -7076,9 +7672,7 @@
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="inlineStr"/>
-      <c r="AH85" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="inlineStr"/>
       <c r="AJ85" t="inlineStr"/>
       <c r="AK85" t="inlineStr"/>
@@ -7100,6 +7694,15 @@
       <c r="BA85" t="inlineStr"/>
       <c r="BB85" t="inlineStr"/>
       <c r="BC85" t="inlineStr"/>
+      <c r="BD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE85" t="inlineStr"/>
+      <c r="BF85" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7107,13 +7710,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
         <v>12</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D86" t="n">
         <v>8</v>
@@ -7151,9 +7754,7 @@
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr"/>
-      <c r="AH86" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="inlineStr"/>
       <c r="AJ86" t="inlineStr"/>
       <c r="AK86" t="inlineStr"/>
@@ -7175,6 +7776,15 @@
       <c r="BA86" t="inlineStr"/>
       <c r="BB86" t="inlineStr"/>
       <c r="BC86" t="inlineStr"/>
+      <c r="BD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE86" t="inlineStr"/>
+      <c r="BF86" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7182,13 +7792,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
         <v>12</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D87" t="n">
         <v>9</v>
@@ -7202,21 +7812,21 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr">
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
         <is>
           <t>Colleen Pierson Ongoing Winners</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr">
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
         <is>
           <t>2,070</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr"/>
@@ -7234,9 +7844,7 @@
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="inlineStr"/>
-      <c r="AH87" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="inlineStr">
         <is>
           <t>6/11/2025</t>
@@ -7282,6 +7890,15 @@
       <c r="BA87" t="inlineStr"/>
       <c r="BB87" t="inlineStr"/>
       <c r="BC87" t="inlineStr"/>
+      <c r="BD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE87" t="inlineStr"/>
+      <c r="BF87" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7289,13 +7906,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
         <v>12</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D88" t="n">
         <v>9</v>
@@ -7309,21 +7926,21 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr">
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
         <is>
           <t>Kody Charles Ongoing Winners</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr">
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
         <is>
           <t>4,250</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr"/>
@@ -7341,9 +7958,7 @@
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="inlineStr"/>
-      <c r="AH88" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -7389,6 +8004,15 @@
       <c r="BA88" t="inlineStr"/>
       <c r="BB88" t="inlineStr"/>
       <c r="BC88" t="inlineStr"/>
+      <c r="BD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE88" t="inlineStr"/>
+      <c r="BF88" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7396,13 +8020,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B89" t="n">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
         <v>12</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D89" t="n">
         <v>9</v>
@@ -7416,21 +8040,21 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
         <is>
           <t>Michael Rylands Ongoing Winners</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr">
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
         <is>
           <t>1,980</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr"/>
@@ -7448,9 +8072,7 @@
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="inlineStr"/>
-      <c r="AH89" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="inlineStr">
         <is>
           <t>16/10/2025</t>
@@ -7496,6 +8118,15 @@
       <c r="BA89" t="inlineStr"/>
       <c r="BB89" t="inlineStr"/>
       <c r="BC89" t="inlineStr"/>
+      <c r="BD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE89" t="inlineStr"/>
+      <c r="BF89" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7503,13 +8134,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
         <v>12</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D90" t="n">
         <v>9</v>
@@ -7523,21 +8154,21 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr">
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
         <is>
           <t>JOSEPH DAILLY BP</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr">
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
         <is>
           <t>7,630</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr"/>
@@ -7555,9 +8186,7 @@
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="inlineStr"/>
-      <c r="AH90" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -7603,6 +8232,15 @@
       <c r="BA90" t="inlineStr"/>
       <c r="BB90" t="inlineStr"/>
       <c r="BC90" t="inlineStr"/>
+      <c r="BD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE90" t="inlineStr"/>
+      <c r="BF90" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7610,13 +8248,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
         <v>12</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D91" t="n">
         <v>9</v>
@@ -7630,21 +8268,21 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr">
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
         <is>
           <t>Justin Wood Ongoing Winners</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr">
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
         <is>
           <t>5,030</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr"/>
@@ -7662,9 +8300,7 @@
       <c r="AE91" t="inlineStr"/>
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr"/>
-      <c r="AH91" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH91" t="inlineStr"/>
       <c r="AI91" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -7710,6 +8346,15 @@
       <c r="BA91" t="inlineStr"/>
       <c r="BB91" t="inlineStr"/>
       <c r="BC91" t="inlineStr"/>
+      <c r="BD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE91" t="inlineStr"/>
+      <c r="BF91" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7717,13 +8362,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
         <v>12</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D92" t="n">
         <v>9</v>
@@ -7737,21 +8382,21 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr">
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
         <is>
           <t>Jesse Erenshaw Ongoing Winners</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr">
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
         <is>
           <t>4,470</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr"/>
@@ -7769,9 +8414,7 @@
       <c r="AE92" t="inlineStr"/>
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="inlineStr"/>
-      <c r="AH92" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH92" t="inlineStr"/>
       <c r="AI92" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -7817,6 +8460,15 @@
       <c r="BA92" t="inlineStr"/>
       <c r="BB92" t="inlineStr"/>
       <c r="BC92" t="inlineStr"/>
+      <c r="BD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE92" t="inlineStr"/>
+      <c r="BF92" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7824,13 +8476,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
         <v>12</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D93" t="n">
         <v>9</v>
@@ -7844,21 +8496,21 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr">
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
         <is>
           <t>Joseph Dailly Ongoing Winners</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr">
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
         <is>
           <t>2,510</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr"/>
@@ -7876,9 +8528,7 @@
       <c r="AE93" t="inlineStr"/>
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="inlineStr"/>
-      <c r="AH93" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH93" t="inlineStr"/>
       <c r="AI93" t="inlineStr">
         <is>
           <t>22/10/2025</t>
@@ -7924,6 +8574,15 @@
       <c r="BA93" t="inlineStr"/>
       <c r="BB93" t="inlineStr"/>
       <c r="BC93" t="inlineStr"/>
+      <c r="BD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE93" t="inlineStr"/>
+      <c r="BF93" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7931,13 +8590,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
         <v>12</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D94" t="n">
         <v>9</v>
@@ -7951,21 +8610,21 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr">
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
         <is>
           <t>Enzo Crudeli Ongoing Winners</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr">
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
         <is>
           <t>2,170</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr"/>
@@ -7980,17 +8639,15 @@
       <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="inlineStr"/>
       <c r="AD94" t="inlineStr"/>
-      <c r="AE94" t="n">
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="n">
         <v>62.59118939180203</v>
       </c>
-      <c r="AF94" t="n">
+      <c r="AG94" t="n">
         <v>62.39168110918546</v>
       </c>
-      <c r="AG94" t="n">
+      <c r="AH94" t="n">
         <v>62.7906976744186</v>
-      </c>
-      <c r="AH94" t="n">
-        <v>2</v>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
@@ -8037,6 +8694,15 @@
       <c r="BA94" t="inlineStr"/>
       <c r="BB94" t="inlineStr"/>
       <c r="BC94" t="inlineStr"/>
+      <c r="BD94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE94" t="inlineStr"/>
+      <c r="BF94" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8044,13 +8710,13 @@
           <t>Cannington</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
         <v>12</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
       </c>
       <c r="D95" t="n">
         <v>9</v>
@@ -8064,21 +8730,21 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr">
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
         <is>
           <t>Glen Currie Ongoing Winners</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr">
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
         <is>
           <t>2,290</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr"/>
@@ -8096,9 +8762,7 @@
       <c r="AE95" t="inlineStr"/>
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="inlineStr"/>
-      <c r="AH95" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH95" t="inlineStr"/>
       <c r="AI95" t="inlineStr">
         <is>
           <t>5/11/2025</t>
@@ -8144,6 +8808,15 @@
       <c r="BA95" t="inlineStr"/>
       <c r="BB95" t="inlineStr"/>
       <c r="BC95" t="inlineStr"/>
+      <c r="BD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE95" t="inlineStr"/>
+      <c r="BF95" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8151,13 +8824,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
         <v>7</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D96" t="n">
         <v>1</v>
@@ -8195,9 +8868,7 @@
       <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="inlineStr"/>
-      <c r="AH96" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH96" t="inlineStr"/>
       <c r="AI96" t="inlineStr"/>
       <c r="AJ96" t="inlineStr"/>
       <c r="AK96" t="inlineStr"/>
@@ -8219,6 +8890,15 @@
       <c r="BA96" t="inlineStr"/>
       <c r="BB96" t="inlineStr"/>
       <c r="BC96" t="inlineStr"/>
+      <c r="BD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE96" t="inlineStr"/>
+      <c r="BF96" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8226,13 +8906,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
         <v>7</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D97" t="n">
         <v>1</v>
@@ -8270,9 +8950,7 @@
       <c r="AE97" t="inlineStr"/>
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="inlineStr"/>
-      <c r="AH97" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH97" t="inlineStr"/>
       <c r="AI97" t="inlineStr"/>
       <c r="AJ97" t="inlineStr"/>
       <c r="AK97" t="inlineStr"/>
@@ -8294,6 +8972,15 @@
       <c r="BA97" t="inlineStr"/>
       <c r="BB97" t="inlineStr"/>
       <c r="BC97" t="inlineStr"/>
+      <c r="BD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE97" t="inlineStr"/>
+      <c r="BF97" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8301,13 +8988,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
         <v>7</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D98" t="n">
         <v>1</v>
@@ -8345,9 +9032,7 @@
       <c r="AE98" t="inlineStr"/>
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="inlineStr"/>
-      <c r="AH98" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH98" t="inlineStr"/>
       <c r="AI98" t="inlineStr"/>
       <c r="AJ98" t="inlineStr"/>
       <c r="AK98" t="inlineStr"/>
@@ -8369,6 +9054,15 @@
       <c r="BA98" t="inlineStr"/>
       <c r="BB98" t="inlineStr"/>
       <c r="BC98" t="inlineStr"/>
+      <c r="BD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE98" t="inlineStr"/>
+      <c r="BF98" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8376,13 +9070,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
         <v>7</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D99" t="n">
         <v>1</v>
@@ -8420,9 +9114,7 @@
       <c r="AE99" t="inlineStr"/>
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="inlineStr"/>
-      <c r="AH99" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH99" t="inlineStr"/>
       <c r="AI99" t="inlineStr"/>
       <c r="AJ99" t="inlineStr"/>
       <c r="AK99" t="inlineStr"/>
@@ -8444,6 +9136,15 @@
       <c r="BA99" t="inlineStr"/>
       <c r="BB99" t="inlineStr"/>
       <c r="BC99" t="inlineStr"/>
+      <c r="BD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE99" t="inlineStr"/>
+      <c r="BF99" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8451,13 +9152,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
         <v>7</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D100" t="n">
         <v>1</v>
@@ -8495,9 +9196,7 @@
       <c r="AE100" t="inlineStr"/>
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="inlineStr"/>
-      <c r="AH100" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH100" t="inlineStr"/>
       <c r="AI100" t="inlineStr"/>
       <c r="AJ100" t="inlineStr"/>
       <c r="AK100" t="inlineStr"/>
@@ -8519,6 +9218,15 @@
       <c r="BA100" t="inlineStr"/>
       <c r="BB100" t="inlineStr"/>
       <c r="BC100" t="inlineStr"/>
+      <c r="BD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE100" t="inlineStr"/>
+      <c r="BF100" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8526,13 +9234,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
         <v>7</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D101" t="n">
         <v>1</v>
@@ -8570,9 +9278,7 @@
       <c r="AE101" t="inlineStr"/>
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="inlineStr"/>
-      <c r="AH101" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH101" t="inlineStr"/>
       <c r="AI101" t="inlineStr"/>
       <c r="AJ101" t="inlineStr"/>
       <c r="AK101" t="inlineStr"/>
@@ -8594,6 +9300,15 @@
       <c r="BA101" t="inlineStr"/>
       <c r="BB101" t="inlineStr"/>
       <c r="BC101" t="inlineStr"/>
+      <c r="BD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE101" t="inlineStr"/>
+      <c r="BF101" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8601,13 +9316,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B102" t="n">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
         <v>7</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -8645,9 +9360,7 @@
       <c r="AE102" t="inlineStr"/>
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="inlineStr"/>
-      <c r="AH102" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH102" t="inlineStr"/>
       <c r="AI102" t="inlineStr"/>
       <c r="AJ102" t="inlineStr"/>
       <c r="AK102" t="inlineStr"/>
@@ -8669,6 +9382,15 @@
       <c r="BA102" t="inlineStr"/>
       <c r="BB102" t="inlineStr"/>
       <c r="BC102" t="inlineStr"/>
+      <c r="BD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE102" t="inlineStr"/>
+      <c r="BF102" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8676,13 +9398,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
         <v>7</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D103" t="n">
         <v>1</v>
@@ -8720,9 +9442,7 @@
       <c r="AE103" t="inlineStr"/>
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="inlineStr"/>
-      <c r="AH103" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH103" t="inlineStr"/>
       <c r="AI103" t="inlineStr"/>
       <c r="AJ103" t="inlineStr"/>
       <c r="AK103" t="inlineStr"/>
@@ -8744,6 +9464,15 @@
       <c r="BA103" t="inlineStr"/>
       <c r="BB103" t="inlineStr"/>
       <c r="BC103" t="inlineStr"/>
+      <c r="BD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE103" t="inlineStr"/>
+      <c r="BF103" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8751,13 +9480,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
         <v>7</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D104" t="n">
         <v>1</v>
@@ -8795,9 +9524,7 @@
       <c r="AE104" t="inlineStr"/>
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="inlineStr"/>
-      <c r="AH104" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH104" t="inlineStr"/>
       <c r="AI104" t="inlineStr"/>
       <c r="AJ104" t="inlineStr"/>
       <c r="AK104" t="inlineStr"/>
@@ -8819,6 +9546,15 @@
       <c r="BA104" t="inlineStr"/>
       <c r="BB104" t="inlineStr"/>
       <c r="BC104" t="inlineStr"/>
+      <c r="BD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE104" t="inlineStr"/>
+      <c r="BF104" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8826,13 +9562,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
         <v>7</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D105" t="n">
         <v>1</v>
@@ -8870,9 +9606,7 @@
       <c r="AE105" t="inlineStr"/>
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="inlineStr"/>
-      <c r="AH105" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH105" t="inlineStr"/>
       <c r="AI105" t="inlineStr"/>
       <c r="AJ105" t="inlineStr"/>
       <c r="AK105" t="inlineStr"/>
@@ -8894,6 +9628,15 @@
       <c r="BA105" t="inlineStr"/>
       <c r="BB105" t="inlineStr"/>
       <c r="BC105" t="inlineStr"/>
+      <c r="BD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE105" t="inlineStr"/>
+      <c r="BF105" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8901,13 +9644,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B106" t="n">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
         <v>7</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D106" t="n">
         <v>2</v>
@@ -8945,9 +9688,7 @@
       <c r="AE106" t="inlineStr"/>
       <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="inlineStr"/>
-      <c r="AH106" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH106" t="inlineStr"/>
       <c r="AI106" t="inlineStr"/>
       <c r="AJ106" t="inlineStr"/>
       <c r="AK106" t="inlineStr"/>
@@ -8969,6 +9710,15 @@
       <c r="BA106" t="inlineStr"/>
       <c r="BB106" t="inlineStr"/>
       <c r="BC106" t="inlineStr"/>
+      <c r="BD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE106" t="inlineStr"/>
+      <c r="BF106" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8976,13 +9726,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B107" t="n">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
         <v>7</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D107" t="n">
         <v>2</v>
@@ -9020,9 +9770,7 @@
       <c r="AE107" t="inlineStr"/>
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="inlineStr"/>
-      <c r="AH107" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH107" t="inlineStr"/>
       <c r="AI107" t="inlineStr"/>
       <c r="AJ107" t="inlineStr"/>
       <c r="AK107" t="inlineStr"/>
@@ -9044,6 +9792,15 @@
       <c r="BA107" t="inlineStr"/>
       <c r="BB107" t="inlineStr"/>
       <c r="BC107" t="inlineStr"/>
+      <c r="BD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE107" t="inlineStr"/>
+      <c r="BF107" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9051,13 +9808,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
         <v>7</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D108" t="n">
         <v>2</v>
@@ -9095,9 +9852,7 @@
       <c r="AE108" t="inlineStr"/>
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="inlineStr"/>
-      <c r="AH108" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH108" t="inlineStr"/>
       <c r="AI108" t="inlineStr"/>
       <c r="AJ108" t="inlineStr"/>
       <c r="AK108" t="inlineStr"/>
@@ -9119,6 +9874,15 @@
       <c r="BA108" t="inlineStr"/>
       <c r="BB108" t="inlineStr"/>
       <c r="BC108" t="inlineStr"/>
+      <c r="BD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE108" t="inlineStr"/>
+      <c r="BF108" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9126,13 +9890,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
         <v>7</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D109" t="n">
         <v>2</v>
@@ -9170,9 +9934,7 @@
       <c r="AE109" t="inlineStr"/>
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="inlineStr"/>
-      <c r="AH109" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH109" t="inlineStr"/>
       <c r="AI109" t="inlineStr"/>
       <c r="AJ109" t="inlineStr"/>
       <c r="AK109" t="inlineStr"/>
@@ -9194,6 +9956,15 @@
       <c r="BA109" t="inlineStr"/>
       <c r="BB109" t="inlineStr"/>
       <c r="BC109" t="inlineStr"/>
+      <c r="BD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE109" t="inlineStr"/>
+      <c r="BF109" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9201,13 +9972,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
         <v>7</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D110" t="n">
         <v>2</v>
@@ -9245,9 +10016,7 @@
       <c r="AE110" t="inlineStr"/>
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="inlineStr"/>
-      <c r="AH110" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH110" t="inlineStr"/>
       <c r="AI110" t="inlineStr"/>
       <c r="AJ110" t="inlineStr"/>
       <c r="AK110" t="inlineStr"/>
@@ -9269,6 +10038,15 @@
       <c r="BA110" t="inlineStr"/>
       <c r="BB110" t="inlineStr"/>
       <c r="BC110" t="inlineStr"/>
+      <c r="BD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE110" t="inlineStr"/>
+      <c r="BF110" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9276,13 +10054,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
         <v>7</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D111" t="n">
         <v>2</v>
@@ -9320,9 +10098,7 @@
       <c r="AE111" t="inlineStr"/>
       <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="inlineStr"/>
-      <c r="AH111" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH111" t="inlineStr"/>
       <c r="AI111" t="inlineStr"/>
       <c r="AJ111" t="inlineStr"/>
       <c r="AK111" t="inlineStr"/>
@@ -9344,6 +10120,15 @@
       <c r="BA111" t="inlineStr"/>
       <c r="BB111" t="inlineStr"/>
       <c r="BC111" t="inlineStr"/>
+      <c r="BD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE111" t="inlineStr"/>
+      <c r="BF111" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9351,13 +10136,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
         <v>7</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D112" t="n">
         <v>2</v>
@@ -9395,9 +10180,7 @@
       <c r="AE112" t="inlineStr"/>
       <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="inlineStr"/>
-      <c r="AH112" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH112" t="inlineStr"/>
       <c r="AI112" t="inlineStr"/>
       <c r="AJ112" t="inlineStr"/>
       <c r="AK112" t="inlineStr"/>
@@ -9419,6 +10202,15 @@
       <c r="BA112" t="inlineStr"/>
       <c r="BB112" t="inlineStr"/>
       <c r="BC112" t="inlineStr"/>
+      <c r="BD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE112" t="inlineStr"/>
+      <c r="BF112" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9426,13 +10218,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
         <v>7</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D113" t="n">
         <v>2</v>
@@ -9470,9 +10262,7 @@
       <c r="AE113" t="inlineStr"/>
       <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="inlineStr"/>
-      <c r="AH113" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH113" t="inlineStr"/>
       <c r="AI113" t="inlineStr"/>
       <c r="AJ113" t="inlineStr"/>
       <c r="AK113" t="inlineStr"/>
@@ -9494,6 +10284,15 @@
       <c r="BA113" t="inlineStr"/>
       <c r="BB113" t="inlineStr"/>
       <c r="BC113" t="inlineStr"/>
+      <c r="BD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE113" t="inlineStr"/>
+      <c r="BF113" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9501,13 +10300,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
         <v>7</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D114" t="n">
         <v>2</v>
@@ -9545,9 +10344,7 @@
       <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="inlineStr"/>
-      <c r="AH114" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH114" t="inlineStr"/>
       <c r="AI114" t="inlineStr"/>
       <c r="AJ114" t="inlineStr"/>
       <c r="AK114" t="inlineStr"/>
@@ -9569,6 +10366,15 @@
       <c r="BA114" t="inlineStr"/>
       <c r="BB114" t="inlineStr"/>
       <c r="BC114" t="inlineStr"/>
+      <c r="BD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE114" t="inlineStr"/>
+      <c r="BF114" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9576,13 +10382,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B115" t="n">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
         <v>7</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D115" t="n">
         <v>2</v>
@@ -9620,9 +10426,7 @@
       <c r="AE115" t="inlineStr"/>
       <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="inlineStr"/>
-      <c r="AH115" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH115" t="inlineStr"/>
       <c r="AI115" t="inlineStr"/>
       <c r="AJ115" t="inlineStr"/>
       <c r="AK115" t="inlineStr"/>
@@ -9644,6 +10448,15 @@
       <c r="BA115" t="inlineStr"/>
       <c r="BB115" t="inlineStr"/>
       <c r="BC115" t="inlineStr"/>
+      <c r="BD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE115" t="inlineStr"/>
+      <c r="BF115" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9651,13 +10464,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B116" t="n">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
         <v>7</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D116" t="n">
         <v>2</v>
@@ -9695,9 +10508,7 @@
       <c r="AE116" t="inlineStr"/>
       <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="inlineStr"/>
-      <c r="AH116" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH116" t="inlineStr"/>
       <c r="AI116" t="inlineStr"/>
       <c r="AJ116" t="inlineStr"/>
       <c r="AK116" t="inlineStr"/>
@@ -9719,6 +10530,15 @@
       <c r="BA116" t="inlineStr"/>
       <c r="BB116" t="inlineStr"/>
       <c r="BC116" t="inlineStr"/>
+      <c r="BD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE116" t="inlineStr"/>
+      <c r="BF116" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9726,13 +10546,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B117" t="n">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
         <v>7</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D117" t="n">
         <v>3</v>
@@ -9770,9 +10590,7 @@
       <c r="AE117" t="inlineStr"/>
       <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="inlineStr"/>
-      <c r="AH117" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH117" t="inlineStr"/>
       <c r="AI117" t="inlineStr"/>
       <c r="AJ117" t="inlineStr"/>
       <c r="AK117" t="inlineStr"/>
@@ -9794,6 +10612,15 @@
       <c r="BA117" t="inlineStr"/>
       <c r="BB117" t="inlineStr"/>
       <c r="BC117" t="inlineStr"/>
+      <c r="BD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE117" t="inlineStr"/>
+      <c r="BF117" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9801,13 +10628,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B118" t="n">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
         <v>7</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D118" t="n">
         <v>3</v>
@@ -9845,9 +10672,7 @@
       <c r="AE118" t="inlineStr"/>
       <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="inlineStr"/>
-      <c r="AH118" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH118" t="inlineStr"/>
       <c r="AI118" t="inlineStr"/>
       <c r="AJ118" t="inlineStr"/>
       <c r="AK118" t="inlineStr"/>
@@ -9869,6 +10694,15 @@
       <c r="BA118" t="inlineStr"/>
       <c r="BB118" t="inlineStr"/>
       <c r="BC118" t="inlineStr"/>
+      <c r="BD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE118" t="inlineStr"/>
+      <c r="BF118" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9876,13 +10710,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B119" t="n">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
         <v>7</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D119" t="n">
         <v>3</v>
@@ -9920,9 +10754,7 @@
       <c r="AE119" t="inlineStr"/>
       <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="inlineStr"/>
-      <c r="AH119" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH119" t="inlineStr"/>
       <c r="AI119" t="inlineStr"/>
       <c r="AJ119" t="inlineStr"/>
       <c r="AK119" t="inlineStr"/>
@@ -9944,6 +10776,15 @@
       <c r="BA119" t="inlineStr"/>
       <c r="BB119" t="inlineStr"/>
       <c r="BC119" t="inlineStr"/>
+      <c r="BD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE119" t="inlineStr"/>
+      <c r="BF119" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9951,13 +10792,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B120" t="n">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
         <v>7</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D120" t="n">
         <v>3</v>
@@ -9995,9 +10836,7 @@
       <c r="AE120" t="inlineStr"/>
       <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="inlineStr"/>
-      <c r="AH120" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH120" t="inlineStr"/>
       <c r="AI120" t="inlineStr"/>
       <c r="AJ120" t="inlineStr"/>
       <c r="AK120" t="inlineStr"/>
@@ -10019,6 +10858,15 @@
       <c r="BA120" t="inlineStr"/>
       <c r="BB120" t="inlineStr"/>
       <c r="BC120" t="inlineStr"/>
+      <c r="BD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE120" t="inlineStr"/>
+      <c r="BF120" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10026,13 +10874,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B121" t="n">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
         <v>7</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D121" t="n">
         <v>3</v>
@@ -10070,9 +10918,7 @@
       <c r="AE121" t="inlineStr"/>
       <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="inlineStr"/>
-      <c r="AH121" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH121" t="inlineStr"/>
       <c r="AI121" t="inlineStr"/>
       <c r="AJ121" t="inlineStr"/>
       <c r="AK121" t="inlineStr"/>
@@ -10094,6 +10940,15 @@
       <c r="BA121" t="inlineStr"/>
       <c r="BB121" t="inlineStr"/>
       <c r="BC121" t="inlineStr"/>
+      <c r="BD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE121" t="inlineStr"/>
+      <c r="BF121" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10101,13 +10956,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B122" t="n">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
         <v>7</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D122" t="n">
         <v>3</v>
@@ -10145,9 +11000,7 @@
       <c r="AE122" t="inlineStr"/>
       <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="inlineStr"/>
-      <c r="AH122" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH122" t="inlineStr"/>
       <c r="AI122" t="inlineStr"/>
       <c r="AJ122" t="inlineStr"/>
       <c r="AK122" t="inlineStr"/>
@@ -10169,6 +11022,15 @@
       <c r="BA122" t="inlineStr"/>
       <c r="BB122" t="inlineStr"/>
       <c r="BC122" t="inlineStr"/>
+      <c r="BD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE122" t="inlineStr"/>
+      <c r="BF122" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10176,13 +11038,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B123" t="n">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
         <v>7</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D123" t="n">
         <v>3</v>
@@ -10220,9 +11082,7 @@
       <c r="AE123" t="inlineStr"/>
       <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="inlineStr"/>
-      <c r="AH123" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH123" t="inlineStr"/>
       <c r="AI123" t="inlineStr"/>
       <c r="AJ123" t="inlineStr"/>
       <c r="AK123" t="inlineStr"/>
@@ -10244,6 +11104,15 @@
       <c r="BA123" t="inlineStr"/>
       <c r="BB123" t="inlineStr"/>
       <c r="BC123" t="inlineStr"/>
+      <c r="BD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE123" t="inlineStr"/>
+      <c r="BF123" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10251,13 +11120,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B124" t="n">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
         <v>7</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D124" t="n">
         <v>3</v>
@@ -10295,9 +11164,7 @@
       <c r="AE124" t="inlineStr"/>
       <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="inlineStr"/>
-      <c r="AH124" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH124" t="inlineStr"/>
       <c r="AI124" t="inlineStr"/>
       <c r="AJ124" t="inlineStr"/>
       <c r="AK124" t="inlineStr"/>
@@ -10319,6 +11186,15 @@
       <c r="BA124" t="inlineStr"/>
       <c r="BB124" t="inlineStr"/>
       <c r="BC124" t="inlineStr"/>
+      <c r="BD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE124" t="inlineStr"/>
+      <c r="BF124" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10326,13 +11202,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B125" t="n">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
         <v>7</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D125" t="n">
         <v>3</v>
@@ -10370,9 +11246,7 @@
       <c r="AE125" t="inlineStr"/>
       <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="inlineStr"/>
-      <c r="AH125" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH125" t="inlineStr"/>
       <c r="AI125" t="inlineStr"/>
       <c r="AJ125" t="inlineStr"/>
       <c r="AK125" t="inlineStr"/>
@@ -10394,6 +11268,15 @@
       <c r="BA125" t="inlineStr"/>
       <c r="BB125" t="inlineStr"/>
       <c r="BC125" t="inlineStr"/>
+      <c r="BD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE125" t="inlineStr"/>
+      <c r="BF125" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10401,13 +11284,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
         <v>7</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D126" t="n">
         <v>3</v>
@@ -10445,9 +11328,7 @@
       <c r="AE126" t="inlineStr"/>
       <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="inlineStr"/>
-      <c r="AH126" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH126" t="inlineStr"/>
       <c r="AI126" t="inlineStr"/>
       <c r="AJ126" t="inlineStr"/>
       <c r="AK126" t="inlineStr"/>
@@ -10469,6 +11350,15 @@
       <c r="BA126" t="inlineStr"/>
       <c r="BB126" t="inlineStr"/>
       <c r="BC126" t="inlineStr"/>
+      <c r="BD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE126" t="inlineStr"/>
+      <c r="BF126" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10476,13 +11366,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
         <v>7</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D127" t="n">
         <v>4</v>
@@ -10520,9 +11410,7 @@
       <c r="AE127" t="inlineStr"/>
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="inlineStr"/>
-      <c r="AH127" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH127" t="inlineStr"/>
       <c r="AI127" t="inlineStr"/>
       <c r="AJ127" t="inlineStr"/>
       <c r="AK127" t="inlineStr"/>
@@ -10544,6 +11432,15 @@
       <c r="BA127" t="inlineStr"/>
       <c r="BB127" t="inlineStr"/>
       <c r="BC127" t="inlineStr"/>
+      <c r="BD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE127" t="inlineStr"/>
+      <c r="BF127" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10551,13 +11448,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B128" t="n">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
         <v>7</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D128" t="n">
         <v>4</v>
@@ -10595,9 +11492,7 @@
       <c r="AE128" t="inlineStr"/>
       <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="inlineStr"/>
-      <c r="AH128" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH128" t="inlineStr"/>
       <c r="AI128" t="inlineStr"/>
       <c r="AJ128" t="inlineStr"/>
       <c r="AK128" t="inlineStr"/>
@@ -10619,6 +11514,15 @@
       <c r="BA128" t="inlineStr"/>
       <c r="BB128" t="inlineStr"/>
       <c r="BC128" t="inlineStr"/>
+      <c r="BD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE128" t="inlineStr"/>
+      <c r="BF128" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10626,13 +11530,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
         <v>7</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D129" t="n">
         <v>4</v>
@@ -10670,9 +11574,7 @@
       <c r="AE129" t="inlineStr"/>
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="inlineStr"/>
-      <c r="AH129" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH129" t="inlineStr"/>
       <c r="AI129" t="inlineStr"/>
       <c r="AJ129" t="inlineStr"/>
       <c r="AK129" t="inlineStr"/>
@@ -10694,6 +11596,15 @@
       <c r="BA129" t="inlineStr"/>
       <c r="BB129" t="inlineStr"/>
       <c r="BC129" t="inlineStr"/>
+      <c r="BD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE129" t="inlineStr"/>
+      <c r="BF129" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10701,13 +11612,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B130" t="n">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
         <v>7</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D130" t="n">
         <v>4</v>
@@ -10745,9 +11656,7 @@
       <c r="AE130" t="inlineStr"/>
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="inlineStr"/>
-      <c r="AH130" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH130" t="inlineStr"/>
       <c r="AI130" t="inlineStr"/>
       <c r="AJ130" t="inlineStr"/>
       <c r="AK130" t="inlineStr"/>
@@ -10769,6 +11678,15 @@
       <c r="BA130" t="inlineStr"/>
       <c r="BB130" t="inlineStr"/>
       <c r="BC130" t="inlineStr"/>
+      <c r="BD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE130" t="inlineStr"/>
+      <c r="BF130" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10776,13 +11694,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
         <v>7</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D131" t="n">
         <v>4</v>
@@ -10820,9 +11738,7 @@
       <c r="AE131" t="inlineStr"/>
       <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="inlineStr"/>
-      <c r="AH131" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH131" t="inlineStr"/>
       <c r="AI131" t="inlineStr"/>
       <c r="AJ131" t="inlineStr"/>
       <c r="AK131" t="inlineStr"/>
@@ -10844,6 +11760,15 @@
       <c r="BA131" t="inlineStr"/>
       <c r="BB131" t="inlineStr"/>
       <c r="BC131" t="inlineStr"/>
+      <c r="BD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE131" t="inlineStr"/>
+      <c r="BF131" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10851,13 +11776,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
         <v>7</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D132" t="n">
         <v>4</v>
@@ -10895,9 +11820,7 @@
       <c r="AE132" t="inlineStr"/>
       <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="inlineStr"/>
-      <c r="AH132" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH132" t="inlineStr"/>
       <c r="AI132" t="inlineStr"/>
       <c r="AJ132" t="inlineStr"/>
       <c r="AK132" t="inlineStr"/>
@@ -10919,6 +11842,15 @@
       <c r="BA132" t="inlineStr"/>
       <c r="BB132" t="inlineStr"/>
       <c r="BC132" t="inlineStr"/>
+      <c r="BD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE132" t="inlineStr"/>
+      <c r="BF132" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10926,13 +11858,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B133" t="n">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
         <v>7</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D133" t="n">
         <v>4</v>
@@ -10970,9 +11902,7 @@
       <c r="AE133" t="inlineStr"/>
       <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="inlineStr"/>
-      <c r="AH133" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH133" t="inlineStr"/>
       <c r="AI133" t="inlineStr"/>
       <c r="AJ133" t="inlineStr"/>
       <c r="AK133" t="inlineStr"/>
@@ -10994,6 +11924,15 @@
       <c r="BA133" t="inlineStr"/>
       <c r="BB133" t="inlineStr"/>
       <c r="BC133" t="inlineStr"/>
+      <c r="BD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE133" t="inlineStr"/>
+      <c r="BF133" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11001,13 +11940,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
         <v>7</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D134" t="n">
         <v>4</v>
@@ -11045,9 +11984,7 @@
       <c r="AE134" t="inlineStr"/>
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="inlineStr"/>
-      <c r="AH134" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH134" t="inlineStr"/>
       <c r="AI134" t="inlineStr"/>
       <c r="AJ134" t="inlineStr"/>
       <c r="AK134" t="inlineStr"/>
@@ -11069,6 +12006,15 @@
       <c r="BA134" t="inlineStr"/>
       <c r="BB134" t="inlineStr"/>
       <c r="BC134" t="inlineStr"/>
+      <c r="BD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE134" t="inlineStr"/>
+      <c r="BF134" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11076,13 +12022,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
         <v>7</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D135" t="n">
         <v>4</v>
@@ -11120,9 +12066,7 @@
       <c r="AE135" t="inlineStr"/>
       <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="inlineStr"/>
-      <c r="AH135" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH135" t="inlineStr"/>
       <c r="AI135" t="inlineStr"/>
       <c r="AJ135" t="inlineStr"/>
       <c r="AK135" t="inlineStr"/>
@@ -11144,6 +12088,15 @@
       <c r="BA135" t="inlineStr"/>
       <c r="BB135" t="inlineStr"/>
       <c r="BC135" t="inlineStr"/>
+      <c r="BD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE135" t="inlineStr"/>
+      <c r="BF135" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11151,13 +12104,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
         <v>7</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D136" t="n">
         <v>4</v>
@@ -11195,9 +12148,7 @@
       <c r="AE136" t="inlineStr"/>
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="inlineStr"/>
-      <c r="AH136" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH136" t="inlineStr"/>
       <c r="AI136" t="inlineStr"/>
       <c r="AJ136" t="inlineStr"/>
       <c r="AK136" t="inlineStr"/>
@@ -11219,6 +12170,15 @@
       <c r="BA136" t="inlineStr"/>
       <c r="BB136" t="inlineStr"/>
       <c r="BC136" t="inlineStr"/>
+      <c r="BD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE136" t="inlineStr"/>
+      <c r="BF136" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11226,13 +12186,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
         <v>7</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D137" t="n">
         <v>5</v>
@@ -11270,9 +12230,7 @@
       <c r="AE137" t="inlineStr"/>
       <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="inlineStr"/>
-      <c r="AH137" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH137" t="inlineStr"/>
       <c r="AI137" t="inlineStr"/>
       <c r="AJ137" t="inlineStr"/>
       <c r="AK137" t="inlineStr"/>
@@ -11294,6 +12252,15 @@
       <c r="BA137" t="inlineStr"/>
       <c r="BB137" t="inlineStr"/>
       <c r="BC137" t="inlineStr"/>
+      <c r="BD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE137" t="inlineStr"/>
+      <c r="BF137" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11301,13 +12268,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B138" t="n">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
         <v>7</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D138" t="n">
         <v>5</v>
@@ -11345,9 +12312,7 @@
       <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="inlineStr"/>
-      <c r="AH138" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH138" t="inlineStr"/>
       <c r="AI138" t="inlineStr"/>
       <c r="AJ138" t="inlineStr"/>
       <c r="AK138" t="inlineStr"/>
@@ -11369,6 +12334,15 @@
       <c r="BA138" t="inlineStr"/>
       <c r="BB138" t="inlineStr"/>
       <c r="BC138" t="inlineStr"/>
+      <c r="BD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE138" t="inlineStr"/>
+      <c r="BF138" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11376,13 +12350,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B139" t="n">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
         <v>7</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D139" t="n">
         <v>5</v>
@@ -11420,9 +12394,7 @@
       <c r="AE139" t="inlineStr"/>
       <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="inlineStr"/>
-      <c r="AH139" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH139" t="inlineStr"/>
       <c r="AI139" t="inlineStr"/>
       <c r="AJ139" t="inlineStr"/>
       <c r="AK139" t="inlineStr"/>
@@ -11444,6 +12416,15 @@
       <c r="BA139" t="inlineStr"/>
       <c r="BB139" t="inlineStr"/>
       <c r="BC139" t="inlineStr"/>
+      <c r="BD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE139" t="inlineStr"/>
+      <c r="BF139" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11451,13 +12432,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B140" t="n">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
         <v>7</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D140" t="n">
         <v>5</v>
@@ -11495,9 +12476,7 @@
       <c r="AE140" t="inlineStr"/>
       <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="inlineStr"/>
-      <c r="AH140" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH140" t="inlineStr"/>
       <c r="AI140" t="inlineStr"/>
       <c r="AJ140" t="inlineStr"/>
       <c r="AK140" t="inlineStr"/>
@@ -11519,6 +12498,15 @@
       <c r="BA140" t="inlineStr"/>
       <c r="BB140" t="inlineStr"/>
       <c r="BC140" t="inlineStr"/>
+      <c r="BD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE140" t="inlineStr"/>
+      <c r="BF140" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11526,13 +12514,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B141" t="n">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
         <v>7</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D141" t="n">
         <v>5</v>
@@ -11570,9 +12558,7 @@
       <c r="AE141" t="inlineStr"/>
       <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="inlineStr"/>
-      <c r="AH141" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH141" t="inlineStr"/>
       <c r="AI141" t="inlineStr"/>
       <c r="AJ141" t="inlineStr"/>
       <c r="AK141" t="inlineStr"/>
@@ -11594,6 +12580,15 @@
       <c r="BA141" t="inlineStr"/>
       <c r="BB141" t="inlineStr"/>
       <c r="BC141" t="inlineStr"/>
+      <c r="BD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE141" t="inlineStr"/>
+      <c r="BF141" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11601,13 +12596,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B142" t="n">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
         <v>7</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D142" t="n">
         <v>5</v>
@@ -11645,9 +12640,7 @@
       <c r="AE142" t="inlineStr"/>
       <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="inlineStr"/>
-      <c r="AH142" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH142" t="inlineStr"/>
       <c r="AI142" t="inlineStr">
         <is>
           <t>4/11/2025</t>
@@ -11693,6 +12686,15 @@
       <c r="BA142" t="inlineStr"/>
       <c r="BB142" t="inlineStr"/>
       <c r="BC142" t="inlineStr"/>
+      <c r="BD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE142" t="inlineStr"/>
+      <c r="BF142" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11700,13 +12702,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B143" t="n">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
         <v>7</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D143" t="n">
         <v>5</v>
@@ -11744,9 +12746,7 @@
       <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="inlineStr"/>
-      <c r="AH143" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH143" t="inlineStr"/>
       <c r="AI143" t="inlineStr"/>
       <c r="AJ143" t="inlineStr"/>
       <c r="AK143" t="inlineStr"/>
@@ -11768,6 +12768,15 @@
       <c r="BA143" t="inlineStr"/>
       <c r="BB143" t="inlineStr"/>
       <c r="BC143" t="inlineStr"/>
+      <c r="BD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE143" t="inlineStr"/>
+      <c r="BF143" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11775,13 +12784,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B144" t="n">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
         <v>7</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D144" t="n">
         <v>5</v>
@@ -11819,9 +12828,7 @@
       <c r="AE144" t="inlineStr"/>
       <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="inlineStr"/>
-      <c r="AH144" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH144" t="inlineStr"/>
       <c r="AI144" t="inlineStr"/>
       <c r="AJ144" t="inlineStr"/>
       <c r="AK144" t="inlineStr"/>
@@ -11843,6 +12850,15 @@
       <c r="BA144" t="inlineStr"/>
       <c r="BB144" t="inlineStr"/>
       <c r="BC144" t="inlineStr"/>
+      <c r="BD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE144" t="inlineStr"/>
+      <c r="BF144" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11850,13 +12866,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B145" t="n">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
         <v>7</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D145" t="n">
         <v>5</v>
@@ -11894,9 +12910,7 @@
       <c r="AE145" t="inlineStr"/>
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="inlineStr"/>
-      <c r="AH145" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH145" t="inlineStr"/>
       <c r="AI145" t="inlineStr"/>
       <c r="AJ145" t="inlineStr"/>
       <c r="AK145" t="inlineStr"/>
@@ -11918,6 +12932,15 @@
       <c r="BA145" t="inlineStr"/>
       <c r="BB145" t="inlineStr"/>
       <c r="BC145" t="inlineStr"/>
+      <c r="BD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE145" t="inlineStr"/>
+      <c r="BF145" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11925,13 +12948,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B146" t="n">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
         <v>7</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D146" t="n">
         <v>5</v>
@@ -11969,9 +12992,7 @@
       <c r="AE146" t="inlineStr"/>
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="inlineStr"/>
-      <c r="AH146" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH146" t="inlineStr"/>
       <c r="AI146" t="inlineStr"/>
       <c r="AJ146" t="inlineStr"/>
       <c r="AK146" t="inlineStr"/>
@@ -11993,6 +13014,15 @@
       <c r="BA146" t="inlineStr"/>
       <c r="BB146" t="inlineStr"/>
       <c r="BC146" t="inlineStr"/>
+      <c r="BD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE146" t="inlineStr"/>
+      <c r="BF146" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12000,13 +13030,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B147" t="n">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
         <v>7</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D147" t="n">
         <v>5</v>
@@ -12044,9 +13074,7 @@
       <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="inlineStr"/>
-      <c r="AH147" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH147" t="inlineStr"/>
       <c r="AI147" t="inlineStr"/>
       <c r="AJ147" t="inlineStr"/>
       <c r="AK147" t="inlineStr"/>
@@ -12068,6 +13096,15 @@
       <c r="BA147" t="inlineStr"/>
       <c r="BB147" t="inlineStr"/>
       <c r="BC147" t="inlineStr"/>
+      <c r="BD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE147" t="inlineStr"/>
+      <c r="BF147" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12075,13 +13112,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B148" t="n">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
         <v>7</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D148" t="n">
         <v>6</v>
@@ -12119,9 +13156,7 @@
       <c r="AE148" t="inlineStr"/>
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="inlineStr"/>
-      <c r="AH148" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH148" t="inlineStr"/>
       <c r="AI148" t="inlineStr"/>
       <c r="AJ148" t="inlineStr"/>
       <c r="AK148" t="inlineStr"/>
@@ -12143,6 +13178,15 @@
       <c r="BA148" t="inlineStr"/>
       <c r="BB148" t="inlineStr"/>
       <c r="BC148" t="inlineStr"/>
+      <c r="BD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE148" t="inlineStr"/>
+      <c r="BF148" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12150,13 +13194,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B149" t="n">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
         <v>7</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D149" t="n">
         <v>6</v>
@@ -12194,9 +13238,7 @@
       <c r="AE149" t="inlineStr"/>
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="inlineStr"/>
-      <c r="AH149" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH149" t="inlineStr"/>
       <c r="AI149" t="inlineStr"/>
       <c r="AJ149" t="inlineStr"/>
       <c r="AK149" t="inlineStr"/>
@@ -12218,6 +13260,15 @@
       <c r="BA149" t="inlineStr"/>
       <c r="BB149" t="inlineStr"/>
       <c r="BC149" t="inlineStr"/>
+      <c r="BD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE149" t="inlineStr"/>
+      <c r="BF149" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12225,13 +13276,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B150" t="n">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
         <v>7</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D150" t="n">
         <v>6</v>
@@ -12269,9 +13320,7 @@
       <c r="AE150" t="inlineStr"/>
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="inlineStr"/>
-      <c r="AH150" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH150" t="inlineStr"/>
       <c r="AI150" t="inlineStr"/>
       <c r="AJ150" t="inlineStr"/>
       <c r="AK150" t="inlineStr"/>
@@ -12293,6 +13342,15 @@
       <c r="BA150" t="inlineStr"/>
       <c r="BB150" t="inlineStr"/>
       <c r="BC150" t="inlineStr"/>
+      <c r="BD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE150" t="inlineStr"/>
+      <c r="BF150" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12300,13 +13358,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B151" t="n">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
         <v>7</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D151" t="n">
         <v>6</v>
@@ -12344,9 +13402,7 @@
       <c r="AE151" t="inlineStr"/>
       <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="inlineStr"/>
-      <c r="AH151" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH151" t="inlineStr"/>
       <c r="AI151" t="inlineStr"/>
       <c r="AJ151" t="inlineStr"/>
       <c r="AK151" t="inlineStr"/>
@@ -12368,6 +13424,15 @@
       <c r="BA151" t="inlineStr"/>
       <c r="BB151" t="inlineStr"/>
       <c r="BC151" t="inlineStr"/>
+      <c r="BD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE151" t="inlineStr"/>
+      <c r="BF151" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12375,13 +13440,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B152" t="n">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
         <v>7</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D152" t="n">
         <v>6</v>
@@ -12419,9 +13484,7 @@
       <c r="AE152" t="inlineStr"/>
       <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="inlineStr"/>
-      <c r="AH152" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH152" t="inlineStr"/>
       <c r="AI152" t="inlineStr"/>
       <c r="AJ152" t="inlineStr"/>
       <c r="AK152" t="inlineStr"/>
@@ -12443,6 +13506,15 @@
       <c r="BA152" t="inlineStr"/>
       <c r="BB152" t="inlineStr"/>
       <c r="BC152" t="inlineStr"/>
+      <c r="BD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE152" t="inlineStr"/>
+      <c r="BF152" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12450,13 +13522,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B153" t="n">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
         <v>7</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D153" t="n">
         <v>6</v>
@@ -12494,9 +13566,7 @@
       <c r="AE153" t="inlineStr"/>
       <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="inlineStr"/>
-      <c r="AH153" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH153" t="inlineStr"/>
       <c r="AI153" t="inlineStr"/>
       <c r="AJ153" t="inlineStr"/>
       <c r="AK153" t="inlineStr"/>
@@ -12518,6 +13588,15 @@
       <c r="BA153" t="inlineStr"/>
       <c r="BB153" t="inlineStr"/>
       <c r="BC153" t="inlineStr"/>
+      <c r="BD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE153" t="inlineStr"/>
+      <c r="BF153" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12525,13 +13604,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B154" t="n">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
         <v>7</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D154" t="n">
         <v>6</v>
@@ -12569,9 +13648,7 @@
       <c r="AE154" t="inlineStr"/>
       <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="inlineStr"/>
-      <c r="AH154" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH154" t="inlineStr"/>
       <c r="AI154" t="inlineStr"/>
       <c r="AJ154" t="inlineStr"/>
       <c r="AK154" t="inlineStr"/>
@@ -12593,6 +13670,15 @@
       <c r="BA154" t="inlineStr"/>
       <c r="BB154" t="inlineStr"/>
       <c r="BC154" t="inlineStr"/>
+      <c r="BD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE154" t="inlineStr"/>
+      <c r="BF154" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12600,13 +13686,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B155" t="n">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
         <v>7</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D155" t="n">
         <v>6</v>
@@ -12644,9 +13730,7 @@
       <c r="AE155" t="inlineStr"/>
       <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="inlineStr"/>
-      <c r="AH155" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH155" t="inlineStr"/>
       <c r="AI155" t="inlineStr"/>
       <c r="AJ155" t="inlineStr"/>
       <c r="AK155" t="inlineStr"/>
@@ -12668,6 +13752,15 @@
       <c r="BA155" t="inlineStr"/>
       <c r="BB155" t="inlineStr"/>
       <c r="BC155" t="inlineStr"/>
+      <c r="BD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE155" t="inlineStr"/>
+      <c r="BF155" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12675,13 +13768,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B156" t="n">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
         <v>7</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D156" t="n">
         <v>6</v>
@@ -12719,9 +13812,7 @@
       <c r="AE156" t="inlineStr"/>
       <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="inlineStr"/>
-      <c r="AH156" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH156" t="inlineStr"/>
       <c r="AI156" t="inlineStr"/>
       <c r="AJ156" t="inlineStr"/>
       <c r="AK156" t="inlineStr"/>
@@ -12743,6 +13834,15 @@
       <c r="BA156" t="inlineStr"/>
       <c r="BB156" t="inlineStr"/>
       <c r="BC156" t="inlineStr"/>
+      <c r="BD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE156" t="inlineStr"/>
+      <c r="BF156" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12750,13 +13850,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B157" t="n">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
         <v>7</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D157" t="n">
         <v>6</v>
@@ -12794,9 +13894,7 @@
       <c r="AE157" t="inlineStr"/>
       <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="inlineStr"/>
-      <c r="AH157" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH157" t="inlineStr"/>
       <c r="AI157" t="inlineStr"/>
       <c r="AJ157" t="inlineStr"/>
       <c r="AK157" t="inlineStr"/>
@@ -12818,6 +13916,15 @@
       <c r="BA157" t="inlineStr"/>
       <c r="BB157" t="inlineStr"/>
       <c r="BC157" t="inlineStr"/>
+      <c r="BD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE157" t="inlineStr"/>
+      <c r="BF157" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12825,13 +13932,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B158" t="n">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
         <v>7</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D158" t="n">
         <v>7</v>
@@ -12845,21 +13952,21 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr">
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
         <is>
           <t>Michael Rylands Ongoing Winners</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr">
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
         <is>
           <t>1,980</t>
         </is>
       </c>
-      <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr"/>
@@ -12877,9 +13984,7 @@
       <c r="AE158" t="inlineStr"/>
       <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="inlineStr"/>
-      <c r="AH158" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH158" t="inlineStr"/>
       <c r="AI158" t="inlineStr">
         <is>
           <t>2/10/2025</t>
@@ -12925,6 +14030,15 @@
       <c r="BA158" t="inlineStr"/>
       <c r="BB158" t="inlineStr"/>
       <c r="BC158" t="inlineStr"/>
+      <c r="BD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE158" t="inlineStr"/>
+      <c r="BF158" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -12932,13 +14046,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B159" t="n">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
         <v>7</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D159" t="n">
         <v>7</v>
@@ -12976,9 +14090,7 @@
       <c r="AE159" t="inlineStr"/>
       <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="inlineStr"/>
-      <c r="AH159" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH159" t="inlineStr"/>
       <c r="AI159" t="inlineStr"/>
       <c r="AJ159" t="inlineStr"/>
       <c r="AK159" t="inlineStr"/>
@@ -13000,6 +14112,15 @@
       <c r="BA159" t="inlineStr"/>
       <c r="BB159" t="inlineStr"/>
       <c r="BC159" t="inlineStr"/>
+      <c r="BD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE159" t="inlineStr"/>
+      <c r="BF159" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -13007,13 +14128,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B160" t="n">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
         <v>7</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D160" t="n">
         <v>7</v>
@@ -13051,9 +14172,7 @@
       <c r="AE160" t="inlineStr"/>
       <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="inlineStr"/>
-      <c r="AH160" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH160" t="inlineStr"/>
       <c r="AI160" t="inlineStr"/>
       <c r="AJ160" t="inlineStr"/>
       <c r="AK160" t="inlineStr"/>
@@ -13075,6 +14194,15 @@
       <c r="BA160" t="inlineStr"/>
       <c r="BB160" t="inlineStr"/>
       <c r="BC160" t="inlineStr"/>
+      <c r="BD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE160" t="inlineStr"/>
+      <c r="BF160" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13082,13 +14210,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B161" t="n">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
         <v>7</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D161" t="n">
         <v>7</v>
@@ -13126,9 +14254,7 @@
       <c r="AE161" t="inlineStr"/>
       <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="inlineStr"/>
-      <c r="AH161" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH161" t="inlineStr"/>
       <c r="AI161" t="inlineStr"/>
       <c r="AJ161" t="inlineStr"/>
       <c r="AK161" t="inlineStr"/>
@@ -13150,6 +14276,15 @@
       <c r="BA161" t="inlineStr"/>
       <c r="BB161" t="inlineStr"/>
       <c r="BC161" t="inlineStr"/>
+      <c r="BD161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE161" t="inlineStr"/>
+      <c r="BF161" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -13157,13 +14292,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B162" t="n">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
         <v>7</v>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D162" t="n">
         <v>7</v>
@@ -13201,9 +14336,7 @@
       <c r="AE162" t="inlineStr"/>
       <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="inlineStr"/>
-      <c r="AH162" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH162" t="inlineStr"/>
       <c r="AI162" t="inlineStr"/>
       <c r="AJ162" t="inlineStr"/>
       <c r="AK162" t="inlineStr"/>
@@ -13225,6 +14358,15 @@
       <c r="BA162" t="inlineStr"/>
       <c r="BB162" t="inlineStr"/>
       <c r="BC162" t="inlineStr"/>
+      <c r="BD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE162" t="inlineStr"/>
+      <c r="BF162" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -13232,13 +14374,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B163" t="n">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
         <v>7</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D163" t="n">
         <v>7</v>
@@ -13276,9 +14418,7 @@
       <c r="AE163" t="inlineStr"/>
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="inlineStr"/>
-      <c r="AH163" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH163" t="inlineStr"/>
       <c r="AI163" t="inlineStr"/>
       <c r="AJ163" t="inlineStr"/>
       <c r="AK163" t="inlineStr"/>
@@ -13300,6 +14440,15 @@
       <c r="BA163" t="inlineStr"/>
       <c r="BB163" t="inlineStr"/>
       <c r="BC163" t="inlineStr"/>
+      <c r="BD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE163" t="inlineStr"/>
+      <c r="BF163" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -13307,13 +14456,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B164" t="n">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
         <v>7</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D164" t="n">
         <v>7</v>
@@ -13327,21 +14476,21 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr">
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
         <is>
           <t>Christopher Halse Ongoing Winners</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr">
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
         <is>
           <t>5,250</t>
         </is>
       </c>
-      <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr"/>
@@ -13359,9 +14508,7 @@
       <c r="AE164" t="inlineStr"/>
       <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="inlineStr"/>
-      <c r="AH164" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH164" t="inlineStr"/>
       <c r="AI164" t="inlineStr">
         <is>
           <t>30/09/2025</t>
@@ -13407,6 +14554,15 @@
       <c r="BA164" t="inlineStr"/>
       <c r="BB164" t="inlineStr"/>
       <c r="BC164" t="inlineStr"/>
+      <c r="BD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE164" t="inlineStr"/>
+      <c r="BF164" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -13414,13 +14570,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B165" t="n">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
         <v>7</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D165" t="n">
         <v>7</v>
@@ -13458,9 +14614,7 @@
       <c r="AE165" t="inlineStr"/>
       <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="inlineStr"/>
-      <c r="AH165" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH165" t="inlineStr"/>
       <c r="AI165" t="inlineStr"/>
       <c r="AJ165" t="inlineStr"/>
       <c r="AK165" t="inlineStr"/>
@@ -13482,6 +14636,15 @@
       <c r="BA165" t="inlineStr"/>
       <c r="BB165" t="inlineStr"/>
       <c r="BC165" t="inlineStr"/>
+      <c r="BD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE165" t="inlineStr"/>
+      <c r="BF165" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -13489,13 +14652,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B166" t="n">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
         <v>7</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D166" t="n">
         <v>7</v>
@@ -13533,9 +14696,7 @@
       <c r="AE166" t="inlineStr"/>
       <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="inlineStr"/>
-      <c r="AH166" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH166" t="inlineStr"/>
       <c r="AI166" t="inlineStr"/>
       <c r="AJ166" t="inlineStr"/>
       <c r="AK166" t="inlineStr"/>
@@ -13557,6 +14718,15 @@
       <c r="BA166" t="inlineStr"/>
       <c r="BB166" t="inlineStr"/>
       <c r="BC166" t="inlineStr"/>
+      <c r="BD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE166" t="inlineStr"/>
+      <c r="BF166" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -13564,13 +14734,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B167" t="n">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
         <v>7</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D167" t="n">
         <v>7</v>
@@ -13608,9 +14778,7 @@
       <c r="AE167" t="inlineStr"/>
       <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="inlineStr"/>
-      <c r="AH167" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH167" t="inlineStr"/>
       <c r="AI167" t="inlineStr"/>
       <c r="AJ167" t="inlineStr"/>
       <c r="AK167" t="inlineStr"/>
@@ -13632,6 +14800,15 @@
       <c r="BA167" t="inlineStr"/>
       <c r="BB167" t="inlineStr"/>
       <c r="BC167" t="inlineStr"/>
+      <c r="BD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE167" t="inlineStr"/>
+      <c r="BF167" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -13639,13 +14816,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B168" t="n">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
         <v>7</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D168" t="n">
         <v>7</v>
@@ -13683,9 +14860,7 @@
       <c r="AE168" t="inlineStr"/>
       <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="inlineStr"/>
-      <c r="AH168" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH168" t="inlineStr"/>
       <c r="AI168" t="inlineStr"/>
       <c r="AJ168" t="inlineStr"/>
       <c r="AK168" t="inlineStr"/>
@@ -13707,6 +14882,15 @@
       <c r="BA168" t="inlineStr"/>
       <c r="BB168" t="inlineStr"/>
       <c r="BC168" t="inlineStr"/>
+      <c r="BD168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE168" t="inlineStr"/>
+      <c r="BF168" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -13714,13 +14898,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B169" t="n">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
         <v>7</v>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D169" t="n">
         <v>8</v>
@@ -13758,9 +14942,7 @@
       <c r="AE169" t="inlineStr"/>
       <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="inlineStr"/>
-      <c r="AH169" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH169" t="inlineStr"/>
       <c r="AI169" t="inlineStr"/>
       <c r="AJ169" t="inlineStr"/>
       <c r="AK169" t="inlineStr"/>
@@ -13782,6 +14964,15 @@
       <c r="BA169" t="inlineStr"/>
       <c r="BB169" t="inlineStr"/>
       <c r="BC169" t="inlineStr"/>
+      <c r="BD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE169" t="inlineStr"/>
+      <c r="BF169" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13789,13 +14980,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B170" t="n">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
         <v>7</v>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D170" t="n">
         <v>8</v>
@@ -13833,9 +15024,7 @@
       <c r="AE170" t="inlineStr"/>
       <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="inlineStr"/>
-      <c r="AH170" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH170" t="inlineStr"/>
       <c r="AI170" t="inlineStr"/>
       <c r="AJ170" t="inlineStr"/>
       <c r="AK170" t="inlineStr"/>
@@ -13857,6 +15046,15 @@
       <c r="BA170" t="inlineStr"/>
       <c r="BB170" t="inlineStr"/>
       <c r="BC170" t="inlineStr"/>
+      <c r="BD170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE170" t="inlineStr"/>
+      <c r="BF170" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -13864,13 +15062,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B171" t="n">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
         <v>7</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D171" t="n">
         <v>8</v>
@@ -13884,21 +15082,21 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr">
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
         <is>
           <t>Andrew McLaren Ongoing Winners</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr">
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
         <is>
           <t>2,070</t>
         </is>
       </c>
-      <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr"/>
@@ -13916,9 +15114,7 @@
       <c r="AE171" t="inlineStr"/>
       <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="inlineStr"/>
-      <c r="AH171" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH171" t="inlineStr"/>
       <c r="AI171" t="inlineStr">
         <is>
           <t>30/09/2025</t>
@@ -13964,6 +15160,15 @@
       <c r="BA171" t="inlineStr"/>
       <c r="BB171" t="inlineStr"/>
       <c r="BC171" t="inlineStr"/>
+      <c r="BD171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE171" t="inlineStr"/>
+      <c r="BF171" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13971,13 +15176,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B172" t="n">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
         <v>7</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D172" t="n">
         <v>8</v>
@@ -13991,21 +15196,21 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr">
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
         <is>
           <t>Paul Kaltsis Ongoing Winners</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr">
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
         <is>
           <t>2,070</t>
         </is>
       </c>
-      <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr"/>
@@ -14023,9 +15228,7 @@
       <c r="AE172" t="inlineStr"/>
       <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="inlineStr"/>
-      <c r="AH172" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH172" t="inlineStr"/>
       <c r="AI172" t="inlineStr">
         <is>
           <t>30/09/2025</t>
@@ -14071,6 +15274,15 @@
       <c r="BA172" t="inlineStr"/>
       <c r="BB172" t="inlineStr"/>
       <c r="BC172" t="inlineStr"/>
+      <c r="BD172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE172" t="inlineStr"/>
+      <c r="BF172" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -14078,13 +15290,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B173" t="n">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
         <v>7</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D173" t="n">
         <v>8</v>
@@ -14098,21 +15310,21 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr">
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
         <is>
           <t>Colleen Pierson Ongoing Winners</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr">
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
         <is>
           <t>4,470</t>
         </is>
       </c>
-      <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr"/>
@@ -14130,9 +15342,7 @@
       <c r="AE173" t="inlineStr"/>
       <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="inlineStr"/>
-      <c r="AH173" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH173" t="inlineStr"/>
       <c r="AI173" t="inlineStr">
         <is>
           <t>30/09/2025</t>
@@ -14178,6 +15388,15 @@
       <c r="BA173" t="inlineStr"/>
       <c r="BB173" t="inlineStr"/>
       <c r="BC173" t="inlineStr"/>
+      <c r="BD173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE173" t="inlineStr"/>
+      <c r="BF173" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -14185,13 +15404,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B174" t="n">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
         <v>7</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D174" t="n">
         <v>8</v>
@@ -14205,21 +15424,21 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr">
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
         <is>
           <t>Michael Rylands Ongoing Winners</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr">
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
         <is>
           <t>5,250</t>
         </is>
       </c>
-      <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr"/>
@@ -14234,17 +15453,15 @@
       <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="inlineStr"/>
       <c r="AD174" t="inlineStr"/>
-      <c r="AE174" t="n">
+      <c r="AE174" t="inlineStr"/>
+      <c r="AF174" t="n">
         <v>62.64857887551197</v>
       </c>
-      <c r="AF174" t="n">
+      <c r="AG174" t="n">
         <v>62.55430060816681</v>
       </c>
-      <c r="AG174" t="n">
+      <c r="AH174" t="n">
         <v>62.74285714285714</v>
-      </c>
-      <c r="AH174" t="n">
-        <v>2</v>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
@@ -14291,6 +15508,15 @@
       <c r="BA174" t="inlineStr"/>
       <c r="BB174" t="inlineStr"/>
       <c r="BC174" t="inlineStr"/>
+      <c r="BD174" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE174" t="inlineStr"/>
+      <c r="BF174" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -14298,13 +15524,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B175" t="n">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
         <v>7</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D175" t="n">
         <v>8</v>
@@ -14318,21 +15544,21 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr">
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
         <is>
           <t>Kellie Buckwell Ongoing Winners</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr">
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
         <is>
           <t>10,050</t>
         </is>
       </c>
-      <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr"/>
@@ -14350,9 +15576,7 @@
       <c r="AE175" t="inlineStr"/>
       <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="inlineStr"/>
-      <c r="AH175" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH175" t="inlineStr"/>
       <c r="AI175" t="inlineStr">
         <is>
           <t>29/09/2025</t>
@@ -14398,6 +15622,15 @@
       <c r="BA175" t="inlineStr"/>
       <c r="BB175" t="inlineStr"/>
       <c r="BC175" t="inlineStr"/>
+      <c r="BD175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE175" t="inlineStr"/>
+      <c r="BF175" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -14405,13 +15638,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B176" t="n">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
         <v>7</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D176" t="n">
         <v>8</v>
@@ -14449,9 +15682,7 @@
       <c r="AE176" t="inlineStr"/>
       <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="inlineStr"/>
-      <c r="AH176" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH176" t="inlineStr"/>
       <c r="AI176" t="inlineStr"/>
       <c r="AJ176" t="inlineStr"/>
       <c r="AK176" t="inlineStr"/>
@@ -14473,6 +15704,15 @@
       <c r="BA176" t="inlineStr"/>
       <c r="BB176" t="inlineStr"/>
       <c r="BC176" t="inlineStr"/>
+      <c r="BD176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE176" t="inlineStr"/>
+      <c r="BF176" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -14480,13 +15720,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B177" t="n">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
         <v>7</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D177" t="n">
         <v>8</v>
@@ -14500,21 +15740,21 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr">
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
         <is>
           <t>Glen Currie Ongoing Winners</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr">
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
         <is>
           <t>2,290</t>
         </is>
       </c>
-      <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr"/>
@@ -14529,9 +15769,7 @@
       <c r="AB177" t="inlineStr"/>
       <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="inlineStr"/>
-      <c r="AE177" t="n">
-        <v>62.39168110918546</v>
-      </c>
+      <c r="AE177" t="inlineStr"/>
       <c r="AF177" t="n">
         <v>62.39168110918546</v>
       </c>
@@ -14539,7 +15777,7 @@
         <v>62.39168110918546</v>
       </c>
       <c r="AH177" t="n">
-        <v>1</v>
+        <v>62.39168110918546</v>
       </c>
       <c r="AI177" t="inlineStr">
         <is>
@@ -14586,6 +15824,15 @@
       <c r="BA177" t="inlineStr"/>
       <c r="BB177" t="inlineStr"/>
       <c r="BC177" t="inlineStr"/>
+      <c r="BD177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE177" t="inlineStr"/>
+      <c r="BF177" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -14593,13 +15840,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B178" t="n">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
         <v>7</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D178" t="n">
         <v>9</v>
@@ -14613,21 +15860,21 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr">
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
         <is>
           <t>Andrew McLaren Ongoing Winners</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr">
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
         <is>
           <t>4,250</t>
         </is>
       </c>
-      <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr"/>
@@ -14645,9 +15892,7 @@
       <c r="AE178" t="inlineStr"/>
       <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="inlineStr"/>
-      <c r="AH178" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH178" t="inlineStr"/>
       <c r="AI178" t="inlineStr">
         <is>
           <t>30/09/2025</t>
@@ -14693,6 +15938,15 @@
       <c r="BA178" t="inlineStr"/>
       <c r="BB178" t="inlineStr"/>
       <c r="BC178" t="inlineStr"/>
+      <c r="BD178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE178" t="inlineStr"/>
+      <c r="BF178" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -14700,13 +15954,13 @@
           <t>Mandurah</t>
         </is>
       </c>
-      <c r="B179" t="n">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
         <v>7</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
       </c>
       <c r="D179" t="n">
         <v>9</v>
@@ -14720,21 +15974,21 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr">
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
         <is>
           <t>Enzo Crudeli Ongoing Winners</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr">
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
         <is>
           <t>2,070</t>
         </is>
       </c>
-      <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr"/>
@@ -14749,17 +16003,15 @@
       <c r="AB179" t="inlineStr"/>
       <c r="AC179" t="inlineStr"/>
       <c r="AD179" t="inlineStr"/>
-      <c r="AE179" t="n">
+      <c r="AE179" t="inlineStr"/>
+      <c r="AF179" t="n">
         <v>62.59118939180203</v>
       </c>
-      <c r="AF179" t="n">
+      <c r="AG179" t="n">
         <v>62.39168110918546</v>
       </c>
-      <c r="AG179" t="n">
+      <c r="AH179" t="n">
         <v>62.7906976744186</v>
-      </c>
-      <c r="AH179" t="n">
-        <v>2</v>
       </c>
       <c r="AI179" t="inlineStr">
         <is>
@@ -14806,6 +16058,15 @@
       <c r="BA179" t="inlineStr"/>
       <c r="BB179" t="inlineStr"/>
       <c r="BC179" t="inlineStr"/>
+      <c r="BD179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE179" t="inlineStr"/>
+      <c r="BF179" t="inlineStr">
+        <is>
+          <t>2025-11-13T07:39:26</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/all_dogs_master.xlsx
+++ b/outputs/all_dogs_master.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="BF85" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="BF92" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="BF93" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -10864,7 +10864,7 @@
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11208,7 @@
       </c>
       <c r="BF123" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -11294,7 +11294,7 @@
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -12412,7 +12412,7 @@
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -12498,7 +12498,7 @@
       </c>
       <c r="BF138" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12584,7 @@
       </c>
       <c r="BF139" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="BF140" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="BF144" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -13100,7 +13100,7 @@
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -13358,7 +13358,7 @@
       </c>
       <c r="BF148" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="BF149" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -13702,7 +13702,7 @@
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -14218,7 +14218,7 @@
       </c>
       <c r="BF158" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="BF159" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="BF161" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="BF163" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="BF164" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="BF165" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="BF166" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -14992,7 +14992,7 @@
       </c>
       <c r="BF167" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15078,7 @@
       </c>
       <c r="BF168" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="BF169" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="BF170" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="BF171" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -15766,7 +15766,7 @@
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -15938,7 +15938,7 @@
       </c>
       <c r="BF178" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -16024,7 +16024,7 @@
       </c>
       <c r="BF179" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -16110,7 +16110,7 @@
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -16196,7 +16196,7 @@
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -16282,7 +16282,7 @@
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -16368,7 +16368,7 @@
       </c>
       <c r="BF183" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="BF184" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -16540,7 +16540,7 @@
       </c>
       <c r="BF185" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -16626,7 +16626,7 @@
       </c>
       <c r="BF186" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="BF187" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -16798,7 +16798,7 @@
       </c>
       <c r="BF188" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="BF189" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -16970,7 +16970,7 @@
       </c>
       <c r="BF190" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -17056,7 +17056,7 @@
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="BF192" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="BF193" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="BF194" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="BF195" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="BF196" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -17572,7 +17572,7 @@
       </c>
       <c r="BF197" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="BF198" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -17744,7 +17744,7 @@
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -17830,7 +17830,7 @@
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="BF202" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -18088,7 +18088,7 @@
       </c>
       <c r="BF203" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -18174,7 +18174,7 @@
       </c>
       <c r="BF204" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -18260,7 +18260,7 @@
       </c>
       <c r="BF205" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -18346,7 +18346,7 @@
       </c>
       <c r="BF206" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="BF207" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -18604,7 +18604,7 @@
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -18690,7 +18690,7 @@
       </c>
       <c r="BF210" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -18776,7 +18776,7 @@
       </c>
       <c r="BF211" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -18862,7 +18862,7 @@
       </c>
       <c r="BF212" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="BF213" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="BF214" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -19120,7 +19120,7 @@
       </c>
       <c r="BF215" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -19206,7 +19206,7 @@
       </c>
       <c r="BF216" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -19292,7 +19292,7 @@
       </c>
       <c r="BF217" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -19378,7 +19378,7 @@
       </c>
       <c r="BF218" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -19464,7 +19464,7 @@
       </c>
       <c r="BF219" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -19550,7 +19550,7 @@
       </c>
       <c r="BF220" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -19636,7 +19636,7 @@
       </c>
       <c r="BF221" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="BF222" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="BF225" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -20066,7 +20066,7 @@
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="BF228" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -20324,7 +20324,7 @@
       </c>
       <c r="BF229" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -20668,7 +20668,7 @@
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="BF234" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -20840,7 +20840,7 @@
       </c>
       <c r="BF235" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -20926,7 +20926,7 @@
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -21012,7 +21012,7 @@
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -21270,7 +21270,7 @@
       </c>
       <c r="BF240" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -21356,7 +21356,7 @@
       </c>
       <c r="BF241" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="BF242" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -21528,7 +21528,7 @@
       </c>
       <c r="BF243" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -21614,7 +21614,7 @@
       </c>
       <c r="BF244" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -21700,7 +21700,7 @@
       </c>
       <c r="BF245" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="BF246" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BF247" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -21958,7 +21958,7 @@
       </c>
       <c r="BF248" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -22044,7 +22044,7 @@
       </c>
       <c r="BF249" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22130,7 @@
       </c>
       <c r="BF250" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -22216,7 +22216,7 @@
       </c>
       <c r="BF251" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="BF252" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -22388,7 +22388,7 @@
       </c>
       <c r="BF253" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="BF254" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -22560,7 +22560,7 @@
       </c>
       <c r="BF255" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="BF256" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -22732,7 +22732,7 @@
       </c>
       <c r="BF257" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -22818,7 +22818,7 @@
       </c>
       <c r="BF258" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -22904,7 +22904,7 @@
       </c>
       <c r="BF259" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -22990,7 +22990,7 @@
       </c>
       <c r="BF260" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -23076,7 +23076,7 @@
       </c>
       <c r="BF261" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -23162,7 +23162,7 @@
       </c>
       <c r="BF262" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -23248,7 +23248,7 @@
       </c>
       <c r="BF263" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -23334,7 +23334,7 @@
       </c>
       <c r="BF264" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -23420,7 +23420,7 @@
       </c>
       <c r="BF265" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -23506,7 +23506,7 @@
       </c>
       <c r="BF266" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -23592,7 +23592,7 @@
       </c>
       <c r="BF267" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -23678,7 +23678,7 @@
       </c>
       <c r="BF268" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -23764,7 +23764,7 @@
       </c>
       <c r="BF269" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -23850,7 +23850,7 @@
       </c>
       <c r="BF270" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -23936,7 +23936,7 @@
       </c>
       <c r="BF271" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -24022,7 +24022,7 @@
       </c>
       <c r="BF272" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -24108,7 +24108,7 @@
       </c>
       <c r="BF273" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -24194,7 +24194,7 @@
       </c>
       <c r="BF274" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -24280,7 +24280,7 @@
       </c>
       <c r="BF275" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -24366,7 +24366,7 @@
       </c>
       <c r="BF276" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -24452,7 +24452,7 @@
       </c>
       <c r="BF277" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -24538,7 +24538,7 @@
       </c>
       <c r="BF278" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="BF279" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="BF280" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -24796,7 +24796,7 @@
       </c>
       <c r="BF281" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -24882,7 +24882,7 @@
       </c>
       <c r="BF282" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -24968,7 +24968,7 @@
       </c>
       <c r="BF283" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -25054,7 +25054,7 @@
       </c>
       <c r="BF284" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -25140,7 +25140,7 @@
       </c>
       <c r="BF285" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -25226,7 +25226,7 @@
       </c>
       <c r="BF286" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="BF287" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -25398,7 +25398,7 @@
       </c>
       <c r="BF288" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -25484,7 +25484,7 @@
       </c>
       <c r="BF289" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -25570,7 +25570,7 @@
       </c>
       <c r="BF290" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -25656,7 +25656,7 @@
       </c>
       <c r="BF291" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -25742,7 +25742,7 @@
       </c>
       <c r="BF292" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -25828,7 +25828,7 @@
       </c>
       <c r="BF293" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="BF294" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -26000,7 +26000,7 @@
       </c>
       <c r="BF295" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -26086,7 +26086,7 @@
       </c>
       <c r="BF296" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="BF297" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -26258,7 +26258,7 @@
       </c>
       <c r="BF298" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -26344,7 +26344,7 @@
       </c>
       <c r="BF299" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -26430,7 +26430,7 @@
       </c>
       <c r="BF300" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -26516,7 +26516,7 @@
       </c>
       <c r="BF301" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -26602,7 +26602,7 @@
       </c>
       <c r="BF302" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -26688,7 +26688,7 @@
       </c>
       <c r="BF303" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="BF304" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -26860,7 +26860,7 @@
       </c>
       <c r="BF305" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -26946,7 +26946,7 @@
       </c>
       <c r="BF306" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>
@@ -27032,7 +27032,7 @@
       </c>
       <c r="BF307" t="inlineStr">
         <is>
-          <t>2025-11-15T09:56:48.334822</t>
+          <t>2025-11-15T10:55:46.629790</t>
         </is>
       </c>
     </row>

--- a/outputs/all_dogs_master.xlsx
+++ b/outputs/all_dogs_master.xlsx
@@ -774,7 +774,11 @@
           <t>3-5-28</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
@@ -822,7 +826,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -880,7 +884,11 @@
           <t>0-3-7</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
@@ -928,7 +936,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -986,7 +994,11 @@
           <t>0-4-17</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
@@ -1034,7 +1046,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1104,11 @@
           <t>1-0-1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3,325</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
@@ -1140,7 +1156,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1258,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1316,11 @@
           <t>5-7-20</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
@@ -1348,7 +1368,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1422,11 @@
           <t>6-18-50</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
@@ -1450,7 +1474,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1580,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1634,11 @@
           <t>5-20-50</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -1658,7 +1686,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1744,11 @@
           <t>8-6-17</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>913</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1764,7 +1796,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1854,11 @@
           <t>6-5-27</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1870,7 +1906,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1964,11 @@
           <t>0-1-11</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1976,7 +2016,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2074,11 @@
           <t>0-0-2</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -2082,7 +2126,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2184,11 @@
           <t>0-5-10</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -2188,7 +2236,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2290,11 @@
           <t>2-6-28</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -2290,7 +2342,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2396,11 @@
           <t>6-18-50</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -2392,7 +2448,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2506,11 @@
           <t>4-11-42</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -2498,7 +2558,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2616,11 @@
           <t>7-22-56</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -2604,7 +2668,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2774,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2824,11 @@
           <t>12-19-60</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
@@ -2808,7 +2876,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2930,11 @@
           <t>6-18-50</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
@@ -2910,7 +2982,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -2968,7 +3040,11 @@
           <t>13-13-64</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -3016,7 +3092,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3146,11 @@
           <t>3-4-22</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
@@ -3118,7 +3198,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3256,11 @@
           <t>0-6-10</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
@@ -3224,7 +3308,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3366,11 @@
           <t>0-4-13</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
@@ -3330,7 +3418,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3476,11 @@
           <t>0-0-7</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
@@ -3436,7 +3528,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3586,11 @@
           <t>3-3-16</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>1,472</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
@@ -3542,7 +3638,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3744,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3794,11 @@
           <t>3-7-36</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
@@ -3746,7 +3846,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3952,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -3906,7 +4006,11 @@
           <t>5-9-22</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -3954,7 +4058,7 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4108,11 @@
           <t>4-17-43</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -4052,7 +4160,7 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4218,11 @@
           <t>0-0-2</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
@@ -4158,7 +4270,7 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4328,11 @@
           <t>0-1-2</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -4264,7 +4380,7 @@
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4430,11 @@
           <t>0-1-2</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -4362,7 +4482,7 @@
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4536,11 @@
           <t>6-18-50</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -4464,7 +4588,7 @@
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4638,11 @@
           <t>1-0-6</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -4562,7 +4690,7 @@
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4796,7 @@
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4850,11 @@
           <t>5-15-41</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -4770,7 +4902,7 @@
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4960,11 @@
           <t>6-21-51</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -4876,7 +5012,7 @@
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -4934,7 +5070,11 @@
           <t>8-17-69</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -4982,7 +5122,7 @@
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5228,7 @@
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5282,11 @@
           <t>13-29-118</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
@@ -5190,7 +5334,7 @@
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5392,11 @@
           <t>0-0-4</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
@@ -5296,7 +5444,7 @@
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5502,11 @@
           <t>0-0-7</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -5402,7 +5554,7 @@
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5612,11 @@
           <t>0-3-9</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
@@ -5508,7 +5664,7 @@
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5762,7 @@
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5820,11 @@
           <t>2-11-22</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
@@ -5712,7 +5872,7 @@
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5926,11 @@
           <t>9-17-50</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
@@ -5814,7 +5978,7 @@
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -5868,7 +6032,11 @@
           <t>4-11-38</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -5916,7 +6084,7 @@
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6190,7 @@
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6288,7 @@
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6346,11 @@
           <t>11-12-40</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
@@ -6226,7 +6398,7 @@
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6456,11 @@
           <t>3-3-21</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -6332,7 +6508,7 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6562,11 @@
           <t>6-18-50</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -6434,7 +6614,7 @@
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6668,11 @@
           <t>6-18-50</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
@@ -6536,7 +6720,7 @@
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6778,11 @@
           <t>1-0-4</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>1,329</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -6642,7 +6830,7 @@
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6888,11 @@
           <t>1-1-7</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
@@ -6748,7 +6940,7 @@
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6998,11 @@
           <t>3-9-28</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>1,092</t>
+        </is>
+      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -6854,7 +7050,7 @@
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -6912,7 +7108,11 @@
           <t>13-18-68</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
@@ -6960,7 +7160,7 @@
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7206,11 @@
           <t>4-11-53</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
@@ -7054,7 +7258,7 @@
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7308,11 @@
           <t>10-23-89</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
@@ -7152,7 +7360,7 @@
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7418,11 @@
           <t>9-22-59</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
@@ -7258,7 +7470,7 @@
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7572,7 @@
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7658,7 @@
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -7504,7 +7716,11 @@
           <t>1-2-4</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>1,647</t>
+        </is>
+      </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
@@ -7552,7 +7768,7 @@
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7818,11 @@
           <t>1-2-7</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
@@ -7650,7 +7870,7 @@
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7928,11 @@
           <t>3-7-18</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>1,608</t>
+        </is>
+      </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
@@ -7756,7 +7980,7 @@
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -7810,7 +8034,11 @@
           <t>6-18-50</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
@@ -7858,7 +8086,7 @@
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -7904,7 +8132,11 @@
           <t>4-8-36</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
@@ -7952,7 +8184,7 @@
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8290,7 @@
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8340,11 @@
           <t>4-2-11</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>1,033</t>
+        </is>
+      </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
@@ -8156,7 +8392,7 @@
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -8202,7 +8438,11 @@
           <t>7-14-50</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
@@ -8250,7 +8490,7 @@
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8596,7 @@
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8654,11 @@
           <t>0-2-6</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
@@ -8462,7 +8706,7 @@
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -8512,7 +8756,11 @@
           <t>0-0-3</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
@@ -8560,7 +8808,7 @@
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8866,11 @@
           <t>1-4-9</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
@@ -8666,7 +8918,7 @@
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -8772,7 +9024,7 @@
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -8830,7 +9082,11 @@
           <t>5-11-34</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
@@ -8878,7 +9134,7 @@
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -8984,7 +9240,7 @@
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9294,11 @@
           <t>5-15-38</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
@@ -9086,7 +9346,7 @@
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9404,11 @@
           <t>4-6-22</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
@@ -9192,7 +9456,7 @@
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9514,11 @@
           <t>8-10-36</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
@@ -9298,7 +9566,7 @@
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9652,7 @@
       </c>
       <c r="BF85" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9738,7 @@
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -9556,7 +9824,7 @@
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9910,7 @@
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9996,7 @@
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -9814,7 +10082,7 @@
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -9900,7 +10168,7 @@
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -9986,7 +10254,7 @@
       </c>
       <c r="BF92" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10340,7 @@
       </c>
       <c r="BF93" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10426,7 @@
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -10244,7 +10512,7 @@
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10598,7 @@
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -10416,7 +10684,7 @@
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10770,7 @@
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10856,7 @@
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10942,7 @@
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -10760,7 +11028,7 @@
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -10846,7 +11114,7 @@
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -10896,7 +11164,11 @@
           <t>0-3-18</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
@@ -10944,7 +11216,7 @@
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11274,11 @@
           <t>0-1-3</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
@@ -11050,7 +11326,7 @@
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11384,11 @@
           <t>0-0-1</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
@@ -11156,7 +11436,7 @@
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -11214,7 +11494,11 @@
           <t>2-0-3</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
@@ -11262,7 +11546,7 @@
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -11320,7 +11604,11 @@
           <t>1-6-22</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr"/>
@@ -11368,7 +11656,7 @@
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11714,11 @@
           <t>1-6-28</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr"/>
@@ -11474,7 +11766,7 @@
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -11532,7 +11824,11 @@
           <t>3-7-23</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
@@ -11580,7 +11876,7 @@
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11934,11 @@
           <t>7-19-68</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
@@ -11686,7 +11986,7 @@
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -11740,7 +12040,11 @@
           <t>1-11-50</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr"/>
@@ -11788,7 +12092,7 @@
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -11894,7 +12198,7 @@
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -11952,7 +12256,11 @@
           <t>0-7-16</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
@@ -12000,7 +12308,7 @@
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -12058,7 +12366,11 @@
           <t>0-0-1</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr"/>
@@ -12106,7 +12418,7 @@
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12476,11 @@
           <t>0-0-1</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr"/>
@@ -12212,7 +12528,7 @@
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12586,11 @@
           <t>1-1-12</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr"/>
@@ -12318,7 +12638,7 @@
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -12376,7 +12696,11 @@
           <t>2-11-19</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr"/>
@@ -12424,7 +12748,7 @@
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -12478,7 +12802,11 @@
           <t>2-0-2</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>2,884</t>
+        </is>
+      </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr"/>
@@ -12526,7 +12854,7 @@
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -12580,7 +12908,11 @@
           <t>2-4-29</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr"/>
@@ -12628,7 +12960,7 @@
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -12682,7 +13014,11 @@
           <t>13-14-50</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>1,277</t>
+        </is>
+      </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr"/>
@@ -12730,7 +13066,7 @@
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -12784,7 +13120,11 @@
           <t>6-3-9</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>1,885</t>
+        </is>
+      </c>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr"/>
@@ -12832,7 +13172,7 @@
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -12918,7 +13258,7 @@
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -13024,7 +13364,7 @@
       </c>
       <c r="BF123" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13462,7 @@
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13516,11 @@
           <t>1-11-50</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr"/>
@@ -13224,7 +13568,7 @@
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -13282,7 +13626,11 @@
           <t>2-1-8</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr"/>
@@ -13330,7 +13678,7 @@
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -13380,7 +13728,11 @@
           <t>2-4-11</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>973</t>
+        </is>
+      </c>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr"/>
@@ -13428,7 +13780,7 @@
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13838,11 @@
           <t>7-9-29</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr"/>
@@ -13534,7 +13890,7 @@
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -13588,7 +13944,11 @@
           <t>13-18-50</t>
         </is>
       </c>
-      <c r="P129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>1,699</t>
+        </is>
+      </c>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr"/>
@@ -13636,7 +13996,7 @@
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -13686,7 +14046,11 @@
           <t>7-20-68</t>
         </is>
       </c>
-      <c r="P130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr"/>
@@ -13734,7 +14098,7 @@
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -13792,7 +14156,11 @@
           <t>8-10-58</t>
         </is>
       </c>
-      <c r="P131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr"/>
@@ -13840,7 +14208,7 @@
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -13898,7 +14266,11 @@
           <t>0-4-28</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr"/>
@@ -13946,7 +14318,7 @@
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14376,11 @@
           <t>0-3-3</t>
         </is>
       </c>
-      <c r="P133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr"/>
@@ -14052,7 +14428,7 @@
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -14110,7 +14486,11 @@
           <t>0-0-1</t>
         </is>
       </c>
-      <c r="P134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr"/>
@@ -14158,7 +14538,7 @@
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -14212,7 +14592,11 @@
           <t>1-11-50</t>
         </is>
       </c>
-      <c r="P135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr"/>
@@ -14260,7 +14644,7 @@
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -14318,7 +14702,11 @@
           <t>1-13-38</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr"/>
@@ -14366,7 +14754,7 @@
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14812,11 @@
           <t>1-9-27</t>
         </is>
       </c>
-      <c r="P137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr"/>
@@ -14472,7 +14864,7 @@
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -14526,7 +14918,11 @@
           <t>2-4-8</t>
         </is>
       </c>
-      <c r="P138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>1,199</t>
+        </is>
+      </c>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
@@ -14574,7 +14970,7 @@
       </c>
       <c r="BF138" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -14632,7 +15028,11 @@
           <t>11-22-66</t>
         </is>
       </c>
-      <c r="P139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr"/>
@@ -14680,7 +15080,7 @@
       </c>
       <c r="BF139" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -14730,7 +15130,11 @@
           <t>14-25-101</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr"/>
@@ -14778,7 +15182,7 @@
       </c>
       <c r="BF140" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -14836,7 +15240,11 @@
           <t>6-13-49</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr"/>
@@ -14884,7 +15292,7 @@
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -14942,7 +15350,11 @@
           <t>0-0-1</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr"/>
@@ -14990,7 +15402,7 @@
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -15048,7 +15460,11 @@
           <t>0-4-14</t>
         </is>
       </c>
-      <c r="P143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr"/>
@@ -15096,7 +15512,7 @@
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15562,11 @@
           <t>1-3-19</t>
         </is>
       </c>
-      <c r="P144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr"/>
@@ -15194,7 +15614,7 @@
       </c>
       <c r="BF144" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15672,11 @@
           <t>2-4-23</t>
         </is>
       </c>
-      <c r="P145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr"/>
@@ -15300,7 +15724,7 @@
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -15358,7 +15782,11 @@
           <t>1-2-5</t>
         </is>
       </c>
-      <c r="P146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr"/>
@@ -15406,7 +15834,7 @@
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -15452,7 +15880,11 @@
           <t>2-1-14</t>
         </is>
       </c>
-      <c r="P147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr"/>
@@ -15500,7 +15932,7 @@
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15990,11 @@
           <t>7-10-32</t>
         </is>
       </c>
-      <c r="P148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>1,210</t>
+        </is>
+      </c>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr"/>
@@ -15606,7 +16042,7 @@
       </c>
       <c r="BF148" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -15664,7 +16100,11 @@
           <t>14-37-112</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr"/>
@@ -15712,7 +16152,7 @@
       </c>
       <c r="BF149" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -15766,7 +16206,11 @@
           <t>1-11-50</t>
         </is>
       </c>
-      <c r="P150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr"/>
@@ -15814,7 +16258,7 @@
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -15872,7 +16316,11 @@
           <t>3-6-18</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr"/>
@@ -15920,7 +16368,7 @@
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16454,7 @@
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -16060,7 +16508,11 @@
           <t>1-2-12</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr"/>
@@ -16108,7 +16560,7 @@
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -16166,7 +16618,11 @@
           <t>1-3-5</t>
         </is>
       </c>
-      <c r="P154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr"/>
@@ -16214,7 +16670,7 @@
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16728,11 @@
           <t>1-2-6</t>
         </is>
       </c>
-      <c r="P155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr"/>
@@ -16320,7 +16780,7 @@
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16834,11 @@
           <t>2-11-34</t>
         </is>
       </c>
-      <c r="P156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr"/>
@@ -16422,7 +16886,7 @@
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -16480,7 +16944,11 @@
           <t>9-22-56</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr"/>
@@ -16528,7 +16996,7 @@
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -16582,7 +17050,11 @@
           <t>9-18-50</t>
         </is>
       </c>
-      <c r="P158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>1,057</t>
+        </is>
+      </c>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr"/>
@@ -16630,7 +17102,7 @@
       </c>
       <c r="BF158" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -16684,7 +17156,11 @@
           <t>8-8-36</t>
         </is>
       </c>
-      <c r="P159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr"/>
@@ -16732,7 +17208,7 @@
       </c>
       <c r="BF159" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -16786,7 +17262,11 @@
           <t>1-11-50</t>
         </is>
       </c>
-      <c r="P160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
       <c r="S160" t="inlineStr"/>
@@ -16834,7 +17314,7 @@
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -16888,7 +17368,11 @@
           <t>0-1-3</t>
         </is>
       </c>
-      <c r="P161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr"/>
@@ -16936,7 +17420,7 @@
       </c>
       <c r="BF161" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -16994,7 +17478,11 @@
           <t>0-0-3</t>
         </is>
       </c>
-      <c r="P162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr"/>
@@ -17042,7 +17530,7 @@
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -17100,7 +17588,11 @@
           <t>0-8-27</t>
         </is>
       </c>
-      <c r="P163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
       <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr"/>
@@ -17148,7 +17640,7 @@
       </c>
       <c r="BF163" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17698,11 @@
           <t>2-5-77</t>
         </is>
       </c>
-      <c r="P164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr"/>
@@ -17254,7 +17750,7 @@
       </c>
       <c r="BF164" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17808,11 @@
           <t>1-4-10</t>
         </is>
       </c>
-      <c r="P165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr"/>
@@ -17360,7 +17860,7 @@
       </c>
       <c r="BF165" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -17418,7 +17918,11 @@
           <t>1-1-3</t>
         </is>
       </c>
-      <c r="P166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>1,246</t>
+        </is>
+      </c>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr"/>
@@ -17466,7 +17970,7 @@
       </c>
       <c r="BF166" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -17516,7 +18020,11 @@
           <t>2-8-38</t>
         </is>
       </c>
-      <c r="P167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr"/>
@@ -17564,7 +18072,7 @@
       </c>
       <c r="BF167" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -17618,7 +18126,11 @@
           <t>8-22-53</t>
         </is>
       </c>
-      <c r="P168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>904</t>
+        </is>
+      </c>
       <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr"/>
@@ -17666,7 +18178,7 @@
       </c>
       <c r="BF168" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -17724,7 +18236,11 @@
           <t>6-14-30</t>
         </is>
       </c>
-      <c r="P169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr"/>
@@ -17772,7 +18288,7 @@
       </c>
       <c r="BF169" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -17830,7 +18346,11 @@
           <t>15-22-89</t>
         </is>
       </c>
-      <c r="P170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr"/>
@@ -17878,7 +18398,7 @@
       </c>
       <c r="BF170" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -17984,7 +18504,7 @@
       </c>
       <c r="BF171" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -18042,7 +18562,11 @@
           <t>0-1-6</t>
         </is>
       </c>
-      <c r="P172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr"/>
@@ -18090,7 +18614,7 @@
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -18140,7 +18664,11 @@
           <t>0-2-22</t>
         </is>
       </c>
-      <c r="P173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr"/>
@@ -18188,7 +18716,7 @@
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -18242,7 +18770,11 @@
           <t>0-8-23</t>
         </is>
       </c>
-      <c r="P174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr"/>
@@ -18290,7 +18822,7 @@
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -18344,7 +18876,11 @@
           <t>1-4-15</t>
         </is>
       </c>
-      <c r="P175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr"/>
@@ -18392,7 +18928,7 @@
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -18446,7 +18982,11 @@
           <t>1-1-5</t>
         </is>
       </c>
-      <c r="P176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr"/>
@@ -18494,7 +19034,7 @@
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -18552,7 +19092,11 @@
           <t>1-0-2</t>
         </is>
       </c>
-      <c r="P177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>1,405</t>
+        </is>
+      </c>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr"/>
@@ -18600,7 +19144,7 @@
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -18698,7 +19242,7 @@
       </c>
       <c r="BF178" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -18752,7 +19296,11 @@
           <t>4-6-21</t>
         </is>
       </c>
-      <c r="P179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
       <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr"/>
@@ -18800,7 +19348,7 @@
       </c>
       <c r="BF179" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -18854,7 +19402,11 @@
           <t>9-18-50</t>
         </is>
       </c>
-      <c r="P180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr"/>
@@ -18902,7 +19454,7 @@
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -18956,7 +19508,11 @@
           <t>16-49-129</t>
         </is>
       </c>
-      <c r="P181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
       <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr"/>
@@ -19004,7 +19560,7 @@
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -19110,7 +19666,7 @@
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -19196,7 +19752,7 @@
       </c>
       <c r="BF183" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -19282,7 +19838,7 @@
       </c>
       <c r="BF184" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -19368,7 +19924,7 @@
       </c>
       <c r="BF185" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -19454,7 +20010,7 @@
       </c>
       <c r="BF186" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -19540,7 +20096,7 @@
       </c>
       <c r="BF187" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -19626,7 +20182,7 @@
       </c>
       <c r="BF188" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -19712,7 +20268,7 @@
       </c>
       <c r="BF189" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -19798,7 +20354,7 @@
       </c>
       <c r="BF190" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -19884,7 +20440,7 @@
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -19942,7 +20498,11 @@
           <t>1-0-3</t>
         </is>
       </c>
-      <c r="P192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr"/>
@@ -19990,7 +20550,7 @@
       </c>
       <c r="BF192" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -20044,7 +20604,11 @@
           <t>1-1-6</t>
         </is>
       </c>
-      <c r="P193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
       <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
@@ -20092,7 +20656,7 @@
       </c>
       <c r="BF193" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -20150,7 +20714,11 @@
           <t>2-3-5</t>
         </is>
       </c>
-      <c r="P194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
@@ -20198,7 +20766,7 @@
       </c>
       <c r="BF194" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -20252,7 +20820,11 @@
           <t>1-14-25</t>
         </is>
       </c>
-      <c r="P195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
@@ -20300,7 +20872,7 @@
       </c>
       <c r="BF195" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -20354,7 +20926,11 @@
           <t>13-12-37</t>
         </is>
       </c>
-      <c r="P196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>2,104</t>
+        </is>
+      </c>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr"/>
@@ -20402,7 +20978,7 @@
       </c>
       <c r="BF196" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -20460,7 +21036,11 @@
           <t>7-7-23</t>
         </is>
       </c>
-      <c r="P197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr"/>
@@ -20508,7 +21088,7 @@
       </c>
       <c r="BF197" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -20558,7 +21138,11 @@
           <t>7-11-49</t>
         </is>
       </c>
-      <c r="P198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr"/>
@@ -20606,7 +21190,7 @@
       </c>
       <c r="BF198" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -20664,7 +21248,11 @@
           <t>3-6-25</t>
         </is>
       </c>
-      <c r="P199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
       <c r="Q199" t="inlineStr"/>
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr"/>
@@ -20712,7 +21300,7 @@
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -20818,7 +21406,7 @@
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -20920,7 +21508,7 @@
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -20974,7 +21562,11 @@
           <t>2-12-37</t>
         </is>
       </c>
-      <c r="P202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
       <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr"/>
       <c r="S202" t="inlineStr"/>
@@ -21022,7 +21614,7 @@
       </c>
       <c r="BF202" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -21080,7 +21672,11 @@
           <t>2-1-8</t>
         </is>
       </c>
-      <c r="P203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
       <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr"/>
@@ -21128,7 +21724,7 @@
       </c>
       <c r="BF203" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -21230,7 +21826,7 @@
       </c>
       <c r="BF204" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -21288,7 +21884,11 @@
           <t>1-6-12</t>
         </is>
       </c>
-      <c r="P205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
       <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr"/>
@@ -21336,7 +21936,7 @@
       </c>
       <c r="BF205" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -21394,7 +21994,11 @@
           <t>1-8-23</t>
         </is>
       </c>
-      <c r="P206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr"/>
@@ -21442,7 +22046,7 @@
       </c>
       <c r="BF206" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -21500,7 +22104,11 @@
           <t>1-1-4</t>
         </is>
       </c>
-      <c r="P207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr"/>
       <c r="S207" t="inlineStr"/>
@@ -21548,7 +22156,7 @@
       </c>
       <c r="BF207" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -21602,7 +22210,11 @@
           <t>1-14-41</t>
         </is>
       </c>
-      <c r="P208" t="inlineStr"/>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
       <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr"/>
       <c r="S208" t="inlineStr"/>
@@ -21650,7 +22262,7 @@
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -21704,7 +22316,11 @@
           <t>1-1-10</t>
         </is>
       </c>
-      <c r="P209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
       <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr"/>
@@ -21752,7 +22368,7 @@
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -21806,7 +22422,11 @@
           <t>5-8-50</t>
         </is>
       </c>
-      <c r="P210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>2,308</t>
+        </is>
+      </c>
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr"/>
       <c r="S210" t="inlineStr"/>
@@ -21854,7 +22474,7 @@
       </c>
       <c r="BF210" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -21956,7 +22576,7 @@
       </c>
       <c r="BF211" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22634,11 @@
           <t>8-1-10</t>
         </is>
       </c>
-      <c r="P212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>3,909</t>
+        </is>
+      </c>
       <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr"/>
@@ -22062,7 +22686,7 @@
       </c>
       <c r="BF212" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -22116,7 +22740,11 @@
           <t>2-13-55</t>
         </is>
       </c>
-      <c r="P213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr"/>
@@ -22164,7 +22792,7 @@
       </c>
       <c r="BF213" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -22270,7 +22898,7 @@
       </c>
       <c r="BF214" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -22324,7 +22952,11 @@
           <t>2-2-8</t>
         </is>
       </c>
-      <c r="P215" t="inlineStr"/>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
       <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr"/>
       <c r="S215" t="inlineStr"/>
@@ -22372,7 +23004,7 @@
       </c>
       <c r="BF215" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -22430,7 +23062,11 @@
           <t>2-2-19</t>
         </is>
       </c>
-      <c r="P216" t="inlineStr"/>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
       <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr"/>
       <c r="S216" t="inlineStr"/>
@@ -22478,7 +23114,7 @@
       </c>
       <c r="BF216" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -22532,7 +23168,11 @@
           <t>0-4-7</t>
         </is>
       </c>
-      <c r="P217" t="inlineStr"/>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
       <c r="Q217" t="inlineStr"/>
       <c r="R217" t="inlineStr"/>
       <c r="S217" t="inlineStr"/>
@@ -22580,7 +23220,7 @@
       </c>
       <c r="BF217" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -22638,7 +23278,11 @@
           <t>1-8-21</t>
         </is>
       </c>
-      <c r="P218" t="inlineStr"/>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr"/>
       <c r="S218" t="inlineStr"/>
@@ -22686,7 +23330,7 @@
       </c>
       <c r="BF218" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -22744,7 +23388,11 @@
           <t>1-2-3</t>
         </is>
       </c>
-      <c r="P219" t="inlineStr"/>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr"/>
@@ -22792,7 +23440,7 @@
       </c>
       <c r="BF219" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -22838,7 +23486,11 @@
           <t>1-3-13</t>
         </is>
       </c>
-      <c r="P220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr"/>
@@ -22886,7 +23538,7 @@
       </c>
       <c r="BF220" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -22940,7 +23592,11 @@
           <t>2-2-7</t>
         </is>
       </c>
-      <c r="P221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr"/>
@@ -22988,7 +23644,7 @@
       </c>
       <c r="BF221" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -23042,7 +23698,11 @@
           <t>1-2-10</t>
         </is>
       </c>
-      <c r="P222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="inlineStr"/>
@@ -23090,7 +23750,7 @@
       </c>
       <c r="BF222" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -23148,7 +23808,11 @@
           <t>2-3-27</t>
         </is>
       </c>
-      <c r="P223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
       <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr"/>
       <c r="S223" t="inlineStr"/>
@@ -23196,7 +23860,7 @@
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -23254,7 +23918,11 @@
           <t>5-10-27</t>
         </is>
       </c>
-      <c r="P224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>1,269</t>
+        </is>
+      </c>
       <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr"/>
@@ -23302,7 +23970,7 @@
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -23404,7 +24072,7 @@
       </c>
       <c r="BF225" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -23454,7 +24122,11 @@
           <t>7-12-40</t>
         </is>
       </c>
-      <c r="P226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr"/>
@@ -23502,7 +24174,7 @@
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -23604,7 +24276,7 @@
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -23702,7 +24374,7 @@
       </c>
       <c r="BF228" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -23756,7 +24428,11 @@
           <t>12-16-38</t>
         </is>
       </c>
-      <c r="P229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
       <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr"/>
@@ -23804,7 +24480,7 @@
       </c>
       <c r="BF229" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -23906,7 +24582,7 @@
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -23956,7 +24632,11 @@
           <t>0-13-31</t>
         </is>
       </c>
-      <c r="P231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
       <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr"/>
@@ -24004,7 +24684,7 @@
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -24062,7 +24742,11 @@
           <t>2-3-6</t>
         </is>
       </c>
-      <c r="P232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
       <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr"/>
@@ -24110,7 +24794,7 @@
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -24168,7 +24852,11 @@
           <t>1-15-48</t>
         </is>
       </c>
-      <c r="P233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
       <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr"/>
@@ -24216,7 +24904,7 @@
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -24274,7 +24962,11 @@
           <t>1-2-22</t>
         </is>
       </c>
-      <c r="P234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr"/>
@@ -24322,7 +25014,7 @@
       </c>
       <c r="BF234" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -24380,7 +25072,11 @@
           <t>1-1-4</t>
         </is>
       </c>
-      <c r="P235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
       <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr"/>
@@ -24428,7 +25124,7 @@
       </c>
       <c r="BF235" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -24486,7 +25182,11 @@
           <t>10-15-37</t>
         </is>
       </c>
-      <c r="P236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>1,315</t>
+        </is>
+      </c>
       <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr"/>
@@ -24534,7 +25234,7 @@
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -24588,7 +25288,11 @@
           <t>19-31-105</t>
         </is>
       </c>
-      <c r="P237" t="inlineStr"/>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
       <c r="Q237" t="inlineStr"/>
       <c r="R237" t="inlineStr"/>
       <c r="S237" t="inlineStr"/>
@@ -24636,7 +25340,7 @@
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -24694,7 +25398,11 @@
           <t>2-3-11</t>
         </is>
       </c>
-      <c r="P238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
       <c r="Q238" t="inlineStr"/>
       <c r="R238" t="inlineStr"/>
       <c r="S238" t="inlineStr"/>
@@ -24742,7 +25450,7 @@
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -24796,7 +25504,11 @@
           <t>7-11-50</t>
         </is>
       </c>
-      <c r="P239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
       <c r="Q239" t="inlineStr"/>
       <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr"/>
@@ -24844,7 +25556,7 @@
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -24902,7 +25614,11 @@
           <t>2-12-51</t>
         </is>
       </c>
-      <c r="P240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
       <c r="Q240" t="inlineStr"/>
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr"/>
@@ -24950,7 +25666,7 @@
       </c>
       <c r="BF240" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -25000,7 +25716,11 @@
           <t>3-6-13</t>
         </is>
       </c>
-      <c r="P241" t="inlineStr"/>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>1,430</t>
+        </is>
+      </c>
       <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr"/>
@@ -25048,7 +25768,7 @@
       </c>
       <c r="BF241" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -25150,7 +25870,7 @@
       </c>
       <c r="BF242" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -25256,7 +25976,7 @@
       </c>
       <c r="BF243" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -25314,7 +26034,11 @@
           <t>1-4-8</t>
         </is>
       </c>
-      <c r="P244" t="inlineStr"/>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
       <c r="Q244" t="inlineStr"/>
       <c r="R244" t="inlineStr"/>
       <c r="S244" t="inlineStr"/>
@@ -25362,7 +26086,7 @@
       </c>
       <c r="BF244" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -25448,7 +26172,7 @@
       </c>
       <c r="BF245" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -25502,7 +26226,11 @@
           <t>2-0-2</t>
         </is>
       </c>
-      <c r="P246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>2,015</t>
+        </is>
+      </c>
       <c r="Q246" t="inlineStr"/>
       <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr"/>
@@ -25550,7 +26278,7 @@
       </c>
       <c r="BF246" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -25608,7 +26336,11 @@
           <t>1-14-28</t>
         </is>
       </c>
-      <c r="P247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
       <c r="Q247" t="inlineStr"/>
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr"/>
@@ -25656,7 +26388,7 @@
       </c>
       <c r="BF247" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -25710,7 +26442,11 @@
           <t>7-11-21</t>
         </is>
       </c>
-      <c r="P248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>1,834</t>
+        </is>
+      </c>
       <c r="Q248" t="inlineStr"/>
       <c r="R248" t="inlineStr"/>
       <c r="S248" t="inlineStr"/>
@@ -25758,7 +26494,7 @@
       </c>
       <c r="BF248" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -25812,7 +26548,11 @@
           <t>4-4-10</t>
         </is>
       </c>
-      <c r="P249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>1,022</t>
+        </is>
+      </c>
       <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr"/>
@@ -25860,7 +26600,7 @@
       </c>
       <c r="BF249" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -25914,7 +26654,11 @@
           <t>15-17-55</t>
         </is>
       </c>
-      <c r="P250" t="inlineStr"/>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>1,004</t>
+        </is>
+      </c>
       <c r="Q250" t="inlineStr"/>
       <c r="R250" t="inlineStr"/>
       <c r="S250" t="inlineStr"/>
@@ -25962,7 +26706,7 @@
       </c>
       <c r="BF250" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -26016,7 +26760,11 @@
           <t>4-16-50</t>
         </is>
       </c>
-      <c r="P251" t="inlineStr"/>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
       <c r="Q251" t="inlineStr"/>
       <c r="R251" t="inlineStr"/>
       <c r="S251" t="inlineStr"/>
@@ -26064,7 +26812,7 @@
       </c>
       <c r="BF251" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -26122,7 +26870,11 @@
           <t>5-17-59</t>
         </is>
       </c>
-      <c r="P252" t="inlineStr"/>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
       <c r="Q252" t="inlineStr"/>
       <c r="R252" t="inlineStr"/>
       <c r="S252" t="inlineStr"/>
@@ -26170,7 +26922,7 @@
       </c>
       <c r="BF252" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -26272,7 +27024,7 @@
       </c>
       <c r="BF253" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -26326,7 +27078,11 @@
           <t>2-6-30</t>
         </is>
       </c>
-      <c r="P254" t="inlineStr"/>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="Q254" t="inlineStr"/>
       <c r="R254" t="inlineStr"/>
       <c r="S254" t="inlineStr"/>
@@ -26374,7 +27130,7 @@
       </c>
       <c r="BF254" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -26432,7 +27188,11 @@
           <t>0-4-6</t>
         </is>
       </c>
-      <c r="P255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
       <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr"/>
@@ -26480,7 +27240,7 @@
       </c>
       <c r="BF255" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -26538,7 +27298,11 @@
           <t>1-0-2</t>
         </is>
       </c>
-      <c r="P256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
       <c r="Q256" t="inlineStr"/>
       <c r="R256" t="inlineStr"/>
       <c r="S256" t="inlineStr"/>
@@ -26586,7 +27350,7 @@
       </c>
       <c r="BF256" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -26632,7 +27396,11 @@
           <t>1-4-16</t>
         </is>
       </c>
-      <c r="P257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
       <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr"/>
@@ -26680,7 +27448,7 @@
       </c>
       <c r="BF257" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -26738,7 +27506,11 @@
           <t>1-6-35</t>
         </is>
       </c>
-      <c r="P258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
       <c r="Q258" t="inlineStr"/>
       <c r="R258" t="inlineStr"/>
       <c r="S258" t="inlineStr"/>
@@ -26786,7 +27558,7 @@
       </c>
       <c r="BF258" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -26844,7 +27616,11 @@
           <t>5-14-35</t>
         </is>
       </c>
-      <c r="P259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
       <c r="Q259" t="inlineStr"/>
       <c r="R259" t="inlineStr"/>
       <c r="S259" t="inlineStr"/>
@@ -26892,7 +27668,7 @@
       </c>
       <c r="BF259" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -26994,7 +27770,7 @@
       </c>
       <c r="BF260" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -27048,7 +27824,11 @@
           <t>2-6-28</t>
         </is>
       </c>
-      <c r="P261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
       <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr"/>
       <c r="S261" t="inlineStr"/>
@@ -27096,7 +27876,7 @@
       </c>
       <c r="BF261" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -27150,7 +27930,11 @@
           <t>18-44-110</t>
         </is>
       </c>
-      <c r="P262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
       <c r="Q262" t="inlineStr"/>
       <c r="R262" t="inlineStr"/>
       <c r="S262" t="inlineStr"/>
@@ -27198,7 +27982,7 @@
       </c>
       <c r="BF262" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -27248,7 +28032,11 @@
           <t>2-1-4</t>
         </is>
       </c>
-      <c r="P263" t="inlineStr"/>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>2,925</t>
+        </is>
+      </c>
       <c r="Q263" t="inlineStr"/>
       <c r="R263" t="inlineStr"/>
       <c r="S263" t="inlineStr"/>
@@ -27296,7 +28084,7 @@
       </c>
       <c r="BF263" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -27354,7 +28142,11 @@
           <t>2-11-39</t>
         </is>
       </c>
-      <c r="P264" t="inlineStr"/>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
       <c r="Q264" t="inlineStr"/>
       <c r="R264" t="inlineStr"/>
       <c r="S264" t="inlineStr"/>
@@ -27402,7 +28194,7 @@
       </c>
       <c r="BF264" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -27460,7 +28252,11 @@
           <t>4-5-14</t>
         </is>
       </c>
-      <c r="P265" t="inlineStr"/>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
       <c r="Q265" t="inlineStr"/>
       <c r="R265" t="inlineStr"/>
       <c r="S265" t="inlineStr"/>
@@ -27508,7 +28304,7 @@
       </c>
       <c r="BF265" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -27558,7 +28354,11 @@
           <t>0-1-2</t>
         </is>
       </c>
-      <c r="P266" t="inlineStr"/>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
       <c r="Q266" t="inlineStr"/>
       <c r="R266" t="inlineStr"/>
       <c r="S266" t="inlineStr"/>
@@ -27606,7 +28406,7 @@
       </c>
       <c r="BF266" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -27664,7 +28464,11 @@
           <t>1-0-2</t>
         </is>
       </c>
-      <c r="P267" t="inlineStr"/>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
       <c r="Q267" t="inlineStr"/>
       <c r="R267" t="inlineStr"/>
       <c r="S267" t="inlineStr"/>
@@ -27712,7 +28516,7 @@
       </c>
       <c r="BF267" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -27770,7 +28574,11 @@
           <t>1-0-3</t>
         </is>
       </c>
-      <c r="P268" t="inlineStr"/>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
       <c r="Q268" t="inlineStr"/>
       <c r="R268" t="inlineStr"/>
       <c r="S268" t="inlineStr"/>
@@ -27818,7 +28626,7 @@
       </c>
       <c r="BF268" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -27924,7 +28732,7 @@
       </c>
       <c r="BF269" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -27982,7 +28790,11 @@
           <t>2-9-22</t>
         </is>
       </c>
-      <c r="P270" t="inlineStr"/>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
       <c r="Q270" t="inlineStr"/>
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr"/>
@@ -28030,7 +28842,7 @@
       </c>
       <c r="BF270" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -28084,7 +28896,11 @@
           <t>14-17-50</t>
         </is>
       </c>
-      <c r="P271" t="inlineStr"/>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>2,881</t>
+        </is>
+      </c>
       <c r="Q271" t="inlineStr"/>
       <c r="R271" t="inlineStr"/>
       <c r="S271" t="inlineStr"/>
@@ -28132,7 +28948,7 @@
       </c>
       <c r="BF271" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -28234,7 +29050,7 @@
       </c>
       <c r="BF272" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -28288,7 +29104,11 @@
           <t>16-13-50</t>
         </is>
       </c>
-      <c r="P273" t="inlineStr"/>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>1,044</t>
+        </is>
+      </c>
       <c r="Q273" t="inlineStr"/>
       <c r="R273" t="inlineStr"/>
       <c r="S273" t="inlineStr"/>
@@ -28336,7 +29156,7 @@
       </c>
       <c r="BF273" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -28390,7 +29210,11 @@
           <t>3-13-50</t>
         </is>
       </c>
-      <c r="P274" t="inlineStr"/>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
       <c r="Q274" t="inlineStr"/>
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr"/>
@@ -28438,7 +29262,7 @@
       </c>
       <c r="BF274" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -28496,7 +29320,11 @@
           <t>4-6-23</t>
         </is>
       </c>
-      <c r="P275" t="inlineStr"/>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
       <c r="Q275" t="inlineStr"/>
       <c r="R275" t="inlineStr"/>
       <c r="S275" t="inlineStr"/>
@@ -28544,7 +29372,7 @@
       </c>
       <c r="BF275" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -28642,7 +29470,7 @@
       </c>
       <c r="BF276" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -28696,7 +29524,11 @@
           <t>1-4-9</t>
         </is>
       </c>
-      <c r="P277" t="inlineStr"/>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
       <c r="Q277" t="inlineStr"/>
       <c r="R277" t="inlineStr"/>
       <c r="S277" t="inlineStr"/>
@@ -28744,7 +29576,7 @@
       </c>
       <c r="BF277" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -28802,7 +29634,11 @@
           <t>1-0-2</t>
         </is>
       </c>
-      <c r="P278" t="inlineStr"/>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
       <c r="Q278" t="inlineStr"/>
       <c r="R278" t="inlineStr"/>
       <c r="S278" t="inlineStr"/>
@@ -28850,7 +29686,7 @@
       </c>
       <c r="BF278" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -28896,7 +29732,11 @@
           <t>1-1-4</t>
         </is>
       </c>
-      <c r="P279" t="inlineStr"/>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
       <c r="Q279" t="inlineStr"/>
       <c r="R279" t="inlineStr"/>
       <c r="S279" t="inlineStr"/>
@@ -28944,7 +29784,7 @@
       </c>
       <c r="BF279" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -29050,7 +29890,7 @@
       </c>
       <c r="BF280" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -29108,7 +29948,11 @@
           <t>1-2-15</t>
         </is>
       </c>
-      <c r="P281" t="inlineStr"/>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
       <c r="Q281" t="inlineStr"/>
       <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr"/>
@@ -29156,7 +30000,7 @@
       </c>
       <c r="BF281" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -29214,7 +30058,11 @@
           <t>1-4-17</t>
         </is>
       </c>
-      <c r="P282" t="inlineStr"/>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
       <c r="Q282" t="inlineStr"/>
       <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr"/>
@@ -29262,7 +30110,7 @@
       </c>
       <c r="BF282" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -29316,7 +30164,11 @@
           <t>6-16-50</t>
         </is>
       </c>
-      <c r="P283" t="inlineStr"/>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
       <c r="Q283" t="inlineStr"/>
       <c r="R283" t="inlineStr"/>
       <c r="S283" t="inlineStr"/>
@@ -29364,7 +30216,7 @@
       </c>
       <c r="BF283" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -29418,7 +30270,11 @@
           <t>5-4-12</t>
         </is>
       </c>
-      <c r="P284" t="inlineStr"/>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
       <c r="Q284" t="inlineStr"/>
       <c r="R284" t="inlineStr"/>
       <c r="S284" t="inlineStr"/>
@@ -29466,7 +30322,7 @@
       </c>
       <c r="BF284" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -29516,7 +30372,11 @@
           <t>8-8-29</t>
         </is>
       </c>
-      <c r="P285" t="inlineStr"/>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>1,141</t>
+        </is>
+      </c>
       <c r="Q285" t="inlineStr"/>
       <c r="R285" t="inlineStr"/>
       <c r="S285" t="inlineStr"/>
@@ -29564,7 +30424,7 @@
       </c>
       <c r="BF285" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -29610,7 +30470,11 @@
           <t>2-5-13</t>
         </is>
       </c>
-      <c r="P286" t="inlineStr"/>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
       <c r="Q286" t="inlineStr"/>
       <c r="R286" t="inlineStr"/>
       <c r="S286" t="inlineStr"/>
@@ -29658,7 +30522,7 @@
       </c>
       <c r="BF286" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -29708,7 +30572,11 @@
           <t>3-3-9</t>
         </is>
       </c>
-      <c r="P287" t="inlineStr"/>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>1,301</t>
+        </is>
+      </c>
       <c r="Q287" t="inlineStr"/>
       <c r="R287" t="inlineStr"/>
       <c r="S287" t="inlineStr"/>
@@ -29756,7 +30624,7 @@
       </c>
       <c r="BF287" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -29810,7 +30678,11 @@
           <t>5-18-54</t>
         </is>
       </c>
-      <c r="P288" t="inlineStr"/>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
       <c r="Q288" t="inlineStr"/>
       <c r="R288" t="inlineStr"/>
       <c r="S288" t="inlineStr"/>
@@ -29858,7 +30730,7 @@
       </c>
       <c r="BF288" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -29916,7 +30788,11 @@
           <t>2-7-14</t>
         </is>
       </c>
-      <c r="P289" t="inlineStr"/>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
       <c r="Q289" t="inlineStr"/>
       <c r="R289" t="inlineStr"/>
       <c r="S289" t="inlineStr"/>
@@ -29964,7 +30840,7 @@
       </c>
       <c r="BF289" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -30050,7 +30926,7 @@
       </c>
       <c r="BF290" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -30136,7 +31012,7 @@
       </c>
       <c r="BF291" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -30222,7 +31098,7 @@
       </c>
       <c r="BF292" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -30308,7 +31184,7 @@
       </c>
       <c r="BF293" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -30394,7 +31270,7 @@
       </c>
       <c r="BF294" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -30480,7 +31356,7 @@
       </c>
       <c r="BF295" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -30566,7 +31442,7 @@
       </c>
       <c r="BF296" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -30616,7 +31492,11 @@
           <t>3-3-9</t>
         </is>
       </c>
-      <c r="P297" t="inlineStr"/>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>1,301</t>
+        </is>
+      </c>
       <c r="Q297" t="inlineStr"/>
       <c r="R297" t="inlineStr"/>
       <c r="S297" t="inlineStr"/>
@@ -30664,7 +31544,7 @@
       </c>
       <c r="BF297" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -30750,7 +31630,7 @@
       </c>
       <c r="BF298" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -30836,7 +31716,7 @@
       </c>
       <c r="BF299" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -30922,7 +31802,7 @@
       </c>
       <c r="BF300" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -31008,7 +31888,7 @@
       </c>
       <c r="BF301" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -31094,7 +31974,7 @@
       </c>
       <c r="BF302" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -31180,7 +32060,7 @@
       </c>
       <c r="BF303" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -31266,7 +32146,7 @@
       </c>
       <c r="BF304" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -31320,7 +32200,11 @@
           <t>15-17-55</t>
         </is>
       </c>
-      <c r="P305" t="inlineStr"/>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>1,004</t>
+        </is>
+      </c>
       <c r="Q305" t="inlineStr"/>
       <c r="R305" t="inlineStr"/>
       <c r="S305" t="inlineStr"/>
@@ -31368,7 +32252,7 @@
       </c>
       <c r="BF305" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -31454,7 +32338,7 @@
       </c>
       <c r="BF306" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>
@@ -31540,7 +32424,7 @@
       </c>
       <c r="BF307" t="inlineStr">
         <is>
-          <t>2025-11-15T20:09:33.390870</t>
+          <t>2025-11-15T23:37:41.662088</t>
         </is>
       </c>
     </row>

--- a/outputs/all_dogs_master.xlsx
+++ b/outputs/all_dogs_master.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -9240,7 +9240,7 @@
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9652,7 @@
       </c>
       <c r="BF85" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="BF92" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="BF93" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10512,7 @@
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10856,7 @@
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11436,7 @@
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -12748,7 +12748,7 @@
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="BF123" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13462,7 @@
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -13678,7 +13678,7 @@
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -13996,7 +13996,7 @@
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -14208,7 +14208,7 @@
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -14318,7 +14318,7 @@
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -14428,7 +14428,7 @@
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -14538,7 +14538,7 @@
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -14644,7 +14644,7 @@
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -14754,7 +14754,7 @@
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -14864,7 +14864,7 @@
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="BF138" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -15080,7 +15080,7 @@
       </c>
       <c r="BF139" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="BF140" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="BF144" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -15932,7 +15932,7 @@
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="BF148" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -16152,7 +16152,7 @@
       </c>
       <c r="BF149" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -16368,7 +16368,7 @@
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -16560,7 +16560,7 @@
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -16670,7 +16670,7 @@
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -16780,7 +16780,7 @@
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -16996,7 +16996,7 @@
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -17102,7 +17102,7 @@
       </c>
       <c r="BF158" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="BF159" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -17314,7 +17314,7 @@
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="BF161" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -17530,7 +17530,7 @@
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="BF163" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="BF164" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -17860,7 +17860,7 @@
       </c>
       <c r="BF165" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -17970,7 +17970,7 @@
       </c>
       <c r="BF166" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -18072,7 +18072,7 @@
       </c>
       <c r="BF167" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -18178,7 +18178,7 @@
       </c>
       <c r="BF168" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -18288,7 +18288,7 @@
       </c>
       <c r="BF169" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="BF170" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -18504,7 +18504,7 @@
       </c>
       <c r="BF171" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -18716,7 +18716,7 @@
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -19144,7 +19144,7 @@
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="BF178" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -19348,7 +19348,7 @@
       </c>
       <c r="BF179" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -19454,7 +19454,7 @@
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="BF183" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="BF184" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -19924,7 +19924,7 @@
       </c>
       <c r="BF185" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="BF186" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -20096,7 +20096,7 @@
       </c>
       <c r="BF187" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -20182,7 +20182,7 @@
       </c>
       <c r="BF188" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -20268,7 +20268,7 @@
       </c>
       <c r="BF189" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -20354,7 +20354,7 @@
       </c>
       <c r="BF190" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -20440,7 +20440,7 @@
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -20550,7 +20550,7 @@
       </c>
       <c r="BF192" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="BF193" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -20766,7 +20766,7 @@
       </c>
       <c r="BF194" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -20872,7 +20872,7 @@
       </c>
       <c r="BF195" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -20978,7 +20978,7 @@
       </c>
       <c r="BF196" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="BF197" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -21190,7 +21190,7 @@
       </c>
       <c r="BF198" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -21300,7 +21300,7 @@
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -21406,7 +21406,7 @@
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -21508,7 +21508,7 @@
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -21614,7 +21614,7 @@
       </c>
       <c r="BF202" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -21724,7 +21724,7 @@
       </c>
       <c r="BF203" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -21826,7 +21826,7 @@
       </c>
       <c r="BF204" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21936,7 @@
       </c>
       <c r="BF205" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -22046,7 +22046,7 @@
       </c>
       <c r="BF206" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -22156,7 +22156,7 @@
       </c>
       <c r="BF207" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -22368,7 +22368,7 @@
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="BF210" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -22576,7 +22576,7 @@
       </c>
       <c r="BF211" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -22686,7 +22686,7 @@
       </c>
       <c r="BF212" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -22792,7 +22792,7 @@
       </c>
       <c r="BF213" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -22898,7 +22898,7 @@
       </c>
       <c r="BF214" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -23004,7 +23004,7 @@
       </c>
       <c r="BF215" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="BF216" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -23220,7 +23220,7 @@
       </c>
       <c r="BF217" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -23330,7 +23330,7 @@
       </c>
       <c r="BF218" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -23440,7 +23440,7 @@
       </c>
       <c r="BF219" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -23538,7 +23538,7 @@
       </c>
       <c r="BF220" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="BF221" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="BF222" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -23860,7 +23860,7 @@
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -23970,7 +23970,7 @@
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -24072,7 +24072,7 @@
       </c>
       <c r="BF225" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -24276,7 +24276,7 @@
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="BF228" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24480,7 @@
       </c>
       <c r="BF229" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -24582,7 +24582,7 @@
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -24684,7 +24684,7 @@
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -24794,7 +24794,7 @@
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -24904,7 +24904,7 @@
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="BF234" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -25124,7 +25124,7 @@
       </c>
       <c r="BF235" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -25450,7 +25450,7 @@
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -25556,7 +25556,7 @@
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -25666,7 +25666,7 @@
       </c>
       <c r="BF240" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -25768,7 +25768,7 @@
       </c>
       <c r="BF241" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -25870,7 +25870,7 @@
       </c>
       <c r="BF242" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -25976,7 +25976,7 @@
       </c>
       <c r="BF243" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -26086,7 +26086,7 @@
       </c>
       <c r="BF244" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="BF245" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -26278,7 +26278,7 @@
       </c>
       <c r="BF246" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -26388,7 +26388,7 @@
       </c>
       <c r="BF247" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="BF248" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -26600,7 +26600,7 @@
       </c>
       <c r="BF249" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -26706,7 +26706,7 @@
       </c>
       <c r="BF250" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -26812,7 +26812,7 @@
       </c>
       <c r="BF251" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="BF252" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -27024,7 +27024,7 @@
       </c>
       <c r="BF253" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -27130,7 +27130,7 @@
       </c>
       <c r="BF254" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -27240,7 +27240,7 @@
       </c>
       <c r="BF255" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="BF256" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -27448,7 +27448,7 @@
       </c>
       <c r="BF257" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -27558,7 +27558,7 @@
       </c>
       <c r="BF258" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -27668,7 +27668,7 @@
       </c>
       <c r="BF259" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -27770,7 +27770,7 @@
       </c>
       <c r="BF260" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -27876,7 +27876,7 @@
       </c>
       <c r="BF261" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -27982,7 +27982,7 @@
       </c>
       <c r="BF262" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -28084,7 +28084,7 @@
       </c>
       <c r="BF263" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -28194,7 +28194,7 @@
       </c>
       <c r="BF264" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -28304,7 +28304,7 @@
       </c>
       <c r="BF265" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="BF266" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -28516,7 +28516,7 @@
       </c>
       <c r="BF267" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="BF268" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="BF269" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -28842,7 +28842,7 @@
       </c>
       <c r="BF270" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -28948,7 +28948,7 @@
       </c>
       <c r="BF271" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -29050,7 +29050,7 @@
       </c>
       <c r="BF272" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -29156,7 +29156,7 @@
       </c>
       <c r="BF273" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -29262,7 +29262,7 @@
       </c>
       <c r="BF274" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -29372,7 +29372,7 @@
       </c>
       <c r="BF275" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -29470,7 +29470,7 @@
       </c>
       <c r="BF276" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -29576,7 +29576,7 @@
       </c>
       <c r="BF277" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="BF278" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -29784,7 +29784,7 @@
       </c>
       <c r="BF279" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -29890,7 +29890,7 @@
       </c>
       <c r="BF280" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -30000,7 +30000,7 @@
       </c>
       <c r="BF281" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -30110,7 +30110,7 @@
       </c>
       <c r="BF282" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -30216,7 +30216,7 @@
       </c>
       <c r="BF283" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -30322,7 +30322,7 @@
       </c>
       <c r="BF284" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -30424,7 +30424,7 @@
       </c>
       <c r="BF285" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -30522,7 +30522,7 @@
       </c>
       <c r="BF286" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -30624,7 +30624,7 @@
       </c>
       <c r="BF287" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -30730,7 +30730,7 @@
       </c>
       <c r="BF288" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -30840,7 +30840,7 @@
       </c>
       <c r="BF289" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -30926,7 +30926,7 @@
       </c>
       <c r="BF290" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -31012,7 +31012,7 @@
       </c>
       <c r="BF291" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -31098,7 +31098,7 @@
       </c>
       <c r="BF292" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -31184,7 +31184,7 @@
       </c>
       <c r="BF293" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -31270,7 +31270,7 @@
       </c>
       <c r="BF294" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -31356,7 +31356,7 @@
       </c>
       <c r="BF295" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -31442,7 +31442,7 @@
       </c>
       <c r="BF296" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -31544,7 +31544,7 @@
       </c>
       <c r="BF297" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -31630,7 +31630,7 @@
       </c>
       <c r="BF298" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -31716,7 +31716,7 @@
       </c>
       <c r="BF299" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="BF300" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -31888,7 +31888,7 @@
       </c>
       <c r="BF301" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -31974,7 +31974,7 @@
       </c>
       <c r="BF302" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -32060,7 +32060,7 @@
       </c>
       <c r="BF303" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -32146,7 +32146,7 @@
       </c>
       <c r="BF304" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -32252,7 +32252,7 @@
       </c>
       <c r="BF305" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -32338,7 +32338,7 @@
       </c>
       <c r="BF306" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>
@@ -32424,7 +32424,7 @@
       </c>
       <c r="BF307" t="inlineStr">
         <is>
-          <t>2025-11-15T23:37:41.662088</t>
+          <t>2025-11-16T02:11:24.063096</t>
         </is>
       </c>
     </row>

--- a/outputs/all_dogs_master.xlsx
+++ b/outputs/all_dogs_master.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr"/>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr"/>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr"/>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr"/>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr"/>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr"/>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr"/>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr"/>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr"/>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr"/>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr"/>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr"/>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr"/>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr"/>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr"/>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr"/>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr"/>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr"/>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr"/>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr"/>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr"/>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr"/>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr"/>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr"/>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr"/>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr"/>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr"/>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr"/>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr"/>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr"/>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr"/>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr"/>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr"/>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr"/>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr"/>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr"/>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr"/>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG60" t="inlineStr"/>
@@ -10424,7 +10424,7 @@
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG61" t="inlineStr"/>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr"/>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr"/>
@@ -11040,7 +11040,7 @@
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr"/>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG66" t="inlineStr"/>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG67" t="inlineStr"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG68" t="inlineStr"/>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr"/>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr"/>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr"/>
@@ -12115,7 +12115,7 @@
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG72" t="inlineStr"/>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr"/>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr"/>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG76" t="inlineStr"/>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr"/>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr"/>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr"/>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG80" t="inlineStr"/>
@@ -13524,7 +13524,7 @@
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr"/>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr"/>
@@ -13842,7 +13842,7 @@
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG83" t="inlineStr"/>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG84" t="inlineStr"/>
@@ -14140,7 +14140,7 @@
       </c>
       <c r="BF85" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG85" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr"/>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG87" t="inlineStr"/>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr"/>
@@ -14688,7 +14688,7 @@
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr"/>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG90" t="inlineStr"/>
@@ -14962,7 +14962,7 @@
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG91" t="inlineStr"/>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="BF92" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG92" t="inlineStr"/>
@@ -15236,7 +15236,7 @@
       </c>
       <c r="BF93" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG93" t="inlineStr"/>
@@ -15373,7 +15373,7 @@
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG94" t="inlineStr"/>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG95" t="inlineStr"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG96" t="inlineStr"/>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG97" t="inlineStr"/>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG98" t="inlineStr"/>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG99" t="inlineStr"/>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG100" t="inlineStr"/>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG101" t="inlineStr"/>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG102" t="inlineStr"/>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr"/>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr"/>
@@ -16944,7 +16944,7 @@
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr"/>
@@ -17105,7 +17105,7 @@
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG106" t="inlineStr"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG107" t="inlineStr"/>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG108" t="inlineStr"/>
@@ -17588,7 +17588,7 @@
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG109" t="inlineStr"/>
@@ -17749,7 +17749,7 @@
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG110" t="inlineStr"/>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG111" t="inlineStr"/>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG112" t="inlineStr"/>
@@ -18224,7 +18224,7 @@
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG113" t="inlineStr"/>
@@ -18385,7 +18385,7 @@
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr"/>
@@ -18546,7 +18546,7 @@
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr"/>
@@ -18707,7 +18707,7 @@
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr"/>
@@ -18868,7 +18868,7 @@
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr"/>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG118" t="inlineStr"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr"/>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG120" t="inlineStr"/>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr"/>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG122" t="inlineStr"/>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="BF123" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG123" t="inlineStr"/>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr"/>
@@ -20096,7 +20096,7 @@
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr"/>
@@ -20257,7 +20257,7 @@
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr"/>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr"/>
@@ -20571,7 +20571,7 @@
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG128" t="inlineStr"/>
@@ -20728,7 +20728,7 @@
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr"/>
@@ -20881,7 +20881,7 @@
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr"/>
@@ -21042,7 +21042,7 @@
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr"/>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG132" t="inlineStr"/>
@@ -21364,7 +21364,7 @@
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG133" t="inlineStr"/>
@@ -21525,7 +21525,7 @@
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG134" t="inlineStr"/>
@@ -21682,7 +21682,7 @@
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG135" t="inlineStr"/>
@@ -21843,7 +21843,7 @@
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr"/>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr"/>
@@ -22161,7 +22161,7 @@
       </c>
       <c r="BF138" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG138" t="inlineStr"/>
@@ -22322,7 +22322,7 @@
       </c>
       <c r="BF139" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG139" t="inlineStr"/>
@@ -22475,7 +22475,7 @@
       </c>
       <c r="BF140" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG140" t="inlineStr"/>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG141" t="inlineStr"/>
@@ -22797,7 +22797,7 @@
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG142" t="inlineStr"/>
@@ -22958,7 +22958,7 @@
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG143" t="inlineStr"/>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="BF144" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG144" t="inlineStr"/>
@@ -23272,7 +23272,7 @@
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr"/>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr"/>
@@ -23582,7 +23582,7 @@
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr"/>
@@ -23743,7 +23743,7 @@
       </c>
       <c r="BF148" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG148" t="inlineStr"/>
@@ -23904,7 +23904,7 @@
       </c>
       <c r="BF149" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG149" t="inlineStr"/>
@@ -24061,7 +24061,7 @@
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr"/>
@@ -24222,7 +24222,7 @@
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG151" t="inlineStr"/>
@@ -24359,7 +24359,7 @@
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr"/>
@@ -24516,7 +24516,7 @@
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG153" t="inlineStr"/>
@@ -24677,7 +24677,7 @@
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG154" t="inlineStr"/>
@@ -24838,7 +24838,7 @@
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG155" t="inlineStr"/>
@@ -24995,7 +24995,7 @@
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG156" t="inlineStr"/>
@@ -25156,7 +25156,7 @@
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG157" t="inlineStr"/>
@@ -25313,7 +25313,7 @@
       </c>
       <c r="BF158" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG158" t="inlineStr"/>
@@ -25470,7 +25470,7 @@
       </c>
       <c r="BF159" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG159" t="inlineStr"/>
@@ -25627,7 +25627,7 @@
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG160" t="inlineStr"/>
@@ -25784,7 +25784,7 @@
       </c>
       <c r="BF161" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG161" t="inlineStr"/>
@@ -25945,7 +25945,7 @@
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG162" t="inlineStr"/>
@@ -26106,7 +26106,7 @@
       </c>
       <c r="BF163" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG163" t="inlineStr"/>
@@ -26267,7 +26267,7 @@
       </c>
       <c r="BF164" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG164" t="inlineStr"/>
@@ -26428,7 +26428,7 @@
       </c>
       <c r="BF165" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG165" t="inlineStr"/>
@@ -26589,7 +26589,7 @@
       </c>
       <c r="BF166" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG166" t="inlineStr"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="BF167" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG167" t="inlineStr"/>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="BF168" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG168" t="inlineStr"/>
@@ -27060,7 +27060,7 @@
       </c>
       <c r="BF169" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG169" t="inlineStr"/>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="BF170" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG170" t="inlineStr"/>
@@ -27378,7 +27378,7 @@
       </c>
       <c r="BF171" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG171" t="inlineStr"/>
@@ -27539,7 +27539,7 @@
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG172" t="inlineStr"/>
@@ -27692,7 +27692,7 @@
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG173" t="inlineStr"/>
@@ -27849,7 +27849,7 @@
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG174" t="inlineStr"/>
@@ -28006,7 +28006,7 @@
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG175" t="inlineStr"/>
@@ -28163,7 +28163,7 @@
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG176" t="inlineStr"/>
@@ -28324,7 +28324,7 @@
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG177" t="inlineStr"/>
@@ -28473,7 +28473,7 @@
       </c>
       <c r="BF178" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG178" t="inlineStr"/>
@@ -28630,7 +28630,7 @@
       </c>
       <c r="BF179" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG179" t="inlineStr"/>
@@ -28787,7 +28787,7 @@
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG180" t="inlineStr"/>
@@ -28944,7 +28944,7 @@
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG181" t="inlineStr"/>
@@ -29101,7 +29101,7 @@
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG182" t="inlineStr"/>
@@ -29238,7 +29238,7 @@
       </c>
       <c r="BF183" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG183" t="inlineStr"/>
@@ -29375,7 +29375,7 @@
       </c>
       <c r="BF184" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG184" t="inlineStr"/>
@@ -29512,7 +29512,7 @@
       </c>
       <c r="BF185" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG185" t="inlineStr"/>
@@ -29649,7 +29649,7 @@
       </c>
       <c r="BF186" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG186" t="inlineStr"/>
@@ -29786,7 +29786,7 @@
       </c>
       <c r="BF187" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG187" t="inlineStr"/>
@@ -29923,7 +29923,7 @@
       </c>
       <c r="BF188" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG188" t="inlineStr"/>
@@ -30060,7 +30060,7 @@
       </c>
       <c r="BF189" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG189" t="inlineStr"/>
@@ -30197,7 +30197,7 @@
       </c>
       <c r="BF190" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG190" t="inlineStr"/>
@@ -30334,7 +30334,7 @@
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG191" t="inlineStr"/>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="BF192" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG192" t="inlineStr"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="BF193" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG193" t="inlineStr"/>
@@ -30813,7 +30813,7 @@
       </c>
       <c r="BF194" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG194" t="inlineStr"/>
@@ -30970,7 +30970,7 @@
       </c>
       <c r="BF195" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG195" t="inlineStr"/>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="BF196" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG196" t="inlineStr"/>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="BF197" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG197" t="inlineStr"/>
@@ -31441,7 +31441,7 @@
       </c>
       <c r="BF198" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG198" t="inlineStr"/>
@@ -31602,7 +31602,7 @@
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG199" t="inlineStr"/>
@@ -31759,7 +31759,7 @@
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG200" t="inlineStr"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG201" t="inlineStr"/>
@@ -32069,7 +32069,7 @@
       </c>
       <c r="BF202" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG202" t="inlineStr"/>
@@ -32230,7 +32230,7 @@
       </c>
       <c r="BF203" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG203" t="inlineStr"/>
@@ -32383,7 +32383,7 @@
       </c>
       <c r="BF204" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG204" t="inlineStr"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="BF205" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG205" t="inlineStr"/>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="BF206" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG206" t="inlineStr"/>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="BF207" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG207" t="inlineStr"/>
@@ -33023,7 +33023,7 @@
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG208" t="inlineStr"/>
@@ -33180,7 +33180,7 @@
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG209" t="inlineStr"/>
@@ -33337,7 +33337,7 @@
       </c>
       <c r="BF210" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG210" t="inlineStr"/>
@@ -33490,7 +33490,7 @@
       </c>
       <c r="BF211" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG211" t="inlineStr"/>
@@ -33651,7 +33651,7 @@
       </c>
       <c r="BF212" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG212" t="inlineStr"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="BF213" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG213" t="inlineStr"/>
@@ -33965,7 +33965,7 @@
       </c>
       <c r="BF214" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG214" t="inlineStr"/>
@@ -34122,7 +34122,7 @@
       </c>
       <c r="BF215" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG215" t="inlineStr"/>
@@ -34283,7 +34283,7 @@
       </c>
       <c r="BF216" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG216" t="inlineStr"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="BF217" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG217" t="inlineStr"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="BF218" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG218" t="inlineStr"/>
@@ -34762,7 +34762,7 @@
       </c>
       <c r="BF219" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG219" t="inlineStr"/>
@@ -34911,7 +34911,7 @@
       </c>
       <c r="BF220" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG220" t="inlineStr"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="BF221" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG221" t="inlineStr"/>
@@ -35225,7 +35225,7 @@
       </c>
       <c r="BF222" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG222" t="inlineStr"/>
@@ -35386,7 +35386,7 @@
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG223" t="inlineStr"/>
@@ -35547,7 +35547,7 @@
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG224" t="inlineStr"/>
@@ -35700,7 +35700,7 @@
       </c>
       <c r="BF225" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG225" t="inlineStr"/>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
@@ -36006,7 +36006,7 @@
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="BF228" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG228" t="inlineStr"/>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="BF229" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG229" t="inlineStr"/>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG230" t="inlineStr"/>
@@ -36618,7 +36618,7 @@
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG232" t="inlineStr"/>
@@ -36940,7 +36940,7 @@
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG233" t="inlineStr"/>
@@ -37101,7 +37101,7 @@
       </c>
       <c r="BF234" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG234" t="inlineStr"/>
@@ -37262,7 +37262,7 @@
       </c>
       <c r="BF235" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG235" t="inlineStr"/>
@@ -37423,7 +37423,7 @@
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG236" t="inlineStr"/>
@@ -37580,7 +37580,7 @@
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
@@ -37741,7 +37741,7 @@
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG238" t="inlineStr"/>
@@ -37898,7 +37898,7 @@
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG239" t="inlineStr"/>
@@ -38059,7 +38059,7 @@
       </c>
       <c r="BF240" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG240" t="inlineStr"/>
@@ -38212,7 +38212,7 @@
       </c>
       <c r="BF241" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG241" t="inlineStr"/>
@@ -38365,7 +38365,7 @@
       </c>
       <c r="BF242" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG242" t="inlineStr"/>
@@ -38522,7 +38522,7 @@
       </c>
       <c r="BF243" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG243" t="inlineStr"/>
@@ -38683,7 +38683,7 @@
       </c>
       <c r="BF244" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG244" t="inlineStr"/>
@@ -38820,7 +38820,7 @@
       </c>
       <c r="BF245" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG245" t="inlineStr"/>
@@ -38977,7 +38977,7 @@
       </c>
       <c r="BF246" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG246" t="inlineStr"/>
@@ -39138,7 +39138,7 @@
       </c>
       <c r="BF247" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG247" t="inlineStr"/>
@@ -39295,7 +39295,7 @@
       </c>
       <c r="BF248" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG248" t="inlineStr"/>
@@ -39452,7 +39452,7 @@
       </c>
       <c r="BF249" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG249" t="inlineStr"/>
@@ -39609,7 +39609,7 @@
       </c>
       <c r="BF250" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG250" t="inlineStr"/>
@@ -39766,7 +39766,7 @@
       </c>
       <c r="BF251" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG251" t="inlineStr"/>
@@ -39927,7 +39927,7 @@
       </c>
       <c r="BF252" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG252" t="inlineStr"/>
@@ -40080,7 +40080,7 @@
       </c>
       <c r="BF253" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG253" t="inlineStr"/>
@@ -40237,7 +40237,7 @@
       </c>
       <c r="BF254" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG254" t="inlineStr"/>
@@ -40398,7 +40398,7 @@
       </c>
       <c r="BF255" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG255" t="inlineStr"/>
@@ -40559,7 +40559,7 @@
       </c>
       <c r="BF256" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG256" t="inlineStr"/>
@@ -40708,7 +40708,7 @@
       </c>
       <c r="BF257" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG257" t="inlineStr"/>
@@ -40869,7 +40869,7 @@
       </c>
       <c r="BF258" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG258" t="inlineStr"/>
@@ -41030,7 +41030,7 @@
       </c>
       <c r="BF259" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG259" t="inlineStr"/>
@@ -41183,7 +41183,7 @@
       </c>
       <c r="BF260" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG260" t="inlineStr"/>
@@ -41340,7 +41340,7 @@
       </c>
       <c r="BF261" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG261" t="inlineStr"/>
@@ -41497,7 +41497,7 @@
       </c>
       <c r="BF262" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG262" t="inlineStr"/>
@@ -41650,7 +41650,7 @@
       </c>
       <c r="BF263" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG263" t="inlineStr"/>
@@ -41811,7 +41811,7 @@
       </c>
       <c r="BF264" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG264" t="inlineStr"/>
@@ -41972,7 +41972,7 @@
       </c>
       <c r="BF265" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG265" t="inlineStr"/>
@@ -42125,7 +42125,7 @@
       </c>
       <c r="BF266" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG266" t="inlineStr"/>
@@ -42286,7 +42286,7 @@
       </c>
       <c r="BF267" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG267" t="inlineStr"/>
@@ -42447,7 +42447,7 @@
       </c>
       <c r="BF268" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG268" t="inlineStr"/>
@@ -42604,7 +42604,7 @@
       </c>
       <c r="BF269" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG269" t="inlineStr"/>
@@ -42765,7 +42765,7 @@
       </c>
       <c r="BF270" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG270" t="inlineStr"/>
@@ -42922,7 +42922,7 @@
       </c>
       <c r="BF271" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG271" t="inlineStr"/>
@@ -43075,7 +43075,7 @@
       </c>
       <c r="BF272" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG272" t="inlineStr"/>
@@ -43232,7 +43232,7 @@
       </c>
       <c r="BF273" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG273" t="inlineStr"/>
@@ -43389,7 +43389,7 @@
       </c>
       <c r="BF274" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG274" t="inlineStr"/>
@@ -43550,7 +43550,7 @@
       </c>
       <c r="BF275" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG275" t="inlineStr"/>
@@ -43699,7 +43699,7 @@
       </c>
       <c r="BF276" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG276" t="inlineStr"/>
@@ -43856,7 +43856,7 @@
       </c>
       <c r="BF277" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG277" t="inlineStr"/>
@@ -44017,7 +44017,7 @@
       </c>
       <c r="BF278" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG278" t="inlineStr"/>
@@ -44166,7 +44166,7 @@
       </c>
       <c r="BF279" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG279" t="inlineStr"/>
@@ -44323,7 +44323,7 @@
       </c>
       <c r="BF280" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG280" t="inlineStr"/>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="BF281" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG281" t="inlineStr"/>
@@ -44645,7 +44645,7 @@
       </c>
       <c r="BF282" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG282" t="inlineStr"/>
@@ -44802,7 +44802,7 @@
       </c>
       <c r="BF283" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG283" t="inlineStr"/>
@@ -44959,7 +44959,7 @@
       </c>
       <c r="BF284" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG284" t="inlineStr"/>
@@ -45112,7 +45112,7 @@
       </c>
       <c r="BF285" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG285" t="inlineStr"/>
@@ -45261,7 +45261,7 @@
       </c>
       <c r="BF286" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG286" t="inlineStr"/>
@@ -45414,7 +45414,7 @@
       </c>
       <c r="BF287" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG287" t="inlineStr"/>
@@ -45571,7 +45571,7 @@
       </c>
       <c r="BF288" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG288" t="inlineStr"/>
@@ -45732,7 +45732,7 @@
       </c>
       <c r="BF289" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG289" t="inlineStr"/>
@@ -45869,7 +45869,7 @@
       </c>
       <c r="BF290" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG290" t="inlineStr"/>
@@ -46006,7 +46006,7 @@
       </c>
       <c r="BF291" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG291" t="inlineStr"/>
@@ -46143,7 +46143,7 @@
       </c>
       <c r="BF292" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG292" t="inlineStr"/>
@@ -46280,7 +46280,7 @@
       </c>
       <c r="BF293" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG293" t="inlineStr"/>
@@ -46417,7 +46417,7 @@
       </c>
       <c r="BF294" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG294" t="inlineStr"/>
@@ -46554,7 +46554,7 @@
       </c>
       <c r="BF295" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG295" t="inlineStr"/>
@@ -46691,7 +46691,7 @@
       </c>
       <c r="BF296" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG296" t="inlineStr"/>
@@ -46844,7 +46844,7 @@
       </c>
       <c r="BF297" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG297" t="inlineStr"/>
@@ -46981,7 +46981,7 @@
       </c>
       <c r="BF298" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG298" t="inlineStr"/>
@@ -47118,7 +47118,7 @@
       </c>
       <c r="BF299" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG299" t="inlineStr"/>
@@ -47255,7 +47255,7 @@
       </c>
       <c r="BF300" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG300" t="inlineStr"/>
@@ -47392,7 +47392,7 @@
       </c>
       <c r="BF301" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG301" t="inlineStr"/>
@@ -47529,7 +47529,7 @@
       </c>
       <c r="BF302" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG302" t="inlineStr"/>
@@ -47666,7 +47666,7 @@
       </c>
       <c r="BF303" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG303" t="inlineStr"/>
@@ -47803,7 +47803,7 @@
       </c>
       <c r="BF304" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG304" t="inlineStr"/>
@@ -47960,7 +47960,7 @@
       </c>
       <c r="BF305" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG305" t="inlineStr"/>
@@ -48097,7 +48097,7 @@
       </c>
       <c r="BF306" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG306" t="inlineStr"/>
@@ -48234,7 +48234,7 @@
       </c>
       <c r="BF307" t="inlineStr">
         <is>
-          <t>2025-11-16T14:27:15.235112</t>
+          <t>2025-11-16T23:08:55.118190</t>
         </is>
       </c>
       <c r="BG307" t="inlineStr"/>

--- a/outputs/all_dogs_master.xlsx
+++ b/outputs/all_dogs_master.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr"/>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr"/>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr"/>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr"/>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr"/>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr"/>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr"/>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr"/>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr"/>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr"/>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr"/>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr"/>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr"/>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr"/>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr"/>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr"/>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr"/>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr"/>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr"/>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr"/>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr"/>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr"/>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr"/>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr"/>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr"/>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr"/>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr"/>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr"/>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr"/>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr"/>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr"/>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr"/>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr"/>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr"/>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr"/>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr"/>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr"/>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG60" t="inlineStr"/>
@@ -10424,7 +10424,7 @@
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG61" t="inlineStr"/>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr"/>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr"/>
@@ -11040,7 +11040,7 @@
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr"/>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG66" t="inlineStr"/>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG67" t="inlineStr"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG68" t="inlineStr"/>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr"/>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr"/>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr"/>
@@ -12115,7 +12115,7 @@
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG72" t="inlineStr"/>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr"/>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr"/>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG76" t="inlineStr"/>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr"/>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr"/>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr"/>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG80" t="inlineStr"/>
@@ -13524,7 +13524,7 @@
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr"/>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr"/>
@@ -13842,7 +13842,7 @@
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG83" t="inlineStr"/>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG84" t="inlineStr"/>
@@ -14140,7 +14140,7 @@
       </c>
       <c r="BF85" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG85" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr"/>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG87" t="inlineStr"/>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr"/>
@@ -14688,7 +14688,7 @@
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr"/>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG90" t="inlineStr"/>
@@ -14962,7 +14962,7 @@
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG91" t="inlineStr"/>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="BF92" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG92" t="inlineStr"/>
@@ -15236,7 +15236,7 @@
       </c>
       <c r="BF93" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG93" t="inlineStr"/>
@@ -15373,7 +15373,7 @@
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG94" t="inlineStr"/>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG95" t="inlineStr"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG96" t="inlineStr"/>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG97" t="inlineStr"/>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG98" t="inlineStr"/>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG99" t="inlineStr"/>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG100" t="inlineStr"/>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG101" t="inlineStr"/>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG102" t="inlineStr"/>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr"/>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr"/>
@@ -16944,7 +16944,7 @@
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr"/>
@@ -17105,7 +17105,7 @@
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG106" t="inlineStr"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG107" t="inlineStr"/>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG108" t="inlineStr"/>
@@ -17588,7 +17588,7 @@
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG109" t="inlineStr"/>
@@ -17749,7 +17749,7 @@
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG110" t="inlineStr"/>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG111" t="inlineStr"/>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG112" t="inlineStr"/>
@@ -18224,7 +18224,7 @@
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG113" t="inlineStr"/>
@@ -18385,7 +18385,7 @@
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr"/>
@@ -18546,7 +18546,7 @@
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr"/>
@@ -18707,7 +18707,7 @@
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr"/>
@@ -18868,7 +18868,7 @@
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr"/>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG118" t="inlineStr"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr"/>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG120" t="inlineStr"/>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr"/>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG122" t="inlineStr"/>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="BF123" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG123" t="inlineStr"/>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr"/>
@@ -20096,7 +20096,7 @@
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr"/>
@@ -20257,7 +20257,7 @@
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr"/>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr"/>
@@ -20571,7 +20571,7 @@
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG128" t="inlineStr"/>
@@ -20728,7 +20728,7 @@
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr"/>
@@ -20881,7 +20881,7 @@
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr"/>
@@ -21042,7 +21042,7 @@
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr"/>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG132" t="inlineStr"/>
@@ -21364,7 +21364,7 @@
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG133" t="inlineStr"/>
@@ -21525,7 +21525,7 @@
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG134" t="inlineStr"/>
@@ -21682,7 +21682,7 @@
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG135" t="inlineStr"/>
@@ -21843,7 +21843,7 @@
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr"/>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr"/>
@@ -22161,7 +22161,7 @@
       </c>
       <c r="BF138" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG138" t="inlineStr"/>
@@ -22322,7 +22322,7 @@
       </c>
       <c r="BF139" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG139" t="inlineStr"/>
@@ -22475,7 +22475,7 @@
       </c>
       <c r="BF140" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG140" t="inlineStr"/>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG141" t="inlineStr"/>
@@ -22797,7 +22797,7 @@
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG142" t="inlineStr"/>
@@ -22958,7 +22958,7 @@
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG143" t="inlineStr"/>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="BF144" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG144" t="inlineStr"/>
@@ -23272,7 +23272,7 @@
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr"/>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr"/>
@@ -23582,7 +23582,7 @@
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr"/>
@@ -23743,7 +23743,7 @@
       </c>
       <c r="BF148" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG148" t="inlineStr"/>
@@ -23904,7 +23904,7 @@
       </c>
       <c r="BF149" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG149" t="inlineStr"/>
@@ -24061,7 +24061,7 @@
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr"/>
@@ -24222,7 +24222,7 @@
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG151" t="inlineStr"/>
@@ -24359,7 +24359,7 @@
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr"/>
@@ -24516,7 +24516,7 @@
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG153" t="inlineStr"/>
@@ -24677,7 +24677,7 @@
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG154" t="inlineStr"/>
@@ -24838,7 +24838,7 @@
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG155" t="inlineStr"/>
@@ -24995,7 +24995,7 @@
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG156" t="inlineStr"/>
@@ -25156,7 +25156,7 @@
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG157" t="inlineStr"/>
@@ -25313,7 +25313,7 @@
       </c>
       <c r="BF158" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG158" t="inlineStr"/>
@@ -25470,7 +25470,7 @@
       </c>
       <c r="BF159" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG159" t="inlineStr"/>
@@ -25627,7 +25627,7 @@
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG160" t="inlineStr"/>
@@ -25784,7 +25784,7 @@
       </c>
       <c r="BF161" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG161" t="inlineStr"/>
@@ -25945,7 +25945,7 @@
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG162" t="inlineStr"/>
@@ -26106,7 +26106,7 @@
       </c>
       <c r="BF163" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG163" t="inlineStr"/>
@@ -26267,7 +26267,7 @@
       </c>
       <c r="BF164" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG164" t="inlineStr"/>
@@ -26428,7 +26428,7 @@
       </c>
       <c r="BF165" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG165" t="inlineStr"/>
@@ -26589,7 +26589,7 @@
       </c>
       <c r="BF166" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG166" t="inlineStr"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="BF167" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG167" t="inlineStr"/>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="BF168" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG168" t="inlineStr"/>
@@ -27060,7 +27060,7 @@
       </c>
       <c r="BF169" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG169" t="inlineStr"/>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="BF170" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG170" t="inlineStr"/>
@@ -27378,7 +27378,7 @@
       </c>
       <c r="BF171" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG171" t="inlineStr"/>
@@ -27539,7 +27539,7 @@
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG172" t="inlineStr"/>
@@ -27692,7 +27692,7 @@
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG173" t="inlineStr"/>
@@ -27849,7 +27849,7 @@
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG174" t="inlineStr"/>
@@ -28006,7 +28006,7 @@
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG175" t="inlineStr"/>
@@ -28163,7 +28163,7 @@
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG176" t="inlineStr"/>
@@ -28324,7 +28324,7 @@
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG177" t="inlineStr"/>
@@ -28473,7 +28473,7 @@
       </c>
       <c r="BF178" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG178" t="inlineStr"/>
@@ -28630,7 +28630,7 @@
       </c>
       <c r="BF179" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG179" t="inlineStr"/>
@@ -28787,7 +28787,7 @@
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG180" t="inlineStr"/>
@@ -28944,7 +28944,7 @@
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG181" t="inlineStr"/>
@@ -29101,7 +29101,7 @@
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG182" t="inlineStr"/>
@@ -29238,7 +29238,7 @@
       </c>
       <c r="BF183" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG183" t="inlineStr"/>
@@ -29375,7 +29375,7 @@
       </c>
       <c r="BF184" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG184" t="inlineStr"/>
@@ -29512,7 +29512,7 @@
       </c>
       <c r="BF185" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG185" t="inlineStr"/>
@@ -29649,7 +29649,7 @@
       </c>
       <c r="BF186" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG186" t="inlineStr"/>
@@ -29786,7 +29786,7 @@
       </c>
       <c r="BF187" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG187" t="inlineStr"/>
@@ -29923,7 +29923,7 @@
       </c>
       <c r="BF188" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG188" t="inlineStr"/>
@@ -30060,7 +30060,7 @@
       </c>
       <c r="BF189" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG189" t="inlineStr"/>
@@ -30197,7 +30197,7 @@
       </c>
       <c r="BF190" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG190" t="inlineStr"/>
@@ -30334,7 +30334,7 @@
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG191" t="inlineStr"/>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="BF192" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG192" t="inlineStr"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="BF193" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG193" t="inlineStr"/>
@@ -30813,7 +30813,7 @@
       </c>
       <c r="BF194" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG194" t="inlineStr"/>
@@ -30970,7 +30970,7 @@
       </c>
       <c r="BF195" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG195" t="inlineStr"/>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="BF196" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG196" t="inlineStr"/>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="BF197" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG197" t="inlineStr"/>
@@ -31441,7 +31441,7 @@
       </c>
       <c r="BF198" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG198" t="inlineStr"/>
@@ -31602,7 +31602,7 @@
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG199" t="inlineStr"/>
@@ -31759,7 +31759,7 @@
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG200" t="inlineStr"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG201" t="inlineStr"/>
@@ -32069,7 +32069,7 @@
       </c>
       <c r="BF202" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG202" t="inlineStr"/>
@@ -32230,7 +32230,7 @@
       </c>
       <c r="BF203" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG203" t="inlineStr"/>
@@ -32383,7 +32383,7 @@
       </c>
       <c r="BF204" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG204" t="inlineStr"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="BF205" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG205" t="inlineStr"/>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="BF206" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG206" t="inlineStr"/>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="BF207" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG207" t="inlineStr"/>
@@ -33023,7 +33023,7 @@
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG208" t="inlineStr"/>
@@ -33180,7 +33180,7 @@
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG209" t="inlineStr"/>
@@ -33337,7 +33337,7 @@
       </c>
       <c r="BF210" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG210" t="inlineStr"/>
@@ -33490,7 +33490,7 @@
       </c>
       <c r="BF211" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG211" t="inlineStr"/>
@@ -33651,7 +33651,7 @@
       </c>
       <c r="BF212" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG212" t="inlineStr"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="BF213" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG213" t="inlineStr"/>
@@ -33965,7 +33965,7 @@
       </c>
       <c r="BF214" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG214" t="inlineStr"/>
@@ -34122,7 +34122,7 @@
       </c>
       <c r="BF215" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG215" t="inlineStr"/>
@@ -34283,7 +34283,7 @@
       </c>
       <c r="BF216" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG216" t="inlineStr"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="BF217" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG217" t="inlineStr"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="BF218" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG218" t="inlineStr"/>
@@ -34762,7 +34762,7 @@
       </c>
       <c r="BF219" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG219" t="inlineStr"/>
@@ -34911,7 +34911,7 @@
       </c>
       <c r="BF220" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG220" t="inlineStr"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="BF221" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG221" t="inlineStr"/>
@@ -35225,7 +35225,7 @@
       </c>
       <c r="BF222" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG222" t="inlineStr"/>
@@ -35386,7 +35386,7 @@
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG223" t="inlineStr"/>
@@ -35547,7 +35547,7 @@
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG224" t="inlineStr"/>
@@ -35700,7 +35700,7 @@
       </c>
       <c r="BF225" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG225" t="inlineStr"/>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
@@ -36006,7 +36006,7 @@
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="BF228" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG228" t="inlineStr"/>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="BF229" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG229" t="inlineStr"/>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG230" t="inlineStr"/>
@@ -36618,7 +36618,7 @@
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG232" t="inlineStr"/>
@@ -36940,7 +36940,7 @@
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG233" t="inlineStr"/>
@@ -37101,7 +37101,7 @@
       </c>
       <c r="BF234" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG234" t="inlineStr"/>
@@ -37262,7 +37262,7 @@
       </c>
       <c r="BF235" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG235" t="inlineStr"/>
@@ -37423,7 +37423,7 @@
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG236" t="inlineStr"/>
@@ -37580,7 +37580,7 @@
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
@@ -37741,7 +37741,7 @@
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG238" t="inlineStr"/>
@@ -37898,7 +37898,7 @@
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG239" t="inlineStr"/>
@@ -38059,7 +38059,7 @@
       </c>
       <c r="BF240" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG240" t="inlineStr"/>
@@ -38212,7 +38212,7 @@
       </c>
       <c r="BF241" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG241" t="inlineStr"/>
@@ -38365,7 +38365,7 @@
       </c>
       <c r="BF242" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG242" t="inlineStr"/>
@@ -38522,7 +38522,7 @@
       </c>
       <c r="BF243" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG243" t="inlineStr"/>
@@ -38683,7 +38683,7 @@
       </c>
       <c r="BF244" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG244" t="inlineStr"/>
@@ -38820,7 +38820,7 @@
       </c>
       <c r="BF245" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG245" t="inlineStr"/>
@@ -38977,7 +38977,7 @@
       </c>
       <c r="BF246" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG246" t="inlineStr"/>
@@ -39138,7 +39138,7 @@
       </c>
       <c r="BF247" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG247" t="inlineStr"/>
@@ -39295,7 +39295,7 @@
       </c>
       <c r="BF248" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG248" t="inlineStr"/>
@@ -39452,7 +39452,7 @@
       </c>
       <c r="BF249" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG249" t="inlineStr"/>
@@ -39609,7 +39609,7 @@
       </c>
       <c r="BF250" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG250" t="inlineStr"/>
@@ -39766,7 +39766,7 @@
       </c>
       <c r="BF251" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG251" t="inlineStr"/>
@@ -39927,7 +39927,7 @@
       </c>
       <c r="BF252" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG252" t="inlineStr"/>
@@ -40080,7 +40080,7 @@
       </c>
       <c r="BF253" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG253" t="inlineStr"/>
@@ -40237,7 +40237,7 @@
       </c>
       <c r="BF254" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG254" t="inlineStr"/>
@@ -40398,7 +40398,7 @@
       </c>
       <c r="BF255" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG255" t="inlineStr"/>
@@ -40559,7 +40559,7 @@
       </c>
       <c r="BF256" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG256" t="inlineStr"/>
@@ -40708,7 +40708,7 @@
       </c>
       <c r="BF257" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG257" t="inlineStr"/>
@@ -40869,7 +40869,7 @@
       </c>
       <c r="BF258" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG258" t="inlineStr"/>
@@ -41030,7 +41030,7 @@
       </c>
       <c r="BF259" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG259" t="inlineStr"/>
@@ -41183,7 +41183,7 @@
       </c>
       <c r="BF260" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG260" t="inlineStr"/>
@@ -41340,7 +41340,7 @@
       </c>
       <c r="BF261" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG261" t="inlineStr"/>
@@ -41497,7 +41497,7 @@
       </c>
       <c r="BF262" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG262" t="inlineStr"/>
@@ -41650,7 +41650,7 @@
       </c>
       <c r="BF263" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG263" t="inlineStr"/>
@@ -41811,7 +41811,7 @@
       </c>
       <c r="BF264" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG264" t="inlineStr"/>
@@ -41972,7 +41972,7 @@
       </c>
       <c r="BF265" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG265" t="inlineStr"/>
@@ -42125,7 +42125,7 @@
       </c>
       <c r="BF266" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG266" t="inlineStr"/>
@@ -42286,7 +42286,7 @@
       </c>
       <c r="BF267" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG267" t="inlineStr"/>
@@ -42447,7 +42447,7 @@
       </c>
       <c r="BF268" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG268" t="inlineStr"/>
@@ -42604,7 +42604,7 @@
       </c>
       <c r="BF269" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG269" t="inlineStr"/>
@@ -42765,7 +42765,7 @@
       </c>
       <c r="BF270" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG270" t="inlineStr"/>
@@ -42922,7 +42922,7 @@
       </c>
       <c r="BF271" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG271" t="inlineStr"/>
@@ -43075,7 +43075,7 @@
       </c>
       <c r="BF272" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG272" t="inlineStr"/>
@@ -43232,7 +43232,7 @@
       </c>
       <c r="BF273" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG273" t="inlineStr"/>
@@ -43389,7 +43389,7 @@
       </c>
       <c r="BF274" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG274" t="inlineStr"/>
@@ -43550,7 +43550,7 @@
       </c>
       <c r="BF275" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG275" t="inlineStr"/>
@@ -43699,7 +43699,7 @@
       </c>
       <c r="BF276" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG276" t="inlineStr"/>
@@ -43856,7 +43856,7 @@
       </c>
       <c r="BF277" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG277" t="inlineStr"/>
@@ -44017,7 +44017,7 @@
       </c>
       <c r="BF278" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG278" t="inlineStr"/>
@@ -44166,7 +44166,7 @@
       </c>
       <c r="BF279" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG279" t="inlineStr"/>
@@ -44323,7 +44323,7 @@
       </c>
       <c r="BF280" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG280" t="inlineStr"/>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="BF281" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG281" t="inlineStr"/>
@@ -44645,7 +44645,7 @@
       </c>
       <c r="BF282" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG282" t="inlineStr"/>
@@ -44802,7 +44802,7 @@
       </c>
       <c r="BF283" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG283" t="inlineStr"/>
@@ -44959,7 +44959,7 @@
       </c>
       <c r="BF284" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG284" t="inlineStr"/>
@@ -45112,7 +45112,7 @@
       </c>
       <c r="BF285" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG285" t="inlineStr"/>
@@ -45261,7 +45261,7 @@
       </c>
       <c r="BF286" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG286" t="inlineStr"/>
@@ -45414,7 +45414,7 @@
       </c>
       <c r="BF287" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG287" t="inlineStr"/>
@@ -45571,7 +45571,7 @@
       </c>
       <c r="BF288" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG288" t="inlineStr"/>
@@ -45732,7 +45732,7 @@
       </c>
       <c r="BF289" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG289" t="inlineStr"/>
@@ -45869,7 +45869,7 @@
       </c>
       <c r="BF290" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG290" t="inlineStr"/>
@@ -46006,7 +46006,7 @@
       </c>
       <c r="BF291" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG291" t="inlineStr"/>
@@ -46143,7 +46143,7 @@
       </c>
       <c r="BF292" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG292" t="inlineStr"/>
@@ -46280,7 +46280,7 @@
       </c>
       <c r="BF293" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG293" t="inlineStr"/>
@@ -46417,7 +46417,7 @@
       </c>
       <c r="BF294" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG294" t="inlineStr"/>
@@ -46554,7 +46554,7 @@
       </c>
       <c r="BF295" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG295" t="inlineStr"/>
@@ -46691,7 +46691,7 @@
       </c>
       <c r="BF296" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG296" t="inlineStr"/>
@@ -46844,7 +46844,7 @@
       </c>
       <c r="BF297" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG297" t="inlineStr"/>
@@ -46981,7 +46981,7 @@
       </c>
       <c r="BF298" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG298" t="inlineStr"/>
@@ -47118,7 +47118,7 @@
       </c>
       <c r="BF299" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG299" t="inlineStr"/>
@@ -47255,7 +47255,7 @@
       </c>
       <c r="BF300" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG300" t="inlineStr"/>
@@ -47392,7 +47392,7 @@
       </c>
       <c r="BF301" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG301" t="inlineStr"/>
@@ -47529,7 +47529,7 @@
       </c>
       <c r="BF302" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG302" t="inlineStr"/>
@@ -47666,7 +47666,7 @@
       </c>
       <c r="BF303" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG303" t="inlineStr"/>
@@ -47803,7 +47803,7 @@
       </c>
       <c r="BF304" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG304" t="inlineStr"/>
@@ -47960,7 +47960,7 @@
       </c>
       <c r="BF305" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG305" t="inlineStr"/>
@@ -48097,7 +48097,7 @@
       </c>
       <c r="BF306" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG306" t="inlineStr"/>
@@ -48234,7 +48234,7 @@
       </c>
       <c r="BF307" t="inlineStr">
         <is>
-          <t>2025-11-16T23:08:55.118190</t>
+          <t>2025-11-16T23:50:10.554641</t>
         </is>
       </c>
       <c r="BG307" t="inlineStr"/>

--- a/outputs/all_dogs_master.xlsx
+++ b/outputs/all_dogs_master.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr"/>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr"/>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr"/>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr"/>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr"/>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr"/>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr"/>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr"/>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr"/>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr"/>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr"/>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr"/>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr"/>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr"/>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr"/>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr"/>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr"/>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr"/>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr"/>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr"/>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr"/>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr"/>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr"/>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr"/>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr"/>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr"/>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr"/>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr"/>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr"/>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr"/>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr"/>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr"/>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr"/>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr"/>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr"/>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr"/>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr"/>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG60" t="inlineStr"/>
@@ -10424,7 +10424,7 @@
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG61" t="inlineStr"/>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr"/>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr"/>
@@ -11040,7 +11040,7 @@
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr"/>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG66" t="inlineStr"/>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG67" t="inlineStr"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG68" t="inlineStr"/>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr"/>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr"/>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr"/>
@@ -12115,7 +12115,7 @@
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG72" t="inlineStr"/>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr"/>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr"/>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG76" t="inlineStr"/>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr"/>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr"/>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr"/>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG80" t="inlineStr"/>
@@ -13524,7 +13524,7 @@
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr"/>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr"/>
@@ -13842,7 +13842,7 @@
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG83" t="inlineStr"/>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG84" t="inlineStr"/>
@@ -14140,7 +14140,7 @@
       </c>
       <c r="BF85" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG85" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr"/>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG87" t="inlineStr"/>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr"/>
@@ -14688,7 +14688,7 @@
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr"/>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG90" t="inlineStr"/>
@@ -14962,7 +14962,7 @@
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG91" t="inlineStr"/>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="BF92" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG92" t="inlineStr"/>
@@ -15236,7 +15236,7 @@
       </c>
       <c r="BF93" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG93" t="inlineStr"/>
@@ -15373,7 +15373,7 @@
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG94" t="inlineStr"/>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG95" t="inlineStr"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG96" t="inlineStr"/>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG97" t="inlineStr"/>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG98" t="inlineStr"/>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG99" t="inlineStr"/>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG100" t="inlineStr"/>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG101" t="inlineStr"/>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG102" t="inlineStr"/>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr"/>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr"/>
@@ -16944,7 +16944,7 @@
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr"/>
@@ -17105,7 +17105,7 @@
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG106" t="inlineStr"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG107" t="inlineStr"/>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG108" t="inlineStr"/>
@@ -17588,7 +17588,7 @@
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG109" t="inlineStr"/>
@@ -17749,7 +17749,7 @@
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG110" t="inlineStr"/>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG111" t="inlineStr"/>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG112" t="inlineStr"/>
@@ -18224,7 +18224,7 @@
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG113" t="inlineStr"/>
@@ -18385,7 +18385,7 @@
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr"/>
@@ -18546,7 +18546,7 @@
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr"/>
@@ -18707,7 +18707,7 @@
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr"/>
@@ -18868,7 +18868,7 @@
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr"/>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG118" t="inlineStr"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr"/>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG120" t="inlineStr"/>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr"/>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG122" t="inlineStr"/>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="BF123" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG123" t="inlineStr"/>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr"/>
@@ -20096,7 +20096,7 @@
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr"/>
@@ -20257,7 +20257,7 @@
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr"/>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr"/>
@@ -20571,7 +20571,7 @@
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG128" t="inlineStr"/>
@@ -20728,7 +20728,7 @@
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr"/>
@@ -20881,7 +20881,7 @@
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr"/>
@@ -21042,7 +21042,7 @@
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr"/>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG132" t="inlineStr"/>
@@ -21364,7 +21364,7 @@
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG133" t="inlineStr"/>
@@ -21525,7 +21525,7 @@
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG134" t="inlineStr"/>
@@ -21682,7 +21682,7 @@
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG135" t="inlineStr"/>
@@ -21843,7 +21843,7 @@
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr"/>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr"/>
@@ -22161,7 +22161,7 @@
       </c>
       <c r="BF138" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG138" t="inlineStr"/>
@@ -22322,7 +22322,7 @@
       </c>
       <c r="BF139" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG139" t="inlineStr"/>
@@ -22475,7 +22475,7 @@
       </c>
       <c r="BF140" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG140" t="inlineStr"/>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG141" t="inlineStr"/>
@@ -22797,7 +22797,7 @@
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG142" t="inlineStr"/>
@@ -22958,7 +22958,7 @@
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG143" t="inlineStr"/>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="BF144" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG144" t="inlineStr"/>
@@ -23272,7 +23272,7 @@
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr"/>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr"/>
@@ -23582,7 +23582,7 @@
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr"/>
@@ -23743,7 +23743,7 @@
       </c>
       <c r="BF148" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG148" t="inlineStr"/>
@@ -23904,7 +23904,7 @@
       </c>
       <c r="BF149" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG149" t="inlineStr"/>
@@ -24061,7 +24061,7 @@
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr"/>
@@ -24222,7 +24222,7 @@
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG151" t="inlineStr"/>
@@ -24359,7 +24359,7 @@
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr"/>
@@ -24516,7 +24516,7 @@
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG153" t="inlineStr"/>
@@ -24677,7 +24677,7 @@
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG154" t="inlineStr"/>
@@ -24838,7 +24838,7 @@
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG155" t="inlineStr"/>
@@ -24995,7 +24995,7 @@
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG156" t="inlineStr"/>
@@ -25156,7 +25156,7 @@
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG157" t="inlineStr"/>
@@ -25313,7 +25313,7 @@
       </c>
       <c r="BF158" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG158" t="inlineStr"/>
@@ -25470,7 +25470,7 @@
       </c>
       <c r="BF159" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG159" t="inlineStr"/>
@@ -25627,7 +25627,7 @@
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG160" t="inlineStr"/>
@@ -25784,7 +25784,7 @@
       </c>
       <c r="BF161" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG161" t="inlineStr"/>
@@ -25945,7 +25945,7 @@
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG162" t="inlineStr"/>
@@ -26106,7 +26106,7 @@
       </c>
       <c r="BF163" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG163" t="inlineStr"/>
@@ -26267,7 +26267,7 @@
       </c>
       <c r="BF164" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG164" t="inlineStr"/>
@@ -26428,7 +26428,7 @@
       </c>
       <c r="BF165" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG165" t="inlineStr"/>
@@ -26589,7 +26589,7 @@
       </c>
       <c r="BF166" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG166" t="inlineStr"/>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="BF167" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG167" t="inlineStr"/>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="BF168" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG168" t="inlineStr"/>
@@ -27060,7 +27060,7 @@
       </c>
       <c r="BF169" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG169" t="inlineStr"/>
@@ -27221,7 +27221,7 @@
       </c>
       <c r="BF170" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG170" t="inlineStr"/>
@@ -27378,7 +27378,7 @@
       </c>
       <c r="BF171" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG171" t="inlineStr"/>
@@ -27539,7 +27539,7 @@
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG172" t="inlineStr"/>
@@ -27692,7 +27692,7 @@
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG173" t="inlineStr"/>
@@ -27849,7 +27849,7 @@
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG174" t="inlineStr"/>
@@ -28006,7 +28006,7 @@
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG175" t="inlineStr"/>
@@ -28163,7 +28163,7 @@
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG176" t="inlineStr"/>
@@ -28324,7 +28324,7 @@
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG177" t="inlineStr"/>
@@ -28473,7 +28473,7 @@
       </c>
       <c r="BF178" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG178" t="inlineStr"/>
@@ -28630,7 +28630,7 @@
       </c>
       <c r="BF179" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG179" t="inlineStr"/>
@@ -28787,7 +28787,7 @@
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG180" t="inlineStr"/>
@@ -28944,7 +28944,7 @@
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG181" t="inlineStr"/>
@@ -29101,7 +29101,7 @@
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG182" t="inlineStr"/>
@@ -29238,7 +29238,7 @@
       </c>
       <c r="BF183" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG183" t="inlineStr"/>
@@ -29375,7 +29375,7 @@
       </c>
       <c r="BF184" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG184" t="inlineStr"/>
@@ -29512,7 +29512,7 @@
       </c>
       <c r="BF185" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG185" t="inlineStr"/>
@@ -29649,7 +29649,7 @@
       </c>
       <c r="BF186" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG186" t="inlineStr"/>
@@ -29786,7 +29786,7 @@
       </c>
       <c r="BF187" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG187" t="inlineStr"/>
@@ -29923,7 +29923,7 @@
       </c>
       <c r="BF188" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG188" t="inlineStr"/>
@@ -30060,7 +30060,7 @@
       </c>
       <c r="BF189" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG189" t="inlineStr"/>
@@ -30197,7 +30197,7 @@
       </c>
       <c r="BF190" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG190" t="inlineStr"/>
@@ -30334,7 +30334,7 @@
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG191" t="inlineStr"/>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="BF192" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG192" t="inlineStr"/>
@@ -30652,7 +30652,7 @@
       </c>
       <c r="BF193" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG193" t="inlineStr"/>
@@ -30813,7 +30813,7 @@
       </c>
       <c r="BF194" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG194" t="inlineStr"/>
@@ -30970,7 +30970,7 @@
       </c>
       <c r="BF195" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG195" t="inlineStr"/>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="BF196" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG196" t="inlineStr"/>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="BF197" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG197" t="inlineStr"/>
@@ -31441,7 +31441,7 @@
       </c>
       <c r="BF198" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG198" t="inlineStr"/>
@@ -31602,7 +31602,7 @@
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG199" t="inlineStr"/>
@@ -31759,7 +31759,7 @@
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG200" t="inlineStr"/>
@@ -31912,7 +31912,7 @@
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG201" t="inlineStr"/>
@@ -32069,7 +32069,7 @@
       </c>
       <c r="BF202" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG202" t="inlineStr"/>
@@ -32230,7 +32230,7 @@
       </c>
       <c r="BF203" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG203" t="inlineStr"/>
@@ -32383,7 +32383,7 @@
       </c>
       <c r="BF204" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG204" t="inlineStr"/>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="BF205" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG205" t="inlineStr"/>
@@ -32705,7 +32705,7 @@
       </c>
       <c r="BF206" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG206" t="inlineStr"/>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="BF207" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG207" t="inlineStr"/>
@@ -33023,7 +33023,7 @@
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG208" t="inlineStr"/>
@@ -33180,7 +33180,7 @@
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG209" t="inlineStr"/>
@@ -33337,7 +33337,7 @@
       </c>
       <c r="BF210" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG210" t="inlineStr"/>
@@ -33490,7 +33490,7 @@
       </c>
       <c r="BF211" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG211" t="inlineStr"/>
@@ -33651,7 +33651,7 @@
       </c>
       <c r="BF212" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG212" t="inlineStr"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="BF213" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG213" t="inlineStr"/>
@@ -33965,7 +33965,7 @@
       </c>
       <c r="BF214" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG214" t="inlineStr"/>
@@ -34122,7 +34122,7 @@
       </c>
       <c r="BF215" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG215" t="inlineStr"/>
@@ -34283,7 +34283,7 @@
       </c>
       <c r="BF216" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG216" t="inlineStr"/>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="BF217" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG217" t="inlineStr"/>
@@ -34601,7 +34601,7 @@
       </c>
       <c r="BF218" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG218" t="inlineStr"/>
@@ -34762,7 +34762,7 @@
       </c>
       <c r="BF219" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG219" t="inlineStr"/>
@@ -34911,7 +34911,7 @@
       </c>
       <c r="BF220" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG220" t="inlineStr"/>
@@ -35068,7 +35068,7 @@
       </c>
       <c r="BF221" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG221" t="inlineStr"/>
@@ -35225,7 +35225,7 @@
       </c>
       <c r="BF222" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG222" t="inlineStr"/>
@@ -35386,7 +35386,7 @@
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG223" t="inlineStr"/>
@@ -35547,7 +35547,7 @@
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG224" t="inlineStr"/>
@@ -35700,7 +35700,7 @@
       </c>
       <c r="BF225" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG225" t="inlineStr"/>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
@@ -36006,7 +36006,7 @@
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="BF228" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG228" t="inlineStr"/>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="BF229" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG229" t="inlineStr"/>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG230" t="inlineStr"/>
@@ -36618,7 +36618,7 @@
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG232" t="inlineStr"/>
@@ -36940,7 +36940,7 @@
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG233" t="inlineStr"/>
@@ -37101,7 +37101,7 @@
       </c>
       <c r="BF234" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG234" t="inlineStr"/>
@@ -37262,7 +37262,7 @@
       </c>
       <c r="BF235" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG235" t="inlineStr"/>
@@ -37423,7 +37423,7 @@
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG236" t="inlineStr"/>
@@ -37580,7 +37580,7 @@
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
@@ -37741,7 +37741,7 @@
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG238" t="inlineStr"/>
@@ -37898,7 +37898,7 @@
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG239" t="inlineStr"/>
@@ -38059,7 +38059,7 @@
       </c>
       <c r="BF240" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG240" t="inlineStr"/>
@@ -38212,7 +38212,7 @@
       </c>
       <c r="BF241" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG241" t="inlineStr"/>
@@ -38365,7 +38365,7 @@
       </c>
       <c r="BF242" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG242" t="inlineStr"/>
@@ -38522,7 +38522,7 @@
       </c>
       <c r="BF243" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG243" t="inlineStr"/>
@@ -38683,7 +38683,7 @@
       </c>
       <c r="BF244" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG244" t="inlineStr"/>
@@ -38820,7 +38820,7 @@
       </c>
       <c r="BF245" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG245" t="inlineStr"/>
@@ -38977,7 +38977,7 @@
       </c>
       <c r="BF246" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG246" t="inlineStr"/>
@@ -39138,7 +39138,7 @@
       </c>
       <c r="BF247" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG247" t="inlineStr"/>
@@ -39295,7 +39295,7 @@
       </c>
       <c r="BF248" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG248" t="inlineStr"/>
@@ -39452,7 +39452,7 @@
       </c>
       <c r="BF249" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG249" t="inlineStr"/>
@@ -39609,7 +39609,7 @@
       </c>
       <c r="BF250" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG250" t="inlineStr"/>
@@ -39766,7 +39766,7 @@
       </c>
       <c r="BF251" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG251" t="inlineStr"/>
@@ -39927,7 +39927,7 @@
       </c>
       <c r="BF252" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG252" t="inlineStr"/>
@@ -40080,7 +40080,7 @@
       </c>
       <c r="BF253" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG253" t="inlineStr"/>
@@ -40237,7 +40237,7 @@
       </c>
       <c r="BF254" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG254" t="inlineStr"/>
@@ -40398,7 +40398,7 @@
       </c>
       <c r="BF255" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG255" t="inlineStr"/>
@@ -40559,7 +40559,7 @@
       </c>
       <c r="BF256" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG256" t="inlineStr"/>
@@ -40708,7 +40708,7 @@
       </c>
       <c r="BF257" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG257" t="inlineStr"/>
@@ -40869,7 +40869,7 @@
       </c>
       <c r="BF258" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG258" t="inlineStr"/>
@@ -41030,7 +41030,7 @@
       </c>
       <c r="BF259" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG259" t="inlineStr"/>
@@ -41183,7 +41183,7 @@
       </c>
       <c r="BF260" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG260" t="inlineStr"/>
@@ -41340,7 +41340,7 @@
       </c>
       <c r="BF261" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG261" t="inlineStr"/>
@@ -41497,7 +41497,7 @@
       </c>
       <c r="BF262" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG262" t="inlineStr"/>
@@ -41650,7 +41650,7 @@
       </c>
       <c r="BF263" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG263" t="inlineStr"/>
@@ -41811,7 +41811,7 @@
       </c>
       <c r="BF264" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG264" t="inlineStr"/>
@@ -41972,7 +41972,7 @@
       </c>
       <c r="BF265" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG265" t="inlineStr"/>
@@ -42125,7 +42125,7 @@
       </c>
       <c r="BF266" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG266" t="inlineStr"/>
@@ -42286,7 +42286,7 @@
       </c>
       <c r="BF267" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG267" t="inlineStr"/>
@@ -42447,7 +42447,7 @@
       </c>
       <c r="BF268" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG268" t="inlineStr"/>
@@ -42604,7 +42604,7 @@
       </c>
       <c r="BF269" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG269" t="inlineStr"/>
@@ -42765,7 +42765,7 @@
       </c>
       <c r="BF270" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG270" t="inlineStr"/>
@@ -42922,7 +42922,7 @@
       </c>
       <c r="BF271" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG271" t="inlineStr"/>
@@ -43075,7 +43075,7 @@
       </c>
       <c r="BF272" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG272" t="inlineStr"/>
@@ -43232,7 +43232,7 @@
       </c>
       <c r="BF273" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG273" t="inlineStr"/>
@@ -43389,7 +43389,7 @@
       </c>
       <c r="BF274" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG274" t="inlineStr"/>
@@ -43550,7 +43550,7 @@
       </c>
       <c r="BF275" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG275" t="inlineStr"/>
@@ -43699,7 +43699,7 @@
       </c>
       <c r="BF276" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG276" t="inlineStr"/>
@@ -43856,7 +43856,7 @@
       </c>
       <c r="BF277" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG277" t="inlineStr"/>
@@ -44017,7 +44017,7 @@
       </c>
       <c r="BF278" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG278" t="inlineStr"/>
@@ -44166,7 +44166,7 @@
       </c>
       <c r="BF279" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG279" t="inlineStr"/>
@@ -44323,7 +44323,7 @@
       </c>
       <c r="BF280" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG280" t="inlineStr"/>
@@ -44484,7 +44484,7 @@
       </c>
       <c r="BF281" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG281" t="inlineStr"/>
@@ -44645,7 +44645,7 @@
       </c>
       <c r="BF282" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG282" t="inlineStr"/>
@@ -44802,7 +44802,7 @@
       </c>
       <c r="BF283" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG283" t="inlineStr"/>
@@ -44959,7 +44959,7 @@
       </c>
       <c r="BF284" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG284" t="inlineStr"/>
@@ -45112,7 +45112,7 @@
       </c>
       <c r="BF285" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG285" t="inlineStr"/>
@@ -45261,7 +45261,7 @@
       </c>
       <c r="BF286" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG286" t="inlineStr"/>
@@ -45414,7 +45414,7 @@
       </c>
       <c r="BF287" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG287" t="inlineStr"/>
@@ -45571,7 +45571,7 @@
       </c>
       <c r="BF288" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG288" t="inlineStr"/>
@@ -45732,7 +45732,7 @@
       </c>
       <c r="BF289" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG289" t="inlineStr"/>
@@ -45869,7 +45869,7 @@
       </c>
       <c r="BF290" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG290" t="inlineStr"/>
@@ -46006,7 +46006,7 @@
       </c>
       <c r="BF291" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG291" t="inlineStr"/>
@@ -46143,7 +46143,7 @@
       </c>
       <c r="BF292" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG292" t="inlineStr"/>
@@ -46280,7 +46280,7 @@
       </c>
       <c r="BF293" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG293" t="inlineStr"/>
@@ -46417,7 +46417,7 @@
       </c>
       <c r="BF294" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG294" t="inlineStr"/>
@@ -46554,7 +46554,7 @@
       </c>
       <c r="BF295" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG295" t="inlineStr"/>
@@ -46691,7 +46691,7 @@
       </c>
       <c r="BF296" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG296" t="inlineStr"/>
@@ -46844,7 +46844,7 @@
       </c>
       <c r="BF297" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG297" t="inlineStr"/>
@@ -46981,7 +46981,7 @@
       </c>
       <c r="BF298" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG298" t="inlineStr"/>
@@ -47118,7 +47118,7 @@
       </c>
       <c r="BF299" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG299" t="inlineStr"/>
@@ -47255,7 +47255,7 @@
       </c>
       <c r="BF300" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG300" t="inlineStr"/>
@@ -47392,7 +47392,7 @@
       </c>
       <c r="BF301" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG301" t="inlineStr"/>
@@ -47529,7 +47529,7 @@
       </c>
       <c r="BF302" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG302" t="inlineStr"/>
@@ -47666,7 +47666,7 @@
       </c>
       <c r="BF303" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG303" t="inlineStr"/>
@@ -47803,7 +47803,7 @@
       </c>
       <c r="BF304" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG304" t="inlineStr"/>
@@ -47960,7 +47960,7 @@
       </c>
       <c r="BF305" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG305" t="inlineStr"/>
@@ -48097,7 +48097,7 @@
       </c>
       <c r="BF306" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG306" t="inlineStr"/>
@@ -48234,7 +48234,7 @@
       </c>
       <c r="BF307" t="inlineStr">
         <is>
-          <t>2025-11-16T23:50:10.554641</t>
+          <t>2025-11-17T01:22:47.084247</t>
         </is>
       </c>
       <c r="BG307" t="inlineStr"/>
